--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1220,6 +1220,822 @@
       <c r="B67" t="inlineStr">
         <is>
           <t>TYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>shop_ui.header</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>상점</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>inventory_ui.header</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>인벤토리</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>upgrade_ui.header</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>강화</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>item_tooltip_ui.sub_option_label</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>부가 옵션</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>item_tooltip_ui.unique_effect_label</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>고유 효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>upgrade_ui.current_stat</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>현재 스탯 : {0} + {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>upgrade_ui.next_stat</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>강화 후 스탯 : {0} + {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>upgrade_ui.cost</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>강화비용 : {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>upgrade_ui.cost_unavailable</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>강화비용 : -</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>upgrade_ui.unknown_item</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>아이템</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>upgrade_ui.selection_required</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>강화할 아이템을 선택하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_success</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>{0} +{1} 강화 성공</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_not_enough_gold</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>골드가 부족합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_invalid_item</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>강화할 수 없는 아이템입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_invalid_cost</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>강화 비용 설정이 올바르지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_wallet_unavailable</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>강화 처리 중 문제가 발생했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_failed</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>강화에 실패했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>npc_ui.quest</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>의뢰</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>npc_ui.rest</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>휴식</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_success</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>장비 처리가 완료되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_swapped</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>장비를 교체했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_invalid_item</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>장착할 수 없는 아이템입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_invalid_slot</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>해당 슬롯에 장착할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_slot_occupied</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>이미 장비가 장착되어 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_not_equipped</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>해제할 장비가 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_no_return_space</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>기존 장비를 인벤토리에 내려놓을 공간이 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_failed</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>장비 처리가 실패했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_wrong_class</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>이 캐릭터가 장착할 수 없는 무기입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_unknown</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>알 수 없는 장비 처리 결과입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_acquisition</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>{0} 아이템을 획득했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_acquisition_colored</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>{0} 획득했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_success_position</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>{0} 위치 : {1}, {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_invalid_item</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>유효하지 않은 아이템입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_no_space</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>인벤토리가 꽉 찼습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_grid_unavailable</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>인벤토리를 사용할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_placement_failed</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>인벤토리에 아이템을 배치하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_add_failed</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>아이템 획득에 실패했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_success</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>{0}을(를) 삭제했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_invalid_item</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>유효하지 않은 아이템입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_unavailable</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>인벤토리를 사용할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_not_player</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>내 인벤토리의 아이템만 삭제할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>장착 중인 아이템은 바로 삭제할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_failed</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>아이템 삭제에 실패했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_default_failed</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>아이템을 삭제하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_buy_success</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>{0}을 구매했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_sell_success</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>{0}을 판매했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_not_enough_gold</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>골드가 부족해 {0} 구매에 실패했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_no_space_buy</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>인벤토리에 공간이 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_no_space_sell</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>상점에 판매 아이템을 놓을 공간이 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_invalid_item</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>유효하지 않은 아이템입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_transfer_failed</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>{0} 이동 중 거래에 실패했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_stock_update_failed</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>{0} 재고 처리에 실패했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_failed</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>거래 처리에 실패했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>chat_ui.pickup_default</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>아이템을 획득했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>chat_ui.out_of_range</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>아이템에 더 가까이 이동해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>chat_ui.already_claimed</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>이미 획득된 아이템입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>chat_ui.pickup_unavailable</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>더 이상 획득할 수 없는 아이템입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>chat_ui.item_unavailable</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>대상 아이템을 찾을 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>chat_ui.stale_revision</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>아이템 상태가 바뀌었습니다. 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>chat_ui.recovery_failed</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>아이템 드랍과 인벤토리 복구에 실패했습니다. 인벤토리 상태를 확인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>chat_ui.upgrade_process_failed</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>강화를 처리하지 못했습니다. 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>chat_ui.drop_failed</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>아이템을 필드에 놓지 못했습니다. 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>chat_ui.acquisition_failed</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>아이템을 획득하지 못했습니다. 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_state_changed</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>상점 상태가 바뀌었습니다. 다시 선택해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_state_changed</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>인벤토리 상태가 바뀌었습니다. 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>chat_ui.trade_failed</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>거래를 처리하지 못했습니다. 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>loading_ui.tooltip_title</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>데브리스-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>loading_ui.tooltip_content</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>이곳은 오염으로 인해 인간이 살 수 없는 버려진 땅이었지만, 수백 년간 쌓인 로봇 잔해들이 스스로를 복구하고 개조하기 시작하면서 기괴한 메카 생태계가 만들어졌습니다.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +2050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2038,6 +2854,822 @@
       <c r="B67" t="inlineStr">
         <is>
           <t>TYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>shop_ui.header</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>inventory_ui.header</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>upgrade_ui.header</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>item_tooltip_ui.sub_option_label</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>item_tooltip_ui.unique_effect_label</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unique Effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>upgrade_ui.current_stat</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Current Stat: {0} + {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>upgrade_ui.next_stat</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>After Upgrade: {0} + {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>upgrade_ui.cost</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Upgrade Cost: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>upgrade_ui.cost_unavailable</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Upgrade Cost: -</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>upgrade_ui.unknown_item</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>upgrade_ui.selection_required</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Please select an item to upgrade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_success</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>{0} +{1} Upgrade Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_not_enough_gold</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Not enough gold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_invalid_item</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>This item cannot be upgraded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_invalid_cost</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>The upgrade cost setting is invalid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_wallet_unavailable</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>A problem occurred while processing the upgrade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_failed</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Upgrade failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>npc_ui.quest</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Quest</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>npc_ui.rest</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_success</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Equipment updated successfully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_swapped</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Equipment swapped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_invalid_item</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>This item cannot be equipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_invalid_slot</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Cannot equip to that slot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_slot_occupied</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Equipment is already equipped there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_not_equipped</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>There is no equipment to unequip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_no_return_space</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>No inventory space to store the previous equipment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_failed</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Failed to process equipment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_wrong_class</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>This character cannot equip this weapon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_unknown</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Unknown equipment processing result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_acquisition</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Obtained item: {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_acquisition_colored</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Obtained {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_success_position</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>{0} Position: {1}, {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_invalid_item</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>This item is not valid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_no_space</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Inventory is full!</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_grid_unavailable</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Inventory is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_placement_failed</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Failed to place the item in the inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_add_failed</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Failed to obtain the item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_success</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deleted {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_invalid_item</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>This item is not valid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_unavailable</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Inventory is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_not_player</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>You can only delete items from your own inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Equipped items cannot be deleted directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_failed</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Failed to delete the item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_default_failed</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Could not delete the item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_buy_success</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Purchased {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_sell_success</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Sold {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_not_enough_gold</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Not enough gold to purchase {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_no_space_buy</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>No space in your inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_no_space_sell</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>No space in the shop to place the item for sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_invalid_item</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>This item is not valid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_transfer_failed</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>The trade failed while moving {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_stock_update_failed</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Failed to update stock for {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_failed</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Failed to process the trade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>chat_ui.pickup_default</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Obtained the item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>chat_ui.out_of_range</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Please move closer to the item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>chat_ui.already_claimed</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>This item has already been claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>chat_ui.pickup_unavailable</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>This item can no longer be obtained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>chat_ui.item_unavailable</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>The target item could not be found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>chat_ui.stale_revision</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>The item's state has changed. Please try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>chat_ui.recovery_failed</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Failed to drop the item and restore the inventory. Please check your inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>chat_ui.upgrade_process_failed</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Failed to process the upgrade. Please try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>chat_ui.drop_failed</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Failed to drop the item on the field. Please try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>chat_ui.acquisition_failed</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Failed to obtain the item. Please try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_state_changed</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>The shop's state has changed. Please select again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_state_changed</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>The inventory's state has changed. Please try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>chat_ui.trade_failed</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Failed to process the trade. Please try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>loading_ui.tooltip_title</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Debris-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>loading_ui.tooltip_content</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>This place was once an abandoned land, uninhabitable due to contamination, but as centuries of accumulated robot wreckage began to repair and modify itself, a bizarre mechanical ecosystem was born.</t>
         </is>
       </c>
     </row>
@@ -2052,7 +3684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2856,6 +4488,822 @@
       <c r="B67" t="inlineStr">
         <is>
           <t>TYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>shop_ui.header</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>ショップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>inventory_ui.header</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>インベントリ</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>upgrade_ui.header</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>強化</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>item_tooltip_ui.sub_option_label</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>追加オプション</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>item_tooltip_ui.unique_effect_label</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>固有効果</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>upgrade_ui.current_stat</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>現在ステータス：{0} + {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>upgrade_ui.next_stat</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>強化後ステータス：{0} + {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>upgrade_ui.cost</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>強化費用：{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>upgrade_ui.cost_unavailable</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>強化費用：-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>upgrade_ui.unknown_item</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>アイテム</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>upgrade_ui.selection_required</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>強化するアイテムを選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_success</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>{0} +{1} 強化成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_not_enough_gold</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ゴールドが不足しています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_invalid_item</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>強化できないアイテムです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_invalid_cost</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>強化費用の設定が正しくありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_wallet_unavailable</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>強化処理中に問題が発生しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_failed</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>強化に失敗しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>npc_ui.quest</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>依頼</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>npc_ui.rest</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>休憩</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_success</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>装備処理が完了しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_swapped</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>装備を交換しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_invalid_item</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>装備できないアイテムです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_invalid_slot</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>そのスロットには装備できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_slot_occupied</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>すでに装備が装着されています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_not_equipped</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>解除する装備がありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_no_return_space</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>既存の装備をインベントリに置くスペースがありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_failed</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>装備処理に失敗しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_wrong_class</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>このキャラクターは装備できない武器です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_unknown</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>不明な装備処理結果です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_acquisition</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>{0} アイテムを獲得しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_acquisition_colored</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>{0} を獲得しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_success_position</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>{0} 位置：{1}, {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_invalid_item</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>無効なアイテムです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_no_space</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>インベントリが満杯です！</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_grid_unavailable</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>インベントリを使用できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_placement_failed</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>インベントリにアイテムを配置できませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_add_failed</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>アイテムの獲得に失敗しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_success</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>{0} を削除しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_invalid_item</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>無効なアイテムです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_unavailable</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>インベントリを使用できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_not_player</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>自分のインベントリのアイテムのみ削除できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>装備中のアイテムは直接削除できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_failed</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>アイテムの削除に失敗しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_default_failed</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>アイテムを削除できませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_buy_success</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>{0} を購入しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_sell_success</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>{0} を売却しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_not_enough_gold</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>ゴールドが不足しているため {0} の購入に失敗しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_no_space_buy</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>インベントリに空きがありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_no_space_sell</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ショップに販売アイテムを置くスペースがありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_invalid_item</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>無効なアイテムです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_transfer_failed</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>{0} の移動中に取引に失敗しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_stock_update_failed</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>{0} の在庫処理に失敗しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_failed</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>取引処理に失敗しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>chat_ui.pickup_default</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>アイテムを獲得しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>chat_ui.out_of_range</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>アイテムにもっと近づいてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>chat_ui.already_claimed</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>すでに獲得済みのアイテムです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>chat_ui.pickup_unavailable</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>これ以上獲得できないアイテムです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>chat_ui.item_unavailable</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>対象のアイテムが見つかりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>chat_ui.stale_revision</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>アイテムの状態が変わりました。もう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>chat_ui.recovery_failed</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>アイテムのドロップとインベントリの復元に失敗しました。インベントリの状態を確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>chat_ui.upgrade_process_failed</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>強化を処理できませんでした。もう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>chat_ui.drop_failed</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>アイテムをフィールドに置けませんでした。もう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>chat_ui.acquisition_failed</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>アイテムを獲得できませんでした。もう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_state_changed</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ショップの状態が変わりました。もう一度選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_state_changed</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>インベントリの状態が変わりました。もう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>chat_ui.trade_failed</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>取引を処理できませんでした。もう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>loading_ui.tooltip_title</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>デブリス-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>loading_ui.tooltip_content</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>この場所は汚染によって人間が住めない廃墟の地でしたが、何百年もの間積み重なったロボットの残骸が自らを修復・改造し始め、奇怪なメカ生態系が生まれました。</t>
         </is>
       </c>
     </row>
@@ -2870,7 +5318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3677,6 +6125,822 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>shop_ui.header</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>商店</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>inventory_ui.header</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>物品栏</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>upgrade_ui.header</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>item_tooltip_ui.sub_option_label</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>附加选项</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>item_tooltip_ui.unique_effect_label</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>固有效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>upgrade_ui.current_stat</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>当前属性：{0} + {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>upgrade_ui.next_stat</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>强化后属性：{0} + {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>upgrade_ui.cost</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>强化费用：{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>upgrade_ui.cost_unavailable</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>强化费用：-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>upgrade_ui.unknown_item</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>物品</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>upgrade_ui.selection_required</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>请选择要强化的物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_success</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>{0} +{1} 强化成功</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_not_enough_gold</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>金币不足。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_invalid_item</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>该物品无法强化。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_invalid_cost</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>强化费用设置不正确。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_wallet_unavailable</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>强化处理过程中发生了问题。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>upgrade_ui.result_failed</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>强化失败。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>npc_ui.quest</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>委托</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>npc_ui.rest</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>休息</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_success</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>装备处理已完成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_swapped</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>已更换装备。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_invalid_item</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>该物品无法装备。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_invalid_slot</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>无法装备到该栏位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_slot_occupied</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>该位置已装备物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_not_equipped</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>没有可卸下的装备。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_no_return_space</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>背包中没有空间放置原有装备。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_failed</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>装备处理失败。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_wrong_class</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>该角色无法装备此武器。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>chat_ui.equip_unknown</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>未知的装备处理结果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_acquisition</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>获得了物品：{0}。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_acquisition_colored</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>获得了 {0}。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_success_position</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>{0} 位置：{1}, {2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_invalid_item</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>无效的物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_no_space</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>背包已满！</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_grid_unavailable</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>无法使用背包。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_placement_failed</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>未能将物品放入背包。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_add_failed</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>获取物品失败。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_success</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>已删除 {0}。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_invalid_item</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>无效的物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_unavailable</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>无法使用背包。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_not_player</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>只能删除自己背包中的物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>已装备的物品无法直接删除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_failed</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>删除物品失败。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_remove_default_failed</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>无法删除物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_buy_success</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>已购买 {0}。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_sell_success</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>已出售 {0}。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_not_enough_gold</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>金币不足，购买 {0} 失败。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_no_space_buy</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>背包中没有空间。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_no_space_sell</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>商店中没有空间放置出售的物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_invalid_item</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>无效的物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_transfer_failed</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>移动 {0} 时交易失败。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_stock_update_failed</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>{0} 库存处理失败。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_failed</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>交易处理失败。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>chat_ui.pickup_default</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>获得了物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>chat_ui.out_of_range</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>请靠近物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>chat_ui.already_claimed</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>该物品已被获取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>chat_ui.pickup_unavailable</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>该物品无法再获取。</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>chat_ui.item_unavailable</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>找不到目标物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>chat_ui.stale_revision</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>物品状态已更改，请重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>chat_ui.recovery_failed</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>物品掉落及背包恢复失败，请检查背包状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>chat_ui.upgrade_process_failed</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>强化处理失败，请重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>chat_ui.drop_failed</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>未能将物品放置到场地上，请重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>chat_ui.acquisition_failed</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>获取物品失败，请重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>chat_ui.shop_state_changed</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>商店状态已更改，请重新选择。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>chat_ui.inventory_state_changed</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>背包状态已更改，请重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>chat_ui.trade_failed</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>交易处理失败，请重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>loading_ui.tooltip_title</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>残骸-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>loading_ui.tooltip_content</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>这里原本是因污染而无法居住的废弃之地，但数百年间堆积的机器人残骸开始自我修复与改造，形成了诡异的机甲生态系统。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B135"/>
+  <dimension ref="A1:B144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2036,6 +2036,114 @@
       <c r="B135" t="inlineStr">
         <is>
           <t>이곳은 오염으로 인해 인간이 살 수 없는 버려진 땅이었지만, 수백 년간 쌓인 로봇 잔해들이 스스로를 복구하고 개조하기 시작하면서 기괴한 메카 생태계가 만들어졌습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>common_ui.yes</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>예</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>common_ui.confirm</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>chat_ui.panel_title</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>채팅</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>chat_ui.input_placeholder</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>메시지 입력…</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>chat_ui.connect_hint</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>접속 후 대화할 수 있습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>chat_ui.unread_indicator</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>새 메시지 ↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.title</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>스킬 진화·강화 설정</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.hint</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>K로 열기/닫기 - 왼쪽 버튼: 진화(없음→진화1→2→3), 오른쪽 버튼: 강화(없음→강화1→2→3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.none</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B135"/>
+  <dimension ref="A1:B144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3670,6 +3778,114 @@
       <c r="B135" t="inlineStr">
         <is>
           <t>This place was once an abandoned land, uninhabitable due to contamination, but as centuries of accumulated robot wreckage began to repair and modify itself, a bizarre mechanical ecosystem was born.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>common_ui.yes</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>common_ui.confirm</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>chat_ui.panel_title</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>chat_ui.input_placeholder</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Enter message…</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>chat_ui.connect_hint</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>You can chat after connecting</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>chat_ui.unread_indicator</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>New message ↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.title</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Skill Evolution &amp; Enhancement Settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.hint</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Press K to open/close - Left button: Evolution (None→Evo1→2→3), Right button: Enhancement (None→Enh1→2→3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.none</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B135"/>
+  <dimension ref="A1:B144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5304,6 +5520,114 @@
       <c r="B135" t="inlineStr">
         <is>
           <t>この場所は汚染によって人間が住めない廃墟の地でしたが、何百年もの間積み重なったロボットの残骸が自らを修復・改造し始め、奇怪なメカ生態系が生まれました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>common_ui.yes</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>common_ui.confirm</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>chat_ui.panel_title</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>チャット</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>chat_ui.input_placeholder</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>メッセージを入力…</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>chat_ui.connect_hint</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>接続後に会話できます</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>chat_ui.unread_indicator</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>新着メッセージ ↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.title</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>スキル進化・強化設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.hint</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Kで開閉 - 左ボタン：進化（なし→進化1→2→3）、右ボタン：強化（なし→強化1→2→3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.none</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>なし</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B135"/>
+  <dimension ref="A1:B144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6941,6 +7265,114 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>common_ui.yes</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>common_ui.confirm</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>chat_ui.panel_title</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>聊天</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>chat_ui.input_placeholder</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>输入消息…</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>chat_ui.connect_hint</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>连接后可以聊天</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>chat_ui.unread_indicator</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>新消息 ↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.title</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>技能进化·强化设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.hint</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>按K键开关 - 左键：进化（无→进化1→2→3），右键：强化（无→强化1→2→3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>skill_evolution_ui.none</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B144"/>
+  <dimension ref="A1:B154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2144,6 +2144,126 @@
       <c r="B144" t="inlineStr">
         <is>
           <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.title</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>패시브 업그레이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.skill_clear</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>초기화</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.skill_points</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>스킬 포인트 -</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.credit_format</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>크레딧 | {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.credit_none</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>크레딧 | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.profile_loading</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>프로필 준비 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.confirm_ok</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_current_level</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>현재 레벨: {0} / {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_current_effect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>현재 효과: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_next_level</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>다음 레벨: {0}</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B144"/>
+  <dimension ref="A1:B154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3886,6 +4006,126 @@
       <c r="B144" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.title</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Passive Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.skill_clear</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Reset</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.skill_points</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Skill Points -</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.credit_format</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Credit | {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.credit_none</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Credit | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.profile_loading</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Loading Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.confirm_ok</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_current_level</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Current Lv: {0} / {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_current_effect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Current Effect: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_next_level</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Next Lv: {0}</t>
         </is>
       </c>
     </row>
@@ -3900,7 +4140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B144"/>
+  <dimension ref="A1:B154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5628,6 +5868,126 @@
       <c r="B144" t="inlineStr">
         <is>
           <t>なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.title</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>パッシブアップグレード</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.skill_clear</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>リセット</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.skill_points</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>スキルポイント -</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.credit_format</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>クレジット | {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.credit_none</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>クレジット | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.profile_loading</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>プロフィール準備中</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.confirm_ok</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_current_level</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>現在レベル: {0} / {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_current_effect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>現在効果: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_next_level</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>次レベル: {0}</t>
         </is>
       </c>
     </row>
@@ -5642,7 +6002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B144"/>
+  <dimension ref="A1:B154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7373,6 +7733,126 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.title</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>被动升级</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.skill_clear</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>重置</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.skill_points</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>技能点 -</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.credit_format</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>点数 | {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.credit_none</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>点数 | -</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.profile_loading</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>配置准备中</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.confirm_ok</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>确定</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_current_level</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>当前等级: {0} / {1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_current_effect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>当前效果: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>passive_skill_ui.detail_next_level</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>下一级: {0}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>골드가 부족합니다.</t>
+          <t>크레딧이 부족합니다.</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>골드가 부족해 {0} 구매에 실패했습니다.</t>
+          <t>크레딧이 부족해 {0} 구매에 실패했습니다.</t>
         </is>
       </c>
     </row>
@@ -2264,6 +2264,91 @@
       <c r="B154" t="inlineStr">
         <is>
           <t>다음 레벨: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>common_ui.cancel</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>취소</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>rest_ui.header</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>휴식</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>rest_ui.description</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>크레딧을 지불하여
+휴식을 취하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>rest_ui.health_recovery</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>체력 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>rest_ui.potion_recharge</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>포션 충전</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>rest_ui.cost_format</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>필요 크레딧 : {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>rest_ui.complete_message</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>{0} 크레딧을 소비하여 체력 {1}, 포션 {2}개를 채웠습니다.</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3237,7 +3322,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Not enough gold.</t>
+          <t>Not enough credits.</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3730,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Not enough gold to purchase {0}.</t>
+          <t>Not enough credits to purchase {0}.</t>
         </is>
       </c>
     </row>
@@ -4126,6 +4211,91 @@
       <c r="B154" t="inlineStr">
         <is>
           <t>Next Lv: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>common_ui.cancel</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Cancel</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>rest_ui.header</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>rest_ui.description</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Spend credits to
+take a rest?</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>rest_ui.health_recovery</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Health Restored</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>rest_ui.potion_recharge</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Potion Charges</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>rest_ui.cost_format</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Required Credits : {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>rest_ui.complete_message</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Spent {0} credits to restore {1} HP and {2} potion charge(s).</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5099,7 +5269,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ゴールドが不足しています。</t>
+          <t>クレジットが不足しています。</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5677,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ゴールドが不足しているため {0} の購入に失敗しました。</t>
+          <t>クレジットが不足しているため {0} の購入に失敗しました。</t>
         </is>
       </c>
     </row>
@@ -5988,6 +6158,91 @@
       <c r="B154" t="inlineStr">
         <is>
           <t>次レベル: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>common_ui.cancel</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>rest_ui.header</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>休息</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>rest_ui.description</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>クレジットを支払って
+休息しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>rest_ui.health_recovery</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>体力回復</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>rest_ui.potion_recharge</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ポーション補充</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>rest_ui.cost_format</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>必要クレジット : {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>rest_ui.complete_message</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>{0}クレジットを消費して体力{1}、ポーション{2}個を補充しました。</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6961,7 +7216,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>金币不足。</t>
+          <t>信用点不足。</t>
         </is>
       </c>
     </row>
@@ -7369,7 +7624,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>金币不足，购买 {0} 失败。</t>
+          <t>信用点不足，购买 {0} 失败。</t>
         </is>
       </c>
     </row>
@@ -7850,6 +8105,91 @@
       <c r="B154" t="inlineStr">
         <is>
           <t>下一级: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>common_ui.cancel</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>取消</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>rest_ui.header</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>休息</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>rest_ui.description</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>支付信用点
+进行休息吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>rest_ui.health_recovery</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>生命恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>rest_ui.potion_recharge</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>药水补充</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>rest_ui.cost_format</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>所需信用点 : {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>rest_ui.complete_message</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>消耗{0}信用点，恢复了{1}点生命和{2}个药水。</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B161"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2349,6 +2349,66 @@
       <c r="B161" t="inlineStr">
         <is>
           <t>{0} 크레딧을 소비하여 체력 {1}, 포션 {2}개를 채웠습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_chat</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[채팅] </t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_acquisition</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[획득] </t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_warning</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[안내] </t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_connection</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[연결] </t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>chat_ui.item_fallback_name</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>아이템</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B161"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4296,6 +4356,66 @@
       <c r="B161" t="inlineStr">
         <is>
           <t>Spent {0} credits to restore {1} HP and {2} potion charge(s).</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_chat</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Chat] </t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_acquisition</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Item] </t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_warning</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Notice] </t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_connection</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Network] </t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>chat_ui.item_fallback_name</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>item</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B161"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6243,6 +6363,66 @@
       <c r="B161" t="inlineStr">
         <is>
           <t>{0}クレジットを消費して体力{1}、ポーション{2}個を補充しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_chat</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[チャット] </t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_acquisition</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[獲得] </t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_warning</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[お知らせ] </t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_connection</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[接続] </t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>chat_ui.item_fallback_name</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>アイテム</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B161"/>
+  <dimension ref="A1:B166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8193,6 +8373,66 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_chat</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[聊天] </t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_acquisition</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[获得] </t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_warning</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[提示] </t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>chat_ui.prefix_connection</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[连接] </t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>chat_ui.item_fallback_name</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>物品</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -5593,7 +5593,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{0} アイテムを獲得しました。</t>
+          <t>{0}アイテムを獲得しました。</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{0} を獲得しました。</t>
+          <t>{0}を獲得しました。</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{0} を削除しました。</t>
+          <t>{0}を削除しました。</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{0} を購入しました。</t>
+          <t>{0}を購入しました。</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{0} を売却しました。</t>
+          <t>{0}を売却しました。</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>クレジットが不足しているため {0} の購入に失敗しました。</t>
+          <t>クレジットが不足しているため{0}の購入に失敗しました。</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>{0} の移動中に取引に失敗しました。</t>
+          <t>{0}の移動中に取引に失敗しました。</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{0} の在庫処理に失敗しました。</t>
+          <t>{0}の在庫処理に失敗しました。</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">[獲得] </t>
+          <t xml:space="preserve">[アイテム] </t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>获得了 {0}。</t>
+          <t>获得了{0}。</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>已删除 {0}。</t>
+          <t>已删除{0}。</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>已购买 {0}。</t>
+          <t>已购买{0}。</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>已出售 {0}。</t>
+          <t>已出售{0}。</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>信用点不足，购买 {0} 失败。</t>
+          <t>信用点不足，购买{0}失败。</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>移动 {0} 时交易失败。</t>
+          <t>移动{0}时交易失败。</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{0} 库存处理失败。</t>
+          <t>{0}库存处理失败。</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">[获得] </t>
+          <t xml:space="preserve">[物品] </t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B166"/>
+  <dimension ref="A1:B169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2409,6 +2409,42 @@
       <c r="B166" t="inlineStr">
         <is>
           <t>아이템</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_cost_format</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 리롤</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_free</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>무료 리롤</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_count_format</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B166"/>
+  <dimension ref="A1:B169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4416,6 +4452,42 @@
       <c r="B166" t="inlineStr">
         <is>
           <t>item</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_cost_format</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Reroll &lt;color=#FFEB04&gt;{0}&lt;/color&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_free</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Free Reroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_count_format</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B166"/>
+  <dimension ref="A1:B169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6423,6 +6495,42 @@
       <c r="B166" t="inlineStr">
         <is>
           <t>アイテム</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_cost_format</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 再抽選</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_free</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>無料 再抽選</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_count_format</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
@@ -6437,7 +6545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B166"/>
+  <dimension ref="A1:B169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8433,6 +8541,42 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_cost_format</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 刷新</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_free</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>免费刷新</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>shop_ui.reroll_count_format</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>[ {0} ]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>세부 스텟 보기</t>
+          <t>세부 스탯 보기</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B169"/>
+  <dimension ref="A1:B171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2445,6 +2445,30 @@
       <c r="B169" t="inlineStr">
         <is>
           <t>[ {0} ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>settings_ui.reset_confirm</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>설정을 기본값으로 초기화하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>settings_ui.reset_warning</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>현재 설정이 모두 기본값으로 변경됩니다.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B169"/>
+  <dimension ref="A1:B171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4488,6 +4512,30 @@
       <c r="B169" t="inlineStr">
         <is>
           <t>[ {0} ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>settings_ui.reset_confirm</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Reset all settings to their defaults?</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>settings_ui.reset_warning</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>All current settings will be restored to their defaults.</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B169"/>
+  <dimension ref="A1:B171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6531,6 +6579,30 @@
       <c r="B169" t="inlineStr">
         <is>
           <t>[ {0} ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>settings_ui.reset_confirm</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>設定を初期値に戻しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>settings_ui.reset_warning</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>現在の設定はすべて初期値に戻ります。</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B169"/>
+  <dimension ref="A1:B171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8577,6 +8649,30 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>settings_ui.reset_confirm</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>要将设置恢复为默认值吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>settings_ui.reset_warning</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>当前所有设置都将恢复为默认值。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2637,6 +2637,871 @@
       <c r="B185" t="inlineStr">
         <is>
           <t>보유 크레딧과 아이템 원가의 50%를 계정 크레딧으로 받고, 현재 원정은 초기화됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>login_ui.title</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>사용자 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>login_ui.subtitle</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>사용자 인증 터미널</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>login_ui.account</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>계정 ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>login_ui.email_placeholder</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>이메일</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>login_ui.password</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>비밀번호</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>login_ui.confirm_password</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>비밀번호 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>login_ui.submit</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>접속</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>login_ui.no_account</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>계정이 없는 상태인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>login_ui.create_account</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>계정 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>login_ui.create</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>login_ui.has_account</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>계정이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>login_ui.login</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>login_ui.footer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>보안 접속 터미널</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>login_ui.submitting</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>로그인 중...</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>login_ui.creating</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>계정 생성 중...</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>login_ui.required</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>이메일과 비밀번호를 입력해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>login_ui.account_required</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>계정 ID와 비밀번호를 입력하십시오.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>login_ui.confirm_required</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>비밀번호 확인을 입력하십시오.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>login_ui.password_mismatch</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>비밀번호가 일치하지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>login_ui.login_error</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>로그인 처리 중 오류가 발생했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>login_ui.profile_incomplete</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>계정은 생성되었지만 기본 프로필을 준비하지 못했습니다. 로그인 화면에서 다시 로그인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>login_ui.created</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>계정 생성이 완료되었습니다. 로그인 화면에서 새 계정으로 로그인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>login_ui.create_error</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>계정 생성 처리 중 오류가 발생했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>login_ui.loader_missing</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>씬 로더가 준비되지 않았습니다. Start 씬부터 실행해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>login_ui.scenes_missing</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>TitleScene과 LoadingScene의 빌드 등록을 확인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>login_ui.user_missing</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>로그인 결과에서 사용자 정보를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>login_ui.auth_failed</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>로그인에 실패했습니다.
+이메일, 비밀번호와 Firebase 인증 설정을 확인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>login_ui.firebase_login_error</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Firebase 로그인 중 오류가 발생했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>login_ui.created_user_missing</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>계정 생성 결과에서 사용자 정보를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>login_ui.firebase_create_error</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Firebase 계정 생성 중 오류가 발생했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>login_ui.email_in_use</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>이미 사용 중인 이메일입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>login_ui.invalid_email</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>올바른 이메일 주소를 입력해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>login_ui.password_policy</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Firebase 비밀번호 정책을 만족하는 비밀번호를 입력해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>login_ui.auth_disabled</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Firebase Console에서 이메일/비밀번호 로그인을 활성화해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>login_ui.network_error</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>네트워크 연결을 확인한 뒤 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>login_ui.too_many_requests</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>요청이 너무 많습니다. 잠시 후 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>login_ui.create_failed</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>계정을 생성하지 못했습니다. 입력값과 Firebase 인증 설정을 확인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>login_ui.config_missing</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Firebase 설정 파일이 없습니다. google-services.json 또는 GoogleService-Info.plist를 Assets 폴더에 추가해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>login_ui.dependencies</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Firebase 의존성을 준비하지 못했습니다: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>login_ui.init_failed</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Firebase 초기화에 실패했습니다. 설정 파일과 프로젝트 연결 상태를 확인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>connection_ui.title</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>멀티플레이 접속</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>connection_ui.subtitle</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>멀티플레이 접속 터미널</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>connection_ui.address</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>서버 주소</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>connection_ui.address_placeholder</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>서버 IP 또는 호스트명</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>connection_ui.nickname</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>닉네임</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>connection_ui.host</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>로컬 테스트 · Host</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>connection_ui.join</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>서버 접속</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>connection_ui.server</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>로컬 테스트 · 서버</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>최근 세션으로 복귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>connection_ui.return_title</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>타이틀로 돌아가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>connection_ui.settings_missing</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>세션 연결 설정을 찾을 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>connection_ui.invalid_nickname</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>닉네임을 1~24자로 입력해 주세요. 태그와 줄바꿈은 사용할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>connection_ui.invalid_address</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>서버 IP 또는 호스트명을 입력해 주세요. 포트 번호는 붙이지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>connection_ui.connecting</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>연결 중…</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>connection_ui.server_running</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>전용 서버 실행 중 · 참가자 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>connection_ui.no_session</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>이 프로필에 저장된 최근 세션이 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_large</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>재접속 프로필 자료가 너무 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_invalid</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>재접속 프로필 자료가 올바르지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_read</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>재접속 프로필을 읽을 수 없습니다. 파일 형식 또는 저장소 접근 권한을 확인하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_path</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>재접속 프로필 저장 위치를 사용할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>connection_ui.run_started</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>이미 출발한 세션에는 새로 참가할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>connection_ui.connection_invalid</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>이미 등록되었거나 유효하지 않은 연결입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>connection_ui.full</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>세션 정원이 찼습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect_denied</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>재접속 자격을 확인할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect_expired</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>재접속 예약이 없거나 만료되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>connection_ui.version_mismatch</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>서버와 클라이언트의 빌드 버전이 다릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>connection_ui.passive_profile</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>저장된 패시브 프로필을 읽지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>connection_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>서버 참가 승인 시간이 초과되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>connection_ui.admitted</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>참가 승인 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>connection_ui.before_connect</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>서버 연결 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>connection_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>서버 연결 대기 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>connection_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>서버와 연결이 끊어졌습니다.</t>
         </is>
       </c>
     </row>
@@ -2651,7 +3516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4872,6 +5737,871 @@
       <c r="B185" t="inlineStr">
         <is>
           <t>You will receive your credits plus 50% of your items' base value as account credits, and the current run will be reset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>login_ui.title</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>User Authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>login_ui.subtitle</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>OPERATOR AUTHENTICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>login_ui.account</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Account ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>login_ui.email_placeholder</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>login_ui.password</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>login_ui.confirm_password</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Confirm Password</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>login_ui.submit</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Log In</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>login_ui.no_account</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Don't have an account?</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>login_ui.create_account</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Create Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>login_ui.create</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Create</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>login_ui.has_account</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Already have an account?</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>login_ui.login</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Log In</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>login_ui.footer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SECURE ACCESS TERMINAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>login_ui.submitting</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Logging in...</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>login_ui.creating</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Creating account...</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>login_ui.required</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Enter your email and password.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>login_ui.account_required</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Enter your account ID and password.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>login_ui.confirm_required</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Confirm your password.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>login_ui.password_mismatch</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Passwords do not match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>login_ui.login_error</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>An error occurred while logging in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>login_ui.profile_incomplete</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Account created, but profile setup failed. Please log in again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>login_ui.created</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Account created. Log in with your new account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>login_ui.create_error</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>An error occurred while creating your account.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>login_ui.loader_missing</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Scene loader is unavailable. Launch from the Start scene.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>login_ui.scenes_missing</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Check that TitleScene and LoadingScene are included in the build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>login_ui.user_missing</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>User information was missing from the login response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>login_ui.auth_failed</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Login failed.
+Check your email, password and Firebase authentication settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>login_ui.firebase_login_error</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>A Firebase login error occurred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>login_ui.created_user_missing</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>User information was missing from the account creation response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>login_ui.firebase_create_error</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>A Firebase account creation error occurred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>login_ui.email_in_use</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>This email is already in use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>login_ui.invalid_email</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Enter a valid email address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>login_ui.password_policy</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Choose a password that meets the password policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>login_ui.auth_disabled</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Enable email/password sign-in in Firebase Console.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>login_ui.network_error</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Check your network connection and try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>login_ui.too_many_requests</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Too many requests. Please try again later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>login_ui.create_failed</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Account creation failed. Check your input and Firebase authentication settings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>login_ui.config_missing</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Firebase configuration is missing. Add google-services.json or GoogleService-Info.plist to Assets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>login_ui.dependencies</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Could not initialize Firebase dependencies: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>login_ui.init_failed</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Firebase initialization failed. Check configuration and project connection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>connection_ui.title</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Multiplayer Connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>connection_ui.subtitle</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>MULTIPLAYER CONNECTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>connection_ui.address</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Server Address</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>connection_ui.address_placeholder</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Server IP or hostname</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>connection_ui.nickname</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Nickname</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>connection_ui.host</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Local Test · Host</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>connection_ui.join</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Connect to Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>connection_ui.server</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Local Test · Server</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Rejoin Last Session</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>connection_ui.return_title</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Return to Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>connection_ui.settings_missing</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Session connection settings are unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>connection_ui.invalid_nickname</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Enter a nickname of 1–24 characters without tags or line breaks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>connection_ui.invalid_address</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Enter a server IP or hostname without a port number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>connection_ui.connecting</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Connecting…</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>connection_ui.server_running</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Dedicated server running · Waiting for players</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>connection_ui.no_session</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>No recent session is saved for this profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_large</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>The reconnect profile is too large.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_invalid</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>The reconnect profile is invalid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_read</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Cannot read the reconnect profile. Check its format and storage permissions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_path</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>The reconnect profile storage location is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>connection_ui.run_started</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>You cannot join a session that has already started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>connection_ui.connection_invalid</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>This connection is already registered or invalid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>connection_ui.full</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>The session is full.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect_denied</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Reconnect eligibility could not be verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect_expired</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>The reconnect reservation is missing or expired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>connection_ui.version_mismatch</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Server and client build versions do not match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>connection_ui.passive_profile</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Could not load the saved passive skill profile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>connection_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Server admission timed out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>connection_ui.admitted</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Admission approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>connection_ui.before_connect</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Not connected</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>connection_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Waiting for server connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>connection_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Disconnected from the server.</t>
         </is>
       </c>
     </row>
@@ -4886,7 +6616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7107,6 +8837,871 @@
       <c r="B185" t="inlineStr">
         <is>
           <t>所持クレジットとアイテム原価の50%をアカウントクレジットとして受け取り、現在の遠征はリセットされます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>login_ui.title</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>ユーザー認証</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>login_ui.subtitle</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ユーザー認証端末</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>login_ui.account</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>アカウントID</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>login_ui.email_placeholder</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>メールアドレス</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>login_ui.password</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>パスワード</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>login_ui.confirm_password</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>パスワード確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>login_ui.submit</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>ログイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>login_ui.no_account</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>アカウントをお持ちでない方</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>login_ui.create_account</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>アカウント作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>login_ui.create</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>作成</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>login_ui.has_account</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>アカウントをお持ちの方</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>login_ui.login</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>ログイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>login_ui.footer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>セキュアアクセス端末</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>login_ui.submitting</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>ログイン中…</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>login_ui.creating</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>アカウント作成中…</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>login_ui.required</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>メールアドレスとパスワードを入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>login_ui.account_required</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>アカウントIDとパスワードを入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>login_ui.confirm_required</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>確認用パスワードを入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>login_ui.password_mismatch</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>パスワードが一致しません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>login_ui.login_error</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ログイン処理中にエラーが発生しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>login_ui.profile_incomplete</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>アカウントは作成されましたが、プロフィールの準備に失敗しました。再度ログインしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>login_ui.created</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>アカウントを作成しました。新しいアカウントでログインしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>login_ui.create_error</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>アカウント作成中にエラーが発生しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>login_ui.loader_missing</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>シーンローダーが未準備です。Startシーンから実行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>login_ui.scenes_missing</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>TitleSceneとLoadingSceneのビルド登録を確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>login_ui.user_missing</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ログイン結果からユーザー情報を取得できませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>login_ui.auth_failed</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ログインに失敗しました。
+メールアドレス、パスワード、Firebase認証設定を確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>login_ui.firebase_login_error</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Firebaseログイン中にエラーが発生しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>login_ui.created_user_missing</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>アカウント作成結果からユーザー情報を取得できませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>login_ui.firebase_create_error</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Firebaseアカウント作成中にエラーが発生しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>login_ui.email_in_use</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>このメールアドレスは既に使用されています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>login_ui.invalid_email</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>有効なメールアドレスを入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>login_ui.password_policy</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>パスワードの要件を満たすパスワードを入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>login_ui.auth_disabled</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Firebase Consoleでメールとパスワードによるログインを有効にしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>login_ui.network_error</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ネットワーク接続を確認して再試行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>login_ui.too_many_requests</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>リクエストが多すぎます。しばらくしてから再試行してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>login_ui.create_failed</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>アカウントを作成できませんでした。入力内容とFirebase認証設定を確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>login_ui.config_missing</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Firebase設定ファイルがありません。google-services.jsonまたはGoogleService-Info.plistをAssetsに追加してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>login_ui.dependencies</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Firebaseの依存関係を準備できませんでした：{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>login_ui.init_failed</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Firebaseの初期化に失敗しました。設定ファイルとプロジェクト接続を確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>connection_ui.title</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>マルチプレイ接続</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>connection_ui.subtitle</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>マルチプレイ接続端末</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>connection_ui.address</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>サーバーアドレス</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>connection_ui.address_placeholder</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>サーバーIPまたはホスト名</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>connection_ui.nickname</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ニックネーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>connection_ui.host</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ローカルテスト · ホスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>connection_ui.join</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>サーバーに接続</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>connection_ui.server</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ローカルテスト · サーバー</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>前回のセッションに復帰</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>connection_ui.return_title</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>タイトルに戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>connection_ui.settings_missing</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>セッション接続設定が見つかりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>connection_ui.invalid_nickname</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>ニックネームは1～24文字で入力してください。タグと改行は使えません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>connection_ui.invalid_address</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ポート番号を付けずにサーバーIPまたはホスト名を入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>connection_ui.connecting</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>接続中…</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>connection_ui.server_running</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>専用サーバー稼働中 · 参加者待機</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>connection_ui.no_session</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>このプロフィールに保存されたセッションはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_large</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>再接続プロフィールのデータが大きすぎます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_invalid</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>再接続プロフィールのデータが無効です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_read</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>再接続プロフィールを読み込めません。形式とストレージ権限を確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_path</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>再接続プロフィールの保存先を使用できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>connection_ui.run_started</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>開始済みのセッションには新規参加できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>connection_ui.connection_invalid</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>登録済み、または無効な接続です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>connection_ui.full</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>セッションが満員です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect_denied</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>再接続の資格を確認できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect_expired</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>再接続予約が存在しないか、有効期限が切れています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>connection_ui.version_mismatch</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>サーバーとクライアントのビルドバージョンが一致しません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>connection_ui.passive_profile</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>保存されたパッシブプロフィールを読み込めませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>connection_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>サーバーの参加承認がタイムアウトしました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>connection_ui.admitted</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>参加が承認されました</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>connection_ui.before_connect</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>未接続</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>connection_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>サーバー接続待機中</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>connection_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>サーバーとの接続が切れました。</t>
         </is>
       </c>
     </row>
@@ -7121,7 +9716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9345,6 +11940,871 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>login_ui.title</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>用户认证</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>login_ui.subtitle</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>用户认证终端</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>login_ui.account</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>login_ui.email_placeholder</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>电子邮箱</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>login_ui.password</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>密码</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>login_ui.confirm_password</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>确认密码</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>login_ui.submit</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>login_ui.no_account</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>还没有账号？</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>login_ui.create_account</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>创建账号</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>login_ui.create</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>创建</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>login_ui.has_account</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>已有账号？</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>login_ui.login</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>登录</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>login_ui.footer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>安全访问终端</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>login_ui.submitting</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>正在登录…</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>login_ui.creating</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>正在创建账号…</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>login_ui.required</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>请输入邮箱和密码。</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>login_ui.account_required</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>请输入账号和密码。</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>login_ui.confirm_required</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>请再次输入密码。</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>login_ui.password_mismatch</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>两次输入的密码不一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>login_ui.login_error</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>登录时发生错误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>login_ui.profile_incomplete</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>账号已创建，但资料初始化失败。请重新登录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>login_ui.created</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>账号创建成功。请使用新账号登录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>login_ui.create_error</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>创建账号时发生错误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>login_ui.loader_missing</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>场景加载器尚未就绪。请从Start场景运行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>login_ui.scenes_missing</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>请确认TitleScene和LoadingScene已加入构建。</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>login_ui.user_missing</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>登录结果中未找到用户信息。</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>login_ui.auth_failed</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>登录失败。
+请检查邮箱、密码及Firebase认证设置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>login_ui.firebase_login_error</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Firebase登录时发生错误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>login_ui.created_user_missing</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>账号创建结果中未找到用户信息。</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>login_ui.firebase_create_error</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>创建Firebase账号时发生错误。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>login_ui.email_in_use</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>此邮箱已被使用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>login_ui.invalid_email</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>请输入有效的邮箱地址。</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>login_ui.password_policy</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>请输入符合密码要求的密码。</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>login_ui.auth_disabled</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>请在Firebase Console启用邮箱和密码登录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>login_ui.network_error</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>请检查网络连接后重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>login_ui.too_many_requests</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>请求过于频繁，请稍后重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>login_ui.create_failed</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>无法创建账号。请检查输入内容及Firebase认证设置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>login_ui.config_missing</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>缺少Firebase配置文件。请将google-services.json或GoogleService-Info.plist添加到Assets。</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>login_ui.dependencies</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>无法初始化Firebase依赖项：{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>login_ui.init_failed</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Firebase初始化失败。请检查配置文件及项目连接。</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>connection_ui.title</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>多人游戏连接</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>connection_ui.subtitle</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>多人游戏连接终端</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>connection_ui.address</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>服务器地址</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>connection_ui.address_placeholder</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>服务器IP或主机名</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>connection_ui.nickname</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>昵称</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>connection_ui.host</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>本地测试 · 主机</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>connection_ui.join</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>连接服务器</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>connection_ui.server</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>本地测试 · 服务器</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>返回上次会话</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>connection_ui.return_title</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>返回标题界面</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>connection_ui.settings_missing</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>未找到会话连接设置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>connection_ui.invalid_nickname</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>请输入1至24个字符的昵称，不可使用标签或换行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>connection_ui.invalid_address</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>请输入服务器IP或主机名，不要附加端口号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>connection_ui.connecting</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>正在连接…</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>connection_ui.server_running</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>专用服务器运行中 · 等待玩家</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>connection_ui.no_session</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>此资料中没有保存的最近会话。</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_large</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>重连资料数据过大。</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_invalid</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>重连资料数据无效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_read</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>无法读取重连资料。请检查文件格式及存储权限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>connection_ui.profile_path</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>无法使用重连资料的存储位置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>connection_ui.run_started</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>无法加入已开始的会话。</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>connection_ui.connection_invalid</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>连接已注册或无效。</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>connection_ui.full</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>会话人数已满。</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect_denied</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>无法确认重连资格。</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>connection_ui.reconnect_expired</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>重连预约不存在或已过期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>connection_ui.version_mismatch</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>服务器与客户端的构建版本不一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>connection_ui.passive_profile</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>无法读取已保存的被动技能资料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>connection_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>等待服务器批准加入超时。</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>connection_ui.admitted</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>已批准加入</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>connection_ui.before_connect</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>尚未连接</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>connection_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>等待连接服务器</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>connection_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>与服务器的连接已断开。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3502,6 +3502,510 @@
       <c r="B257" t="inlineStr">
         <is>
           <t>서버와 연결이 끊어졌습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>upgrade_ui.request_failed</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>서버 강화 요청을 시작하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>upgrade_ui.request_pending</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>서버가 강화 가능 여부와 골드를 확인하고 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>upgrade_ui.state_changed</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>아이템 상태가 먼저 바뀌어 강화를 취소했습니다. 다시 선택해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>upgrade_ui.item_missing</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>인벤토리에서 해당 아이템을 찾지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>result_ui.stage</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>최종 도달 스테이지</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>result_ui.defeated</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>처치한 적</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>result_ui.play_time</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>플레이 시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>result_ui.credits</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>획득 크레딧</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>result_ui.retry</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>다시 시작</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>result_ui.return_lobby</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>로비로 돌아가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>result_ui.leave_session</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>세션 나가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>result_ui.clear_description</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>모든 스테이지를 클리어했습니다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>result_ui.defeat_description</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>이번 원정이 종료되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>result_ui.data_waiting</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>서버에서 결과를 받는 중입니다…</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>result_ui.data_missing</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>결과를 아직 받지 못했습니다. 계속 기다리거나 나갈 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>result_ui.request_pending</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>서버 응답을 기다리고 있습니다…</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>session_ui.end_host</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>호스트 세션 종료</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>session_ui.leave</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>세션 떠나기</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>session_ui.leave_temporarily</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>잠시 나가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_end_host</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>호스트 세션을 종료하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>session_ui.warn_end_host</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>모든 참가자의 연결과 현재 런이 종료됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_leave</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>이 세션에서 떠나시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>session_ui.warn_leave</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_temporary_leave</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>잠시 세션에서 나가시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>session_ui.warn_temporary_leave</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>session_ui.passive_locked</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>준비를 취소한 뒤 패시브를 변경할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait_host</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>참가자의 결과 저장을 기다리고 있습니다. 저장 후 세션을 종료해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait_player</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>{0}의 결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>session_ui.lobby_loading</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>로비 이동이 끝난 뒤 출발할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>session_ui.player_prefabs_missing</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>두 클래스의 네트워크 프리팹 연결을 확인하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>session_ui.session_missing</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>참여 중인 세션을 찾을 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>session_ui.unsupported_request</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>지원하지 않는 로비 요청입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>session_ui.return_lobby_denied</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>서버가 결과를 확정한 뒤 방장만 파티를 로비로 이동할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>session_ui.passive_invalid</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>패시브 프로필을 확인할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>session_ui.party_not_ready</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>모든 참가자가 캐릭터 선택과 준비를 완료해야 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>preparation_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>플레이를 준비하고 있습니다…</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>플레이 준비 시간이 초과되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout_retry</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>플레이 준비 시간이 초과되었습니다. 연결을 종료하고 다시 시도하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>preparation_ui.combat_failed</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>전투 웨이브 또는 생성 지점 준비에 실패했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>연결이 종료되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>preparation_ui.exit</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>나가기</t>
         </is>
       </c>
     </row>
@@ -3516,7 +4020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6602,6 +7106,510 @@
       <c r="B257" t="inlineStr">
         <is>
           <t>Disconnected from the server.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>upgrade_ui.request_failed</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Could not send the upgrade request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>upgrade_ui.request_pending</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Checking the item and available gold…</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>upgrade_ui.state_changed</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>The item changed. Select it again to upgrade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>upgrade_ui.item_missing</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>The item is no longer in your inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>result_ui.stage</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Stage Reached</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>result_ui.defeated</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Enemies Defeated</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>result_ui.play_time</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Play Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>result_ui.credits</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Credits Earned</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>result_ui.retry</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Play Again</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>result_ui.return_lobby</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Return to Lobby</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>result_ui.leave_session</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Leave Session</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>result_ui.clear_description</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>All stages cleared!</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>result_ui.defeat_description</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>This expedition has ended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>result_ui.data_waiting</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Receiving results from the server…</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>result_ui.data_missing</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Results have not arrived yet. You can wait or leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>result_ui.request_pending</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Waiting for the server…</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>session_ui.end_host</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>End Host Session</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>session_ui.leave</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Leave Session</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>session_ui.leave_temporarily</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Disconnect Temporarily</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_end_host</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>End this host session?</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>session_ui.warn_end_host</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>All players will disconnect and the current run will end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_leave</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Leave this session?</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>session_ui.warn_leave</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>You will forfeit your place and cannot rejoin this run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_temporary_leave</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Disconnect from this session temporarily?</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>session_ui.warn_temporary_leave</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>You can reconnect within 5 minutes while the server stays online. The party will keep playing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>session_ui.passive_locked</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Cancel Ready before changing passives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Results are still being saved. Please try again shortly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait_host</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Waiting for player results to save. End the session after saving finishes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait_player</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Waiting for {0}'s results to save. Please try again shortly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>session_ui.lobby_loading</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Wait for the lobby to finish loading before starting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>session_ui.player_prefabs_missing</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Player setup is incomplete. Please reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>session_ui.session_missing</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>The current session could not be found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>session_ui.unsupported_request</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>This lobby action is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>session_ui.return_lobby_denied</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Only the leader can return the party to the lobby after results are confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>session_ui.passive_invalid</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Your passive profile could not be verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>session_ui.party_not_ready</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>All players must choose a character and be ready.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>preparation_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Preparing the game…</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Game preparation timed out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout_retry</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Game preparation timed out. Disconnect and try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>preparation_ui.combat_failed</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>The battle could not be prepared. Please reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>The connection has ended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>preparation_ui.exit</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Leave</t>
         </is>
       </c>
     </row>
@@ -6616,7 +7624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9702,6 +10710,510 @@
       <c r="B257" t="inlineStr">
         <is>
           <t>サーバーとの接続が切れました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>upgrade_ui.request_failed</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>強化リクエストを送信できませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>upgrade_ui.request_pending</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>アイテムと所持ゴールドを確認しています…</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>upgrade_ui.state_changed</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>アイテムの状態が変わりました。もう一度選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>upgrade_ui.item_missing</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>インベントリに対象のアイテムがありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>result_ui.stage</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>最終到達ステージ</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>result_ui.defeated</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>倒した敵</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>result_ui.play_time</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>プレイ時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>result_ui.credits</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>獲得クレジット</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>result_ui.retry</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>もう一度プレイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>result_ui.return_lobby</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>ロビーに戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>result_ui.leave_session</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>セッションを退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>result_ui.clear_description</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>全ステージをクリアしました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>result_ui.defeat_description</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>今回の遠征は終了しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>result_ui.data_waiting</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>サーバーから結果を受信しています…</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>result_ui.data_missing</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>結果がまだ届いていません。待機するか退出できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>result_ui.request_pending</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>サーバーの応答を待っています…</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>session_ui.end_host</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ホストセッションを終了</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>session_ui.leave</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>セッションを退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>session_ui.leave_temporarily</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>一時的に退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_end_host</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>ホストセッションを終了しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>session_ui.warn_end_host</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>全員の接続と現在のプレイが終了します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_leave</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>このセッションを退出しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>session_ui.warn_leave</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>参加権を放棄するため、このプレイには再接続できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_temporary_leave</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>セッションから一時的に退出しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>session_ui.warn_temporary_leave</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>サーバーが稼働中なら5分以内に再接続できます。パーティーのゲームは続行されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>session_ui.passive_locked</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>準備を解除するとパッシブを変更できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>結果を保存しています。少し待ってからお試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait_host</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>参加者の結果を保存しています。保存完了後にセッションを終了してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait_player</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>{0}の結果を保存しています。少し待ってからお試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>session_ui.lobby_loading</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>ロビーの読み込みが終わってから出発してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>session_ui.player_prefabs_missing</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>プレイヤーの準備が不完全です。再接続してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>session_ui.session_missing</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>参加中のセッションが見つかりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>session_ui.unsupported_request</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>このロビー操作は利用できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>session_ui.return_lobby_denied</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>結果確定後、リーダーのみがパーティーをロビーに戻せます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>session_ui.passive_invalid</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>パッシブのプロフィールを確認できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>session_ui.party_not_ready</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>全員がキャラクターを選択し、準備を完了してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>preparation_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ゲームを準備しています…</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>ゲームの準備がタイムアウトしました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout_retry</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>ゲームの準備がタイムアウトしました。切断してもう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>preparation_ui.combat_failed</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>戦闘の準備に失敗しました。再接続してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>接続が終了しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>preparation_ui.exit</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>退出</t>
         </is>
       </c>
     </row>
@@ -9716,7 +11228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12805,6 +14317,510 @@
         </is>
       </c>
     </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>upgrade_ui.request_failed</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>无法发送强化请求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>upgrade_ui.request_pending</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>正在确认物品和金币…</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>upgrade_ui.state_changed</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>物品状态已变更，请重新选择。</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>upgrade_ui.item_missing</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>背包中未找到该物品。</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>result_ui.stage</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>最终到达关卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>result_ui.defeated</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>击败敌人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>result_ui.play_time</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>游戏时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>result_ui.credits</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>获得信用点</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>result_ui.retry</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>再玩一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>result_ui.return_lobby</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>返回大厅</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>result_ui.leave_session</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>离开会话</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>result_ui.clear_description</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>已通关全部关卡！</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>result_ui.defeat_description</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>本次远征已结束。</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>result_ui.data_waiting</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>正在接收服务器结果…</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>result_ui.data_missing</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>尚未收到结果。您可以继续等待或离开。</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>result_ui.request_pending</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>正在等待服务器响应…</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>session_ui.end_host</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>结束主机会话</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>session_ui.leave</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>离开会话</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>session_ui.leave_temporarily</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>暂时离开</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_end_host</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>要结束主机会话吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>session_ui.warn_end_host</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>所有玩家将断开连接，当前冒险将结束。</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_leave</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>要离开此会话吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>session_ui.warn_leave</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>您将放弃参与资格，无法重新加入本次冒险。</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>session_ui.confirm_temporary_leave</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>要暂时离开此会话吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>session_ui.warn_temporary_leave</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>服务器在线时可在5分钟内重新连接。队伍的游戏会继续。</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>session_ui.passive_locked</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>取消准备后才能更改被动技能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>正在保存结果，请稍后重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait_host</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>正在等待玩家结果保存。请在保存完成后结束会话。</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>session_ui.settlement_wait_player</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>正在等待{0}的结果保存，请稍后重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>session_ui.lobby_loading</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>请等待大厅加载完成后再出发。</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>session_ui.player_prefabs_missing</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>玩家配置不完整，请重新连接。</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>session_ui.session_missing</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>未找到当前会话。</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>session_ui.unsupported_request</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>此大厅操作不可用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>session_ui.return_lobby_denied</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>结果确认后，仅队长能带领队伍返回大厅。</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>session_ui.passive_invalid</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>无法验证被动技能资料。</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>session_ui.party_not_ready</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>所有玩家必须选择角色并准备就绪。</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>preparation_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>正在准备游戏…</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>游戏准备超时。</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout_retry</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>游戏准备超时，请断开连接后重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>preparation_ui.combat_failed</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>战斗准备失败，请重新连接。</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>连接已结束。</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>preparation_ui.exit</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>离开</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -2960,6 +2960,510 @@
         <x:v>서버와 연결이 끊어졌습니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="244">
+      <x:c r="A244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.request_failed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">서버 강화 요청을 시작하지 못했습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.request_pending</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">서버가 강화 가능 여부와 골드를 확인하고 있습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.state_changed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">아이템 상태가 먼저 바뀌어 강화를 취소했습니다. 다시 선택해 주세요.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.item_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">인벤토리에서 해당 아이템을 찾지 못했습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.stage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">최종 도달 스테이지</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.defeated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">처치한 적</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.play_time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">플레이 시간</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.credits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">획득 크레딧</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.retry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">다시 시작</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.return_lobby</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로비로 돌아가기</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.leave_session</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">세션 나가기</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.clear_description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">모든 스테이지를 클리어했습니다!</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.defeat_description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이번 원정이 종료되었습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.data_waiting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">서버에서 결과를 받는 중입니다…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.data_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">결과를 아직 받지 못했습니다. 계속 기다리거나 나갈 수 있습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.request_pending</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">서버 응답을 기다리고 있습니다…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">호스트 세션 종료</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">세션 떠나기</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.leave_temporarily</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">잠시 나가기</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">호스트 세션을 종료하시겠습니까?</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">모든 참가자의 연결과 현재 런이 종료됩니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">이 세션에서 떠나시겠습니까?</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_temporary_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">잠시 세션에서 나가시겠습니까?</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_temporary_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.passive_locked</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">준비를 취소한 뒤 패시브를 변경할 수 있습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">참가자의 결과 저장을 기다리고 있습니다. 저장 후 세션을 종료해 주세요.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait_player</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0}의 결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.lobby_loading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">로비 이동이 끝난 뒤 출발할 수 있습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.player_prefabs_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">두 클래스의 네트워크 프리팹 연결을 확인하세요.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.session_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">참여 중인 세션을 찾을 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.unsupported_request</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">지원하지 않는 로비 요청입니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.return_lobby_denied</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">서버가 결과를 확정한 뒤 방장만 파티를 로비로 이동할 수 있습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.passive_invalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">패시브 프로필을 확인할 수 없습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.party_not_ready</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">모든 참가자가 캐릭터 선택과 준비를 완료해야 합니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.waiting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">플레이를 준비하고 있습니다…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.timeout</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">플레이 준비 시간이 초과되었습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.timeout_retry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">플레이 준비 시간이 초과되었습니다. 연결을 종료하고 다시 시도하세요.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.combat_failed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">전투 웨이브 또는 생성 지점 준비에 실패했습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.disconnected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">연결이 종료되었습니다.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.exit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">나가기</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -5599,6 +6103,510 @@
         <x:v>Disconnected from the server.</x:v>
       </x:c>
     </x:row>
+    <x:row r="244">
+      <x:c r="A244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.request_failed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Could not send the upgrade request.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.request_pending</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Checking the item and available gold…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.state_changed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The item changed. Select it again to upgrade.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.item_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The item is no longer in your inventory.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.stage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Stage Reached</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.defeated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enemies Defeated</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.play_time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Play Time</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.credits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Credits Earned</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.retry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Play Again</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.return_lobby</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Return to Lobby</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.leave_session</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Leave Session</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.clear_description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">All stages cleared!</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.defeat_description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This expedition has ended.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.data_waiting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Receiving results from the server…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.data_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Results have not arrived yet. You can wait or leave.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.request_pending</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Waiting for the server…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">End Host Session</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Leave Session</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.leave_temporarily</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Disconnect Temporarily</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">End this host session?</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">All players will disconnect and the current run will end.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Leave this session?</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">You will forfeit your place and cannot rejoin this run.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_temporary_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Disconnect from this session temporarily?</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_temporary_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">You can reconnect within 5 minutes while the server stays online. The party will keep playing.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.passive_locked</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Cancel Ready before changing passives.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Results are still being saved. Please try again shortly.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Waiting for player results to save. End the session after saving finishes.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait_player</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Waiting for {0}'s results to save. Please try again shortly.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.lobby_loading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Wait for the lobby to finish loading before starting.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.player_prefabs_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Player setup is incomplete. Please reconnect.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.session_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The current session could not be found.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.unsupported_request</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This lobby action is unavailable.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.return_lobby_denied</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Only the leader can return the party to the lobby after results are confirmed.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.passive_invalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Your passive profile could not be verified.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.party_not_ready</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">All players must choose a character and be ready.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.waiting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Preparing the game…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.timeout</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Game preparation timed out.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.timeout_retry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Game preparation timed out. Disconnect and try again.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.combat_failed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The battle could not be prepared. Please reconnect.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.disconnected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">The connection has ended.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.exit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Leave</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -8238,6 +9246,510 @@
         <x:v>サーバーとの接続が切れました。</x:v>
       </x:c>
     </x:row>
+    <x:row r="244">
+      <x:c r="A244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.request_failed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">強化リクエストを送信できませんでした。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.request_pending</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">アイテムと所持ゴールドを確認しています…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.state_changed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">アイテムの状態が変わりました。もう一度選択してください。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.item_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">インベントリに対象のアイテムがありません。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.stage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">最終到達ステージ</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.defeated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">倒した敵</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.play_time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">プレイ時間</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.credits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">獲得クレジット</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.retry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">もう一度プレイ</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.return_lobby</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ロビーに戻る</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.leave_session</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">セッションを退出</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.clear_description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全ステージをクリアしました！</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.defeat_description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">今回の遠征は終了しました。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.data_waiting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">サーバーから結果を受信しています…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.data_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">結果がまだ届いていません。待機するか退出できます。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.request_pending</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">サーバーの応答を待っています…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ホストセッションを終了</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">セッションを退出</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.leave_temporarily</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">一時的に退出</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ホストセッションを終了しますか？</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全員の接続と現在のプレイが終了します。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">このセッションを退出しますか？</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">参加権を放棄するため、このプレイには再接続できません。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_temporary_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">セッションから一時的に退出しますか？</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_temporary_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">サーバーが稼働中なら5分以内に再接続できます。パーティーのゲームは続行されます。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.passive_locked</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">準備を解除するとパッシブを変更できます。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">結果を保存しています。少し待ってからお試しください。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">参加者の結果を保存しています。保存完了後にセッションを終了してください。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait_player</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{0}の結果を保存しています。少し待ってからお試しください。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.lobby_loading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ロビーの読み込みが終わってから出発してください。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.player_prefabs_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">プレイヤーの準備が不完全です。再接続してください。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.session_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">参加中のセッションが見つかりません。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.unsupported_request</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">このロビー操作は利用できません。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.return_lobby_denied</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">結果確定後、リーダーのみがパーティーをロビーに戻せます。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.passive_invalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">パッシブのプロフィールを確認できません。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.party_not_ready</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全員がキャラクターを選択し、準備を完了してください。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.waiting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ゲームを準備しています…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.timeout</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ゲームの準備がタイムアウトしました。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.timeout_retry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ゲームの準備がタイムアウトしました。切断してもう一度お試しください。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.combat_failed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">戦闘の準備に失敗しました。再接続してください。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.disconnected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">接続が終了しました。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.exit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">退出</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -10877,6 +12389,510 @@
         <x:v>与服务器的连接已断开。</x:v>
       </x:c>
     </x:row>
+    <x:row r="244">
+      <x:c r="A244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.request_failed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B244" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">无法发送强化请求。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="245">
+      <x:c r="A245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.request_pending</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B245" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">正在确认物品和金币…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="246">
+      <x:c r="A246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.state_changed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B246" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">物品状态已变更，请重新选择。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="247">
+      <x:c r="A247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">upgrade_ui.item_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B247" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">背包中未找到该物品。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="248">
+      <x:c r="A248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.stage</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B248" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">最终到达关卡</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="249">
+      <x:c r="A249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.defeated</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B249" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">击败敌人数</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="250">
+      <x:c r="A250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.play_time</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B250" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">游戏时间</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="251">
+      <x:c r="A251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.credits</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B251" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得信用点</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="252">
+      <x:c r="A252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.retry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B252" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">再玩一次</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="253">
+      <x:c r="A253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.return_lobby</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B253" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">返回大厅</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="254">
+      <x:c r="A254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.leave_session</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B254" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">离开会话</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="255">
+      <x:c r="A255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.clear_description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B255" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已通关全部关卡！</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="256">
+      <x:c r="A256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.defeat_description</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B256" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本次远征已结束。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="257">
+      <x:c r="A257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.data_waiting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B257" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">正在接收服务器结果…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="258">
+      <x:c r="A258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.data_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B258" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">尚未收到结果。您可以继续等待或离开。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="259">
+      <x:c r="A259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">result_ui.request_pending</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B259" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">正在等待服务器响应…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="260">
+      <x:c r="A260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B260" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">结束主机会话</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="261">
+      <x:c r="A261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B261" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">离开会话</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="262">
+      <x:c r="A262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.leave_temporarily</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B262" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">暂时离开</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="263">
+      <x:c r="A263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B263" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">要结束主机会话吗？</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="264">
+      <x:c r="A264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_end_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B264" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">所有玩家将断开连接，当前冒险将结束。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="265">
+      <x:c r="A265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B265" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">要离开此会话吗？</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B266" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">您将放弃参与资格，无法重新加入本次冒险。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.confirm_temporary_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B267" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">要暂时离开此会话吗？</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.warn_temporary_leave</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B268" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">服务器在线时可在5分钟内重新连接。队伍的游戏会继续。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="269">
+      <x:c r="A269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.passive_locked</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B269" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">取消准备后才能更改被动技能。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="270">
+      <x:c r="A270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B270" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">正在保存结果，请稍后重试。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="271">
+      <x:c r="A271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait_host</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B271" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">正在等待玩家结果保存。请在保存完成后结束会话。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="272">
+      <x:c r="A272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.settlement_wait_player</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B272" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">正在等待{0}的结果保存，请稍后重试。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="273">
+      <x:c r="A273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.lobby_loading</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B273" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">请等待大厅加载完成后再出发。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="274">
+      <x:c r="A274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.player_prefabs_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B274" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">玩家配置不完整，请重新连接。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="275">
+      <x:c r="A275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.session_missing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B275" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未找到当前会话。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="276">
+      <x:c r="A276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.unsupported_request</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B276" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">此大厅操作不可用。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="277">
+      <x:c r="A277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.return_lobby_denied</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B277" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">结果确认后，仅队长能带领队伍返回大厅。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="278">
+      <x:c r="A278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.passive_invalid</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B278" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">无法验证被动技能资料。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="279">
+      <x:c r="A279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">session_ui.party_not_ready</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B279" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">所有玩家必须选择角色并准备就绪。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="280">
+      <x:c r="A280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.waiting</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B280" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">正在准备游戏…</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="281">
+      <x:c r="A281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.timeout</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B281" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">游戏准备超时。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="282">
+      <x:c r="A282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.timeout_retry</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B282" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">游戏准备超时，请断开连接后重试。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="283">
+      <x:c r="A283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.combat_failed</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B283" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">战斗准备失败，请重新连接。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="284">
+      <x:c r="A284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.disconnected</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B284" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">连接已结束。</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="285">
+      <x:c r="A285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">preparation_ui.exit</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B285" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">离开</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B171"/>
+  <dimension ref="A1:B185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,174 @@
       <c r="B171" t="inlineStr">
         <is>
           <t>현재 설정이 모두 기본값으로 변경됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_confirm</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>게임을 포기하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_warning</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>경고: 현재 게임 데이터가 사라집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_reconfirm</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>정말 포기하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_reconfirm_warning</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>진행 중인 원정이 초기화되며 크레딧을 받을 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>pause_ui.save_and_quit_confirm</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>게임을 저장하고 종료하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>pause_ui.host_end_confirm</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>호스트 세션을 종료하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>pause_ui.host_end_warning</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>모든 참가자의 연결과 현재 런이 종료됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>pause_ui.leave_confirm</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>이 세션에서 떠나시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>pause_ui.leave_warning</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>pause_ui.temp_leave_confirm</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>잠시 세션에서 나가시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>pause_ui.temp_leave_warning</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>pause_ui.adjustment</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>정산 후 액트 종료</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>pause_ui.settle_confirm</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>정산 후 게임을 종료하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>pause_ui.settle_warning</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>보유 크레딧과 아이템 원가의 50%를 계정 크레딧으로 받고, 현재 원정은 초기화됩니다.</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B171"/>
+  <dimension ref="A1:B185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4536,6 +4704,174 @@
       <c r="B171" t="inlineStr">
         <is>
           <t>All current settings will be restored to their defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_confirm</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Give up this game?</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_warning</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Warning: Your current game data will be lost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_reconfirm</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Are you sure you want to give up?</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_reconfirm_warning</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>The current run will be reset and no credits will be earned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>pause_ui.save_and_quit_confirm</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Save and quit the game?</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>pause_ui.host_end_confirm</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>End the host session?</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>pause_ui.host_end_warning</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>All participants will be disconnected and the current run will end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>pause_ui.leave_confirm</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Leave this session?</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>pause_ui.leave_warning</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>You will give up your spot and cannot rejoin this run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>pause_ui.temp_leave_confirm</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Step out of the session for now?</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>pause_ui.temp_leave_warning</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>You can rejoin within 5 minutes while the server is running. The party's game will continue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>pause_ui.adjustment</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Settle &amp; End Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>pause_ui.settle_confirm</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Settle and end the game?</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>pause_ui.settle_warning</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>You will receive your credits plus 50% of your items' base value as account credits, and the current run will be reset.</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B171"/>
+  <dimension ref="A1:B185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6603,6 +6939,174 @@
       <c r="B171" t="inlineStr">
         <is>
           <t>現在の設定はすべて初期値に戻ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_confirm</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ゲームをあきらめますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_warning</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>警告：現在のゲームデータは失われます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_reconfirm</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>本当に諦めますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_reconfirm_warning</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>進行中の遠征はリセットされ、クレジットは獲得できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>pause_ui.save_and_quit_confirm</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ゲームを保存して終了しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>pause_ui.host_end_confirm</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ホストセッションを終了しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>pause_ui.host_end_warning</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>すべての参加者の接続と現在のランが終了します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>pause_ui.leave_confirm</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>このセッションから退出しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>pause_ui.leave_warning</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>参加資格を放棄し、このランには再接続できません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>pause_ui.temp_leave_confirm</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>一時的にセッションから退出しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>pause_ui.temp_leave_warning</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>サーバーが維持されている間は5分以内に再接続できます。パーティーのゲームは続行されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>pause_ui.adjustment</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>精算して終了</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>pause_ui.settle_confirm</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>精算してゲームを終了しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>pause_ui.settle_warning</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>所持クレジットとアイテム原価の50%をアカウントクレジットとして受け取り、現在の遠征はリセットされます。</t>
         </is>
       </c>
     </row>
@@ -6617,7 +7121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B171"/>
+  <dimension ref="A1:B185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8673,6 +9177,174 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_confirm</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>要放弃游戏吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_warning</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>警告：当前游戏数据将会丢失。</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_reconfirm</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>确定要放弃吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>pause_ui.giveup_reconfirm_warning</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>当前远征将被重置，且无法获得信用点。</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>pause_ui.save_and_quit_confirm</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>要保存并退出游戏吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>pause_ui.host_end_confirm</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>要结束主机会话吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>pause_ui.host_end_warning</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>所有参与者的连接和当前轮次都将结束。</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>pause_ui.leave_confirm</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>要离开此会话吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>pause_ui.leave_warning</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>你将放弃参与资格，且无法重新加入本轮。</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>pause_ui.temp_leave_confirm</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>要暂时离开会话吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>pause_ui.temp_leave_warning</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>服务器保持运行期间，可在5分钟内重新连接。队伍的游戏将继续进行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>pause_ui.adjustment</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>结算并结束</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>pause_ui.settle_confirm</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>要结算并结束游戏吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>pause_ui.settle_warning</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>将获得持有信用点及物品原价的50%作为账号信用点，当前远征将被重置。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -2312,7 +2312,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>체력 회복</t>
+          <t>체력 25% 회복</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Health Restored</t>
+          <t>Restore 25% HP</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>体力回復</t>
+          <t>体力25%回復</t>
         </is>
       </c>
     </row>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>生命恢复</t>
+          <t>恢复25%生命</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1190,1451 +1190,1463 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>status_ui.header</t>
+          <t>skill_ui.arc_laser_name</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>아크 레이저</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>status_ui.detail_toggle</t>
+          <t>status_ui.header</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>세부 스탯 보기</t>
+          <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>status_ui.type_header</t>
+          <t>status_ui.detail_toggle</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TYPE</t>
+          <t>세부 스탯 보기</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>shop_ui.header</t>
+          <t>status_ui.type_header</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>TYPE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>inventory_ui.header</t>
+          <t>shop_ui.header</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>인벤토리</t>
+          <t>상점</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>upgrade_ui.header</t>
+          <t>inventory_ui.header</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>강화</t>
+          <t>인벤토리</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>item_tooltip_ui.sub_option_label</t>
+          <t>upgrade_ui.header</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>부가 옵션</t>
+          <t>강화</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>item_tooltip_ui.unique_effect_label</t>
+          <t>item_tooltip_ui.sub_option_label</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>고유 효과</t>
+          <t>부가 옵션</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>upgrade_ui.current_stat</t>
+          <t>item_tooltip_ui.unique_effect_label</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>현재 스탯 : {0} + {1}</t>
+          <t>고유 효과</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>upgrade_ui.next_stat</t>
+          <t>upgrade_ui.current_stat</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>강화 후 스탯 : {0} + {1}</t>
+          <t>현재 스탯 : {0} + {1}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>upgrade_ui.cost</t>
+          <t>upgrade_ui.next_stat</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>강화비용 : {0}</t>
+          <t>강화 후 스탯 : {0} + {1}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>upgrade_ui.cost_unavailable</t>
+          <t>upgrade_ui.cost</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>강화비용 : -</t>
+          <t>강화비용 : {0}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>upgrade_ui.unknown_item</t>
+          <t>upgrade_ui.cost_unavailable</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t>강화비용 : -</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>upgrade_ui.selection_required</t>
+          <t>upgrade_ui.unknown_item</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>강화할 아이템을 선택하세요.</t>
+          <t>아이템</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_success</t>
+          <t>upgrade_ui.selection_required</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{0} +{1} 강화 성공</t>
+          <t>강화할 아이템을 선택하세요.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_not_enough_gold</t>
+          <t>upgrade_ui.result_success</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>크레딧이 부족합니다.</t>
+          <t>{0} +{1} 강화 성공</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_invalid_item</t>
+          <t>upgrade_ui.result_not_enough_gold</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>강화할 수 없는 아이템입니다.</t>
+          <t>크레딧이 부족합니다.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_invalid_cost</t>
+          <t>upgrade_ui.result_invalid_item</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>강화 비용 설정이 올바르지 않습니다.</t>
+          <t>강화할 수 없는 아이템입니다.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_wallet_unavailable</t>
+          <t>upgrade_ui.result_invalid_cost</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>강화 처리 중 문제가 발생했습니다.</t>
+          <t>강화 비용 설정이 올바르지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_failed</t>
+          <t>upgrade_ui.result_wallet_unavailable</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>강화에 실패했습니다.</t>
+          <t>강화 처리 중 문제가 발생했습니다.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>npc_ui.quest</t>
+          <t>upgrade_ui.result_failed</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>의뢰</t>
+          <t>강화에 실패했습니다.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>npc_ui.rest</t>
+          <t>npc_ui.quest</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>휴식</t>
+          <t>의뢰</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>chat_ui.equip_success</t>
+          <t>npc_ui.rest</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>장비 처리가 완료되었습니다.</t>
+          <t>휴식</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>chat_ui.equip_swapped</t>
+          <t>chat_ui.equip_success</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>장비를 교체했습니다.</t>
+          <t>장비 처리가 완료되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>chat_ui.equip_invalid_item</t>
+          <t>chat_ui.equip_swapped</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>장착할 수 없는 아이템입니다.</t>
+          <t>장비를 교체했습니다.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>chat_ui.equip_invalid_slot</t>
+          <t>chat_ui.equip_invalid_item</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>해당 슬롯에 장착할 수 없습니다.</t>
+          <t>장착할 수 없는 아이템입니다.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>chat_ui.equip_slot_occupied</t>
+          <t>chat_ui.equip_invalid_slot</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>이미 장비가 장착되어 있습니다.</t>
+          <t>해당 슬롯에 장착할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>chat_ui.equip_not_equipped</t>
+          <t>chat_ui.equip_slot_occupied</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>해제할 장비가 없습니다.</t>
+          <t>이미 장비가 장착되어 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>chat_ui.equip_no_return_space</t>
+          <t>chat_ui.equip_not_equipped</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>기존 장비를 인벤토리에 내려놓을 공간이 없습니다.</t>
+          <t>해제할 장비가 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>chat_ui.equip_failed</t>
+          <t>chat_ui.equip_no_return_space</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>장비 처리가 실패했습니다.</t>
+          <t>기존 장비를 인벤토리에 내려놓을 공간이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>chat_ui.equip_wrong_class</t>
+          <t>chat_ui.equip_failed</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>이 캐릭터가 장착할 수 없는 무기입니다.</t>
+          <t>장비 처리가 실패했습니다.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>chat_ui.equip_unknown</t>
+          <t>chat_ui.equip_wrong_class</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>알 수 없는 장비 처리 결과입니다.</t>
+          <t>이 캐릭터가 장착할 수 없는 무기입니다.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_acquisition</t>
+          <t>chat_ui.equip_unknown</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{0} 아이템을 획득했습니다.</t>
+          <t>알 수 없는 장비 처리 결과입니다.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_acquisition_colored</t>
+          <t>chat_ui.inventory_acquisition</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{0} 획득했습니다.</t>
+          <t>{0} 아이템을 획득했습니다.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_success_position</t>
+          <t>chat_ui.inventory_acquisition_colored</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{0} 위치 : {1}, {2}</t>
+          <t>{0} 획득했습니다.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_invalid_item</t>
+          <t>chat_ui.inventory_success_position</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>유효하지 않은 아이템입니다.</t>
+          <t>{0} 위치 : {1}, {2}</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_no_space</t>
+          <t>chat_ui.inventory_invalid_item</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>인벤토리가 꽉 찼습니다!</t>
+          <t>유효하지 않은 아이템입니다.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_grid_unavailable</t>
+          <t>chat_ui.inventory_no_space</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>인벤토리를 사용할 수 없습니다.</t>
+          <t>인벤토리가 꽉 찼습니다!</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_placement_failed</t>
+          <t>chat_ui.inventory_grid_unavailable</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>인벤토리에 아이템을 배치하지 못했습니다.</t>
+          <t>인벤토리를 사용할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_add_failed</t>
+          <t>chat_ui.inventory_placement_failed</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>아이템 획득에 실패했습니다.</t>
+          <t>인벤토리에 아이템을 배치하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_success</t>
+          <t>chat_ui.inventory_add_failed</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{0}을(를) 삭제했습니다.</t>
+          <t>아이템 획득에 실패했습니다.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_invalid_item</t>
+          <t>chat_ui.inventory_remove_success</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>유효하지 않은 아이템입니다.</t>
+          <t>{0}을(를) 삭제했습니다.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_unavailable</t>
+          <t>chat_ui.inventory_remove_invalid_item</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>인벤토리를 사용할 수 없습니다.</t>
+          <t>유효하지 않은 아이템입니다.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_not_player</t>
+          <t>chat_ui.inventory_remove_unavailable</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>내 인벤토리의 아이템만 삭제할 수 있습니다.</t>
+          <t>인벤토리를 사용할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
+          <t>chat_ui.inventory_remove_not_player</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>장착 중인 아이템은 바로 삭제할 수 없습니다.</t>
+          <t>내 인벤토리의 아이템만 삭제할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_failed</t>
+          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>아이템 삭제에 실패했습니다.</t>
+          <t>장착 중인 아이템은 바로 삭제할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_default_failed</t>
+          <t>chat_ui.inventory_remove_failed</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>아이템을 삭제하지 못했습니다.</t>
+          <t>아이템 삭제에 실패했습니다.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>chat_ui.shop_buy_success</t>
+          <t>chat_ui.inventory_remove_default_failed</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{0}을 구매했습니다.</t>
+          <t>아이템을 삭제하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>chat_ui.shop_sell_success</t>
+          <t>chat_ui.shop_buy_success</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{0}을 판매했습니다.</t>
+          <t>{0}을 구매했습니다.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>chat_ui.shop_not_enough_gold</t>
+          <t>chat_ui.shop_sell_success</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>크레딧이 부족해 {0} 구매에 실패했습니다.</t>
+          <t>{0}을 판매했습니다.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>chat_ui.shop_no_space_buy</t>
+          <t>chat_ui.shop_not_enough_gold</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>인벤토리에 공간이 없습니다.</t>
+          <t>크레딧이 부족해 {0} 구매에 실패했습니다.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>chat_ui.shop_no_space_sell</t>
+          <t>chat_ui.shop_no_space_buy</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>상점에 판매 아이템을 놓을 공간이 없습니다.</t>
+          <t>인벤토리에 공간이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>chat_ui.shop_invalid_item</t>
+          <t>chat_ui.shop_no_space_sell</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>유효하지 않은 아이템입니다.</t>
+          <t>상점에 판매 아이템을 놓을 공간이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>chat_ui.shop_transfer_failed</t>
+          <t>chat_ui.shop_invalid_item</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>{0} 이동 중 거래에 실패했습니다.</t>
+          <t>유효하지 않은 아이템입니다.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>chat_ui.shop_stock_update_failed</t>
+          <t>chat_ui.shop_transfer_failed</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{0} 재고 처리에 실패했습니다.</t>
+          <t>{0} 이동 중 거래에 실패했습니다.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>chat_ui.shop_failed</t>
+          <t>chat_ui.shop_stock_update_failed</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>거래 처리에 실패했습니다.</t>
+          <t>{0} 재고 처리에 실패했습니다.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>chat_ui.pickup_default</t>
+          <t>chat_ui.shop_failed</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>아이템을 획득했습니다.</t>
+          <t>거래 처리에 실패했습니다.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>chat_ui.out_of_range</t>
+          <t>chat_ui.pickup_default</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>아이템에 더 가까이 이동해 주세요.</t>
+          <t>아이템을 획득했습니다.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>chat_ui.already_claimed</t>
+          <t>chat_ui.out_of_range</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>이미 획득된 아이템입니다.</t>
+          <t>아이템에 더 가까이 이동해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>chat_ui.pickup_unavailable</t>
+          <t>chat_ui.already_claimed</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>더 이상 획득할 수 없는 아이템입니다.</t>
+          <t>이미 획득된 아이템입니다.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>chat_ui.item_unavailable</t>
+          <t>chat_ui.pickup_unavailable</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>대상 아이템을 찾을 수 없습니다.</t>
+          <t>더 이상 획득할 수 없는 아이템입니다.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>chat_ui.stale_revision</t>
+          <t>chat_ui.item_unavailable</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>아이템 상태가 바뀌었습니다. 다시 시도해 주세요.</t>
+          <t>대상 아이템을 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>chat_ui.recovery_failed</t>
+          <t>chat_ui.stale_revision</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>아이템 드랍과 인벤토리 복구에 실패했습니다. 인벤토리 상태를 확인해 주세요.</t>
+          <t>아이템 상태가 바뀌었습니다. 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>chat_ui.upgrade_process_failed</t>
+          <t>chat_ui.recovery_failed</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>강화를 처리하지 못했습니다. 다시 시도해 주세요.</t>
+          <t>아이템 드랍과 인벤토리 복구에 실패했습니다. 인벤토리 상태를 확인해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>chat_ui.drop_failed</t>
+          <t>chat_ui.upgrade_process_failed</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>아이템을 필드에 놓지 못했습니다. 다시 시도해 주세요.</t>
+          <t>강화를 처리하지 못했습니다. 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>chat_ui.acquisition_failed</t>
+          <t>chat_ui.drop_failed</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>아이템을 획득하지 못했습니다. 다시 시도해 주세요.</t>
+          <t>아이템을 필드에 놓지 못했습니다. 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>chat_ui.shop_state_changed</t>
+          <t>chat_ui.acquisition_failed</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>상점 상태가 바뀌었습니다. 다시 선택해 주세요.</t>
+          <t>아이템을 획득하지 못했습니다. 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_state_changed</t>
+          <t>chat_ui.shop_state_changed</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>인벤토리 상태가 바뀌었습니다. 다시 시도해 주세요.</t>
+          <t>상점 상태가 바뀌었습니다. 다시 선택해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>chat_ui.trade_failed</t>
+          <t>chat_ui.inventory_state_changed</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>거래를 처리하지 못했습니다. 다시 시도해 주세요.</t>
+          <t>인벤토리 상태가 바뀌었습니다. 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>loading_ui.tooltip_title</t>
+          <t>chat_ui.trade_failed</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>데브리스-9</t>
+          <t>거래를 처리하지 못했습니다. 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>loading_ui.tooltip_content</t>
+          <t>loading_ui.tooltip_title</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>이곳은 오염으로 인해 인간이 살 수 없는 버려진 땅이었지만, 수백 년간 쌓인 로봇 잔해들이 스스로를 복구하고 개조하기 시작하면서 기괴한 메카 생태계가 만들어졌습니다.</t>
+          <t>데브리스-9</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>common_ui.yes</t>
+          <t>loading_ui.tooltip_content</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>예</t>
+          <t>이곳은 오염으로 인해 인간이 살 수 없는 버려진 땅이었지만, 수백 년간 쌓인 로봇 잔해들이 스스로를 복구하고 개조하기 시작하면서 기괴한 메카 생태계가 만들어졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>common_ui.confirm</t>
+          <t>common_ui.yes</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>예</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>chat_ui.panel_title</t>
+          <t>common_ui.confirm</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>채팅</t>
+          <t>확인</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>chat_ui.input_placeholder</t>
+          <t>chat_ui.panel_title</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>메시지 입력…</t>
+          <t>채팅</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>chat_ui.connect_hint</t>
+          <t>chat_ui.input_placeholder</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>접속 후 대화할 수 있습니다</t>
+          <t>메시지 입력…</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>chat_ui.unread_indicator</t>
+          <t>chat_ui.connect_hint</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>새 메시지 ↓</t>
+          <t>접속 후 대화할 수 있습니다</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.title</t>
+          <t>chat_ui.unread_indicator</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>스킬 진화·강화 설정</t>
+          <t>새 메시지 ↓</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.hint</t>
+          <t>skill_evolution_ui.title</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>K로 열기/닫기 - 왼쪽 버튼: 진화(없음→진화1→2→3), 오른쪽 버튼: 강화(없음→강화1→2→3)</t>
+          <t>스킬 진화·강화 설정</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.none</t>
+          <t>skill_evolution_ui.hint</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>K로 열기/닫기 - 왼쪽 버튼: 진화(없음→진화1→2→3), 오른쪽 버튼: 강화(없음→강화1→2→3)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>passive_skill_ui.title</t>
+          <t>skill_evolution_ui.none</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>패시브 업그레이드</t>
+          <t>없음</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>passive_skill_ui.skill_clear</t>
+          <t>passive_skill_ui.title</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>초기화</t>
+          <t>패시브 업그레이드</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>passive_skill_ui.skill_points</t>
+          <t>passive_skill_ui.skill_clear</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>스킬 포인트 -</t>
+          <t>초기화</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>passive_skill_ui.credit_format</t>
+          <t>passive_skill_ui.skill_points</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>크레딧 | {0}</t>
+          <t>스킬 포인트 -</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>passive_skill_ui.credit_none</t>
+          <t>passive_skill_ui.credit_format</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>크레딧 | -</t>
+          <t>크레딧 | {0}</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>passive_skill_ui.profile_loading</t>
+          <t>passive_skill_ui.credit_none</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>프로필 준비 중</t>
+          <t>크레딧 | -</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>passive_skill_ui.confirm_ok</t>
+          <t>passive_skill_ui.profile_loading</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>프로필 준비 중</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_current_level</t>
+          <t>passive_skill_ui.confirm_ok</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>현재 레벨: {0} / {1}</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_current_effect</t>
+          <t>passive_skill_ui.detail_current_level</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>현재 효과: {0}</t>
+          <t>현재 레벨: {0} / {1}</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_next_level</t>
+          <t>passive_skill_ui.detail_current_effect</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>다음 레벨: {0}</t>
+          <t>현재 효과: {0}</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>common_ui.cancel</t>
+          <t>passive_skill_ui.detail_next_level</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>다음 레벨: {0}</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rest_ui.header</t>
+          <t>common_ui.cancel</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>휴식</t>
+          <t>취소</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>rest_ui.header</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>휴식</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>rest_ui.description</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>크레딧을 지불하여
 휴식을 취하시겠습니까?</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>rest_ui.health_recovery</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>체력 25% 회복</t>
-        </is>
-      </c>
-    </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rest_ui.potion_recharge</t>
+          <t>rest_ui.health_recovery</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>포션 충전</t>
+          <t>체력 25% 회복</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rest_ui.cost_format</t>
+          <t>rest_ui.potion_recharge</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>필요 크레딧 : {0}</t>
+          <t>포션 충전</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rest_ui.complete_message</t>
+          <t>rest_ui.cost_format</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>{0} 크레딧을 소비하여 체력 {1}, 포션 {2}개를 채웠습니다.</t>
+          <t>필요 크레딧 : {0}</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_chat</t>
+          <t>rest_ui.complete_message</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">[채팅] </t>
+          <t>{0} 크레딧을 소비하여 체력 {1}, 포션 {2}개를 채웠습니다.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_acquisition</t>
+          <t>chat_ui.prefix_chat</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">[획득] </t>
+          <t xml:space="preserve">[채팅] </t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_warning</t>
+          <t>chat_ui.prefix_acquisition</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">[안내] </t>
+          <t xml:space="preserve">[획득] </t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_connection</t>
+          <t>chat_ui.prefix_warning</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">[연결] </t>
+          <t xml:space="preserve">[안내] </t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>chat_ui.item_fallback_name</t>
+          <t>chat_ui.prefix_connection</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t xml:space="preserve">[연결] </t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_cost_format</t>
+          <t>chat_ui.item_fallback_name</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 리롤</t>
+          <t>아이템</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_free</t>
+          <t>shop_ui.reroll_cost_format</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>무료 리롤</t>
+          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 리롤</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_count_format</t>
+          <t>shop_ui.reroll_free</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[ {0} ]</t>
+          <t>무료 리롤</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>settings_ui.reset_confirm</t>
+          <t>shop_ui.reroll_count_format</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>설정을 기본값으로 초기화하시겠습니까?</t>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>settings_ui.reset_warning</t>
+          <t>settings_ui.reset_confirm</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>현재 설정이 모두 기본값으로 변경됩니다.</t>
+          <t>설정을 기본값으로 초기화하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_confirm</t>
+          <t>settings_ui.reset_warning</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>게임을 포기하시겠습니까?</t>
+          <t>현재 설정이 모두 기본값으로 변경됩니다.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_warning</t>
+          <t>pause_ui.giveup_confirm</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>경고: 현재 게임 데이터가 사라집니다.</t>
+          <t>게임을 포기하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm</t>
+          <t>pause_ui.giveup_warning</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>정말 포기하시겠습니까?</t>
+          <t>경고: 현재 게임 데이터가 사라집니다.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm_warning</t>
+          <t>pause_ui.giveup_reconfirm</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>진행 중인 원정이 초기화되며 크레딧을 받을 수 없습니다.</t>
+          <t>정말 포기하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>pause_ui.save_and_quit_confirm</t>
+          <t>pause_ui.giveup_reconfirm_warning</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>게임을 저장하고 종료하시겠습니까?</t>
+          <t>진행 중인 원정이 초기화되며 크레딧을 받을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_confirm</t>
+          <t>pause_ui.save_and_quit_confirm</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>호스트 세션을 종료하시겠습니까?</t>
+          <t>게임을 저장하고 종료하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_warning</t>
+          <t>pause_ui.host_end_confirm</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>모든 참가자의 연결과 현재 런이 종료됩니다.</t>
+          <t>호스트 세션을 종료하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>pause_ui.leave_confirm</t>
+          <t>pause_ui.host_end_warning</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>이 세션에서 떠나시겠습니까?</t>
+          <t>모든 참가자의 연결과 현재 런이 종료됩니다.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>pause_ui.leave_warning</t>
+          <t>pause_ui.leave_confirm</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</t>
+          <t>이 세션에서 떠나시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_confirm</t>
+          <t>pause_ui.leave_warning</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>잠시 세션에서 나가시겠습니까?</t>
+          <t>현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_warning</t>
+          <t>pause_ui.temp_leave_confirm</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</t>
+          <t>잠시 세션에서 나가시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>pause_ui.adjustment</t>
+          <t>pause_ui.temp_leave_warning</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>정산 후 액트 종료</t>
+          <t>서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>pause_ui.settle_confirm</t>
+          <t>pause_ui.adjustment</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>정산 후 게임을 종료하시겠습니까?</t>
+          <t>정산 후 액트 종료</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>pause_ui.settle_confirm</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>정산 후 게임을 종료하시겠습니까?</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
           <t>pause_ui.settle_warning</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>보유 크레딧과 아이템 원가의 50%를 계정 크레딧으로 받고, 현재 원정은 초기화됩니다.</t>
         </is>
@@ -2651,7 +2663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3425,1451 +3437,1463 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>status_ui.header</t>
+          <t>skill_ui.arc_laser_name</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>Arc Laser</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>status_ui.detail_toggle</t>
+          <t>status_ui.header</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Show Detailed Stats</t>
+          <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>status_ui.type_header</t>
+          <t>status_ui.detail_toggle</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TYPE</t>
+          <t>Show Detailed Stats</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>shop_ui.header</t>
+          <t>status_ui.type_header</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>TYPE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>inventory_ui.header</t>
+          <t>shop_ui.header</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Shop</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>upgrade_ui.header</t>
+          <t>inventory_ui.header</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Upgrade</t>
+          <t>Inventory</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>item_tooltip_ui.sub_option_label</t>
+          <t>upgrade_ui.header</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Upgrade</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>item_tooltip_ui.unique_effect_label</t>
+          <t>item_tooltip_ui.sub_option_label</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Unique Effect</t>
+          <t>Additional Options</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>upgrade_ui.current_stat</t>
+          <t>item_tooltip_ui.unique_effect_label</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Current Stat: {0} + {1}</t>
+          <t>Unique Effect</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>upgrade_ui.next_stat</t>
+          <t>upgrade_ui.current_stat</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>After Upgrade: {0} + {1}</t>
+          <t>Current Stat: {0} + {1}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>upgrade_ui.cost</t>
+          <t>upgrade_ui.next_stat</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Upgrade Cost: {0}</t>
+          <t>After Upgrade: {0} + {1}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>upgrade_ui.cost_unavailable</t>
+          <t>upgrade_ui.cost</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Upgrade Cost: -</t>
+          <t>Upgrade Cost: {0}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>upgrade_ui.unknown_item</t>
+          <t>upgrade_ui.cost_unavailable</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Upgrade Cost: -</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>upgrade_ui.selection_required</t>
+          <t>upgrade_ui.unknown_item</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Please select an item to upgrade.</t>
+          <t>Item</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_success</t>
+          <t>upgrade_ui.selection_required</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{0} +{1} Upgrade Success</t>
+          <t>Please select an item to upgrade.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_not_enough_gold</t>
+          <t>upgrade_ui.result_success</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Not enough credits.</t>
+          <t>{0} +{1} Upgrade Success</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_invalid_item</t>
+          <t>upgrade_ui.result_not_enough_gold</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>This item cannot be upgraded.</t>
+          <t>Not enough credits.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_invalid_cost</t>
+          <t>upgrade_ui.result_invalid_item</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The upgrade cost setting is invalid.</t>
+          <t>This item cannot be upgraded.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_wallet_unavailable</t>
+          <t>upgrade_ui.result_invalid_cost</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>A problem occurred while processing the upgrade.</t>
+          <t>The upgrade cost setting is invalid.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_failed</t>
+          <t>upgrade_ui.result_wallet_unavailable</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Upgrade failed.</t>
+          <t>A problem occurred while processing the upgrade.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>npc_ui.quest</t>
+          <t>upgrade_ui.result_failed</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Quest</t>
+          <t>Upgrade failed.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>npc_ui.rest</t>
+          <t>npc_ui.quest</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Quest</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>chat_ui.equip_success</t>
+          <t>npc_ui.rest</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Equipment updated successfully.</t>
+          <t>Rest</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>chat_ui.equip_swapped</t>
+          <t>chat_ui.equip_success</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Equipment swapped.</t>
+          <t>Equipment updated successfully.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>chat_ui.equip_invalid_item</t>
+          <t>chat_ui.equip_swapped</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>This item cannot be equipped.</t>
+          <t>Equipment swapped.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>chat_ui.equip_invalid_slot</t>
+          <t>chat_ui.equip_invalid_item</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cannot equip to that slot.</t>
+          <t>This item cannot be equipped.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>chat_ui.equip_slot_occupied</t>
+          <t>chat_ui.equip_invalid_slot</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Equipment is already equipped there.</t>
+          <t>Cannot equip to that slot.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>chat_ui.equip_not_equipped</t>
+          <t>chat_ui.equip_slot_occupied</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>There is no equipment to unequip.</t>
+          <t>Equipment is already equipped there.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>chat_ui.equip_no_return_space</t>
+          <t>chat_ui.equip_not_equipped</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>No inventory space to store the previous equipment.</t>
+          <t>There is no equipment to unequip.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>chat_ui.equip_failed</t>
+          <t>chat_ui.equip_no_return_space</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Failed to process equipment.</t>
+          <t>No inventory space to store the previous equipment.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>chat_ui.equip_wrong_class</t>
+          <t>chat_ui.equip_failed</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>This character cannot equip this weapon.</t>
+          <t>Failed to process equipment.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>chat_ui.equip_unknown</t>
+          <t>chat_ui.equip_wrong_class</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Unknown equipment processing result.</t>
+          <t>This character cannot equip this weapon.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_acquisition</t>
+          <t>chat_ui.equip_unknown</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Obtained item: {0}.</t>
+          <t>Unknown equipment processing result.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_acquisition_colored</t>
+          <t>chat_ui.inventory_acquisition</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Obtained {0}.</t>
+          <t>Obtained item: {0}.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_success_position</t>
+          <t>chat_ui.inventory_acquisition_colored</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{0} Position: {1}, {2}</t>
+          <t>Obtained {0}.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_invalid_item</t>
+          <t>chat_ui.inventory_success_position</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>This item is not valid.</t>
+          <t>{0} Position: {1}, {2}</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_no_space</t>
+          <t>chat_ui.inventory_invalid_item</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Inventory is full!</t>
+          <t>This item is not valid.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_grid_unavailable</t>
+          <t>chat_ui.inventory_no_space</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Inventory is unavailable.</t>
+          <t>Inventory is full!</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_placement_failed</t>
+          <t>chat_ui.inventory_grid_unavailable</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Failed to place the item in the inventory.</t>
+          <t>Inventory is unavailable.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_add_failed</t>
+          <t>chat_ui.inventory_placement_failed</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Failed to obtain the item.</t>
+          <t>Failed to place the item in the inventory.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_success</t>
+          <t>chat_ui.inventory_add_failed</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deleted {0}.</t>
+          <t>Failed to obtain the item.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_invalid_item</t>
+          <t>chat_ui.inventory_remove_success</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>This item is not valid.</t>
+          <t>Deleted {0}.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_unavailable</t>
+          <t>chat_ui.inventory_remove_invalid_item</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Inventory is unavailable.</t>
+          <t>This item is not valid.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_not_player</t>
+          <t>chat_ui.inventory_remove_unavailable</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>You can only delete items from your own inventory.</t>
+          <t>Inventory is unavailable.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
+          <t>chat_ui.inventory_remove_not_player</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Equipped items cannot be deleted directly.</t>
+          <t>You can only delete items from your own inventory.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_failed</t>
+          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Failed to delete the item.</t>
+          <t>Equipped items cannot be deleted directly.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_default_failed</t>
+          <t>chat_ui.inventory_remove_failed</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Could not delete the item.</t>
+          <t>Failed to delete the item.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>chat_ui.shop_buy_success</t>
+          <t>chat_ui.inventory_remove_default_failed</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Purchased {0}.</t>
+          <t>Could not delete the item.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>chat_ui.shop_sell_success</t>
+          <t>chat_ui.shop_buy_success</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sold {0}.</t>
+          <t>Purchased {0}.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>chat_ui.shop_not_enough_gold</t>
+          <t>chat_ui.shop_sell_success</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Not enough credits to purchase {0}.</t>
+          <t>Sold {0}.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>chat_ui.shop_no_space_buy</t>
+          <t>chat_ui.shop_not_enough_gold</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>No space in your inventory.</t>
+          <t>Not enough credits to purchase {0}.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>chat_ui.shop_no_space_sell</t>
+          <t>chat_ui.shop_no_space_buy</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>No space in the shop to place the item for sale.</t>
+          <t>No space in your inventory.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>chat_ui.shop_invalid_item</t>
+          <t>chat_ui.shop_no_space_sell</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>This item is not valid.</t>
+          <t>No space in the shop to place the item for sale.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>chat_ui.shop_transfer_failed</t>
+          <t>chat_ui.shop_invalid_item</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>The trade failed while moving {0}.</t>
+          <t>This item is not valid.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>chat_ui.shop_stock_update_failed</t>
+          <t>chat_ui.shop_transfer_failed</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Failed to update stock for {0}.</t>
+          <t>The trade failed while moving {0}.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>chat_ui.shop_failed</t>
+          <t>chat_ui.shop_stock_update_failed</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Failed to process the trade.</t>
+          <t>Failed to update stock for {0}.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>chat_ui.pickup_default</t>
+          <t>chat_ui.shop_failed</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Obtained the item.</t>
+          <t>Failed to process the trade.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>chat_ui.out_of_range</t>
+          <t>chat_ui.pickup_default</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Please move closer to the item.</t>
+          <t>Obtained the item.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>chat_ui.already_claimed</t>
+          <t>chat_ui.out_of_range</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>This item has already been claimed.</t>
+          <t>Please move closer to the item.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>chat_ui.pickup_unavailable</t>
+          <t>chat_ui.already_claimed</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>This item can no longer be obtained.</t>
+          <t>This item has already been claimed.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>chat_ui.item_unavailable</t>
+          <t>chat_ui.pickup_unavailable</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>The target item could not be found.</t>
+          <t>This item can no longer be obtained.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>chat_ui.stale_revision</t>
+          <t>chat_ui.item_unavailable</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>The item's state has changed. Please try again.</t>
+          <t>The target item could not be found.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>chat_ui.recovery_failed</t>
+          <t>chat_ui.stale_revision</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Failed to drop the item and restore the inventory. Please check your inventory.</t>
+          <t>The item's state has changed. Please try again.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>chat_ui.upgrade_process_failed</t>
+          <t>chat_ui.recovery_failed</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Failed to process the upgrade. Please try again.</t>
+          <t>Failed to drop the item and restore the inventory. Please check your inventory.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>chat_ui.drop_failed</t>
+          <t>chat_ui.upgrade_process_failed</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Failed to drop the item on the field. Please try again.</t>
+          <t>Failed to process the upgrade. Please try again.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>chat_ui.acquisition_failed</t>
+          <t>chat_ui.drop_failed</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Failed to obtain the item. Please try again.</t>
+          <t>Failed to drop the item on the field. Please try again.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>chat_ui.shop_state_changed</t>
+          <t>chat_ui.acquisition_failed</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>The shop's state has changed. Please select again.</t>
+          <t>Failed to obtain the item. Please try again.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_state_changed</t>
+          <t>chat_ui.shop_state_changed</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>The inventory's state has changed. Please try again.</t>
+          <t>The shop's state has changed. Please select again.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>chat_ui.trade_failed</t>
+          <t>chat_ui.inventory_state_changed</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Failed to process the trade. Please try again.</t>
+          <t>The inventory's state has changed. Please try again.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>loading_ui.tooltip_title</t>
+          <t>chat_ui.trade_failed</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Debris-9</t>
+          <t>Failed to process the trade. Please try again.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>loading_ui.tooltip_content</t>
+          <t>loading_ui.tooltip_title</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>This place was once an abandoned land, uninhabitable due to contamination, but as centuries of accumulated robot wreckage began to repair and modify itself, a bizarre mechanical ecosystem was born.</t>
+          <t>Debris-9</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>common_ui.yes</t>
+          <t>loading_ui.tooltip_content</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>This place was once an abandoned land, uninhabitable due to contamination, but as centuries of accumulated robot wreckage began to repair and modify itself, a bizarre mechanical ecosystem was born.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>common_ui.confirm</t>
+          <t>common_ui.yes</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>chat_ui.panel_title</t>
+          <t>common_ui.confirm</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>chat_ui.input_placeholder</t>
+          <t>chat_ui.panel_title</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Enter message…</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>chat_ui.connect_hint</t>
+          <t>chat_ui.input_placeholder</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>You can chat after connecting</t>
+          <t>Enter message…</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>chat_ui.unread_indicator</t>
+          <t>chat_ui.connect_hint</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>New message ↓</t>
+          <t>You can chat after connecting</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.title</t>
+          <t>chat_ui.unread_indicator</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Skill Evolution &amp; Enhancement Settings</t>
+          <t>New message ↓</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.hint</t>
+          <t>skill_evolution_ui.title</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Press K to open/close - Left button: Evolution (None→Evo1→2→3), Right button: Enhancement (None→Enh1→2→3)</t>
+          <t>Skill Evolution &amp; Enhancement Settings</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.none</t>
+          <t>skill_evolution_ui.hint</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Press K to open/close - Left button: Evolution (None→Evo1→2→3), Right button: Enhancement (None→Enh1→2→3)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>passive_skill_ui.title</t>
+          <t>skill_evolution_ui.none</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Passive Upgrade</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>passive_skill_ui.skill_clear</t>
+          <t>passive_skill_ui.title</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>Passive Upgrade</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>passive_skill_ui.skill_points</t>
+          <t>passive_skill_ui.skill_clear</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Skill Points -</t>
+          <t>Reset</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>passive_skill_ui.credit_format</t>
+          <t>passive_skill_ui.skill_points</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Credit | {0}</t>
+          <t>Skill Points -</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>passive_skill_ui.credit_none</t>
+          <t>passive_skill_ui.credit_format</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Credit | -</t>
+          <t>Credit | {0}</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>passive_skill_ui.profile_loading</t>
+          <t>passive_skill_ui.credit_none</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Loading Profile</t>
+          <t>Credit | -</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>passive_skill_ui.confirm_ok</t>
+          <t>passive_skill_ui.profile_loading</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Loading Profile</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_current_level</t>
+          <t>passive_skill_ui.confirm_ok</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Current Lv: {0} / {1}</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_current_effect</t>
+          <t>passive_skill_ui.detail_current_level</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Current Effect: {0}</t>
+          <t>Current Lv: {0} / {1}</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_next_level</t>
+          <t>passive_skill_ui.detail_current_effect</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Next Lv: {0}</t>
+          <t>Current Effect: {0}</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>common_ui.cancel</t>
+          <t>passive_skill_ui.detail_next_level</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Next Lv: {0}</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rest_ui.header</t>
+          <t>common_ui.cancel</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Rest</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>rest_ui.header</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Rest</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>rest_ui.description</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>Spend credits to
 take a rest?</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>rest_ui.health_recovery</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Restore 25% HP</t>
-        </is>
-      </c>
-    </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rest_ui.potion_recharge</t>
+          <t>rest_ui.health_recovery</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Potion Charges</t>
+          <t>Restore 25% HP</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rest_ui.cost_format</t>
+          <t>rest_ui.potion_recharge</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Required Credits : {0}</t>
+          <t>Potion Charges</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rest_ui.complete_message</t>
+          <t>rest_ui.cost_format</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Spent {0} credits to restore {1} HP and {2} potion charge(s).</t>
+          <t>Required Credits : {0}</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_chat</t>
+          <t>rest_ui.complete_message</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Chat] </t>
+          <t>Spent {0} credits to restore {1} HP and {2} potion charge(s).</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_acquisition</t>
+          <t>chat_ui.prefix_chat</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Item] </t>
+          <t xml:space="preserve">[Chat] </t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_warning</t>
+          <t>chat_ui.prefix_acquisition</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Notice] </t>
+          <t xml:space="preserve">[Item] </t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_connection</t>
+          <t>chat_ui.prefix_warning</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Network] </t>
+          <t xml:space="preserve">[Notice] </t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>chat_ui.item_fallback_name</t>
+          <t>chat_ui.prefix_connection</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>item</t>
+          <t xml:space="preserve">[Network] </t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_cost_format</t>
+          <t>chat_ui.item_fallback_name</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Reroll &lt;color=#FFEB04&gt;{0}&lt;/color&gt;</t>
+          <t>item</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_free</t>
+          <t>shop_ui.reroll_cost_format</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Free Reroll</t>
+          <t>Reroll &lt;color=#FFEB04&gt;{0}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_count_format</t>
+          <t>shop_ui.reroll_free</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[ {0} ]</t>
+          <t>Free Reroll</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>settings_ui.reset_confirm</t>
+          <t>shop_ui.reroll_count_format</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Reset all settings to their defaults?</t>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>settings_ui.reset_warning</t>
+          <t>settings_ui.reset_confirm</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>All current settings will be restored to their defaults.</t>
+          <t>Reset all settings to their defaults?</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_confirm</t>
+          <t>settings_ui.reset_warning</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Give up this game?</t>
+          <t>All current settings will be restored to their defaults.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_warning</t>
+          <t>pause_ui.giveup_confirm</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Warning: Your current game data will be lost.</t>
+          <t>Give up this game?</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm</t>
+          <t>pause_ui.giveup_warning</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Are you sure you want to give up?</t>
+          <t>Warning: Your current game data will be lost.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm_warning</t>
+          <t>pause_ui.giveup_reconfirm</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>The current run will be reset and no credits will be earned.</t>
+          <t>Are you sure you want to give up?</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>pause_ui.save_and_quit_confirm</t>
+          <t>pause_ui.giveup_reconfirm_warning</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Save and quit the game?</t>
+          <t>The current run will be reset and no credits will be earned.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_confirm</t>
+          <t>pause_ui.save_and_quit_confirm</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>End the host session?</t>
+          <t>Save and quit the game?</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_warning</t>
+          <t>pause_ui.host_end_confirm</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>All participants will be disconnected and the current run will end.</t>
+          <t>End the host session?</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>pause_ui.leave_confirm</t>
+          <t>pause_ui.host_end_warning</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Leave this session?</t>
+          <t>All participants will be disconnected and the current run will end.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>pause_ui.leave_warning</t>
+          <t>pause_ui.leave_confirm</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>You will give up your spot and cannot rejoin this run.</t>
+          <t>Leave this session?</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_confirm</t>
+          <t>pause_ui.leave_warning</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Step out of the session for now?</t>
+          <t>You will give up your spot and cannot rejoin this run.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_warning</t>
+          <t>pause_ui.temp_leave_confirm</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>You can rejoin within 5 minutes while the server is running. The party's game will continue.</t>
+          <t>Step out of the session for now?</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>pause_ui.adjustment</t>
+          <t>pause_ui.temp_leave_warning</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Settle &amp; End Run</t>
+          <t>You can rejoin within 5 minutes while the server is running. The party's game will continue.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>pause_ui.settle_confirm</t>
+          <t>pause_ui.adjustment</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Settle and end the game?</t>
+          <t>Settle &amp; End Run</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>pause_ui.settle_confirm</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Settle and end the game?</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
           <t>pause_ui.settle_warning</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>You will receive your credits plus 50% of your items' base value as account credits, and the current run will be reset.</t>
         </is>
@@ -4886,7 +4910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5660,1451 +5684,1463 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>status_ui.header</t>
+          <t>skill_ui.arc_laser_name</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>アークレーザー</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>status_ui.detail_toggle</t>
+          <t>status_ui.header</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>詳細ステータス表示</t>
+          <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>status_ui.type_header</t>
+          <t>status_ui.detail_toggle</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TYPE</t>
+          <t>詳細ステータス表示</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>shop_ui.header</t>
+          <t>status_ui.type_header</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ショップ</t>
+          <t>TYPE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>inventory_ui.header</t>
+          <t>shop_ui.header</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>インベントリ</t>
+          <t>ショップ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>upgrade_ui.header</t>
+          <t>inventory_ui.header</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>強化</t>
+          <t>インベントリ</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>item_tooltip_ui.sub_option_label</t>
+          <t>upgrade_ui.header</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>追加オプション</t>
+          <t>強化</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>item_tooltip_ui.unique_effect_label</t>
+          <t>item_tooltip_ui.sub_option_label</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>固有効果</t>
+          <t>追加オプション</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>upgrade_ui.current_stat</t>
+          <t>item_tooltip_ui.unique_effect_label</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>現在ステータス：{0} + {1}</t>
+          <t>固有効果</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>upgrade_ui.next_stat</t>
+          <t>upgrade_ui.current_stat</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>強化後ステータス：{0} + {1}</t>
+          <t>現在ステータス：{0} + {1}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>upgrade_ui.cost</t>
+          <t>upgrade_ui.next_stat</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>強化費用：{0}</t>
+          <t>強化後ステータス：{0} + {1}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>upgrade_ui.cost_unavailable</t>
+          <t>upgrade_ui.cost</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>強化費用：-</t>
+          <t>強化費用：{0}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>upgrade_ui.unknown_item</t>
+          <t>upgrade_ui.cost_unavailable</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>アイテム</t>
+          <t>強化費用：-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>upgrade_ui.selection_required</t>
+          <t>upgrade_ui.unknown_item</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>強化するアイテムを選択してください。</t>
+          <t>アイテム</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_success</t>
+          <t>upgrade_ui.selection_required</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{0} +{1} 強化成功</t>
+          <t>強化するアイテムを選択してください。</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_not_enough_gold</t>
+          <t>upgrade_ui.result_success</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>クレジットが不足しています。</t>
+          <t>{0} +{1} 強化成功</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_invalid_item</t>
+          <t>upgrade_ui.result_not_enough_gold</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>強化できないアイテムです。</t>
+          <t>クレジットが不足しています。</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_invalid_cost</t>
+          <t>upgrade_ui.result_invalid_item</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>強化費用の設定が正しくありません。</t>
+          <t>強化できないアイテムです。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_wallet_unavailable</t>
+          <t>upgrade_ui.result_invalid_cost</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>強化処理中に問題が発生しました。</t>
+          <t>強化費用の設定が正しくありません。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_failed</t>
+          <t>upgrade_ui.result_wallet_unavailable</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>強化に失敗しました。</t>
+          <t>強化処理中に問題が発生しました。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>npc_ui.quest</t>
+          <t>upgrade_ui.result_failed</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>依頼</t>
+          <t>強化に失敗しました。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>npc_ui.rest</t>
+          <t>npc_ui.quest</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>休憩</t>
+          <t>依頼</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>chat_ui.equip_success</t>
+          <t>npc_ui.rest</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>装備処理が完了しました。</t>
+          <t>休憩</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>chat_ui.equip_swapped</t>
+          <t>chat_ui.equip_success</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>装備を交換しました。</t>
+          <t>装備処理が完了しました。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>chat_ui.equip_invalid_item</t>
+          <t>chat_ui.equip_swapped</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>装備できないアイテムです。</t>
+          <t>装備を交換しました。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>chat_ui.equip_invalid_slot</t>
+          <t>chat_ui.equip_invalid_item</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>そのスロットには装備できません。</t>
+          <t>装備できないアイテムです。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>chat_ui.equip_slot_occupied</t>
+          <t>chat_ui.equip_invalid_slot</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>すでに装備が装着されています。</t>
+          <t>そのスロットには装備できません。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>chat_ui.equip_not_equipped</t>
+          <t>chat_ui.equip_slot_occupied</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>解除する装備がありません。</t>
+          <t>すでに装備が装着されています。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>chat_ui.equip_no_return_space</t>
+          <t>chat_ui.equip_not_equipped</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>既存の装備をインベントリに置くスペースがありません。</t>
+          <t>解除する装備がありません。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>chat_ui.equip_failed</t>
+          <t>chat_ui.equip_no_return_space</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>装備処理に失敗しました。</t>
+          <t>既存の装備をインベントリに置くスペースがありません。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>chat_ui.equip_wrong_class</t>
+          <t>chat_ui.equip_failed</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>このキャラクターは装備できない武器です。</t>
+          <t>装備処理に失敗しました。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>chat_ui.equip_unknown</t>
+          <t>chat_ui.equip_wrong_class</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>不明な装備処理結果です。</t>
+          <t>このキャラクターは装備できない武器です。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_acquisition</t>
+          <t>chat_ui.equip_unknown</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{0}アイテムを獲得しました。</t>
+          <t>不明な装備処理結果です。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_acquisition_colored</t>
+          <t>chat_ui.inventory_acquisition</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{0}を獲得しました。</t>
+          <t>{0}アイテムを獲得しました。</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_success_position</t>
+          <t>chat_ui.inventory_acquisition_colored</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{0} 位置：{1}, {2}</t>
+          <t>{0}を獲得しました。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_invalid_item</t>
+          <t>chat_ui.inventory_success_position</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>無効なアイテムです。</t>
+          <t>{0} 位置：{1}, {2}</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_no_space</t>
+          <t>chat_ui.inventory_invalid_item</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>インベントリが満杯です！</t>
+          <t>無効なアイテムです。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_grid_unavailable</t>
+          <t>chat_ui.inventory_no_space</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>インベントリを使用できません。</t>
+          <t>インベントリが満杯です！</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_placement_failed</t>
+          <t>chat_ui.inventory_grid_unavailable</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>インベントリにアイテムを配置できませんでした。</t>
+          <t>インベントリを使用できません。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_add_failed</t>
+          <t>chat_ui.inventory_placement_failed</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>アイテムの獲得に失敗しました。</t>
+          <t>インベントリにアイテムを配置できませんでした。</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_success</t>
+          <t>chat_ui.inventory_add_failed</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{0}を削除しました。</t>
+          <t>アイテムの獲得に失敗しました。</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_invalid_item</t>
+          <t>chat_ui.inventory_remove_success</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>無効なアイテムです。</t>
+          <t>{0}を削除しました。</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_unavailable</t>
+          <t>chat_ui.inventory_remove_invalid_item</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>インベントリを使用できません。</t>
+          <t>無効なアイテムです。</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_not_player</t>
+          <t>chat_ui.inventory_remove_unavailable</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>自分のインベントリのアイテムのみ削除できます。</t>
+          <t>インベントリを使用できません。</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
+          <t>chat_ui.inventory_remove_not_player</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>装備中のアイテムは直接削除できません。</t>
+          <t>自分のインベントリのアイテムのみ削除できます。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_failed</t>
+          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>アイテムの削除に失敗しました。</t>
+          <t>装備中のアイテムは直接削除できません。</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_default_failed</t>
+          <t>chat_ui.inventory_remove_failed</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>アイテムを削除できませんでした。</t>
+          <t>アイテムの削除に失敗しました。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>chat_ui.shop_buy_success</t>
+          <t>chat_ui.inventory_remove_default_failed</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{0}を購入しました。</t>
+          <t>アイテムを削除できませんでした。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>chat_ui.shop_sell_success</t>
+          <t>chat_ui.shop_buy_success</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{0}を売却しました。</t>
+          <t>{0}を購入しました。</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>chat_ui.shop_not_enough_gold</t>
+          <t>chat_ui.shop_sell_success</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>クレジットが不足しているため{0}の購入に失敗しました。</t>
+          <t>{0}を売却しました。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>chat_ui.shop_no_space_buy</t>
+          <t>chat_ui.shop_not_enough_gold</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>インベントリに空きがありません。</t>
+          <t>クレジットが不足しているため{0}の購入に失敗しました。</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>chat_ui.shop_no_space_sell</t>
+          <t>chat_ui.shop_no_space_buy</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ショップに販売アイテムを置くスペースがありません。</t>
+          <t>インベントリに空きがありません。</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>chat_ui.shop_invalid_item</t>
+          <t>chat_ui.shop_no_space_sell</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>無効なアイテムです。</t>
+          <t>ショップに販売アイテムを置くスペースがありません。</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>chat_ui.shop_transfer_failed</t>
+          <t>chat_ui.shop_invalid_item</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>{0}の移動中に取引に失敗しました。</t>
+          <t>無効なアイテムです。</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>chat_ui.shop_stock_update_failed</t>
+          <t>chat_ui.shop_transfer_failed</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{0}の在庫処理に失敗しました。</t>
+          <t>{0}の移動中に取引に失敗しました。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>chat_ui.shop_failed</t>
+          <t>chat_ui.shop_stock_update_failed</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>取引処理に失敗しました。</t>
+          <t>{0}の在庫処理に失敗しました。</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>chat_ui.pickup_default</t>
+          <t>chat_ui.shop_failed</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>アイテムを獲得しました。</t>
+          <t>取引処理に失敗しました。</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>chat_ui.out_of_range</t>
+          <t>chat_ui.pickup_default</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>アイテムにもっと近づいてください。</t>
+          <t>アイテムを獲得しました。</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>chat_ui.already_claimed</t>
+          <t>chat_ui.out_of_range</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>すでに獲得済みのアイテムです。</t>
+          <t>アイテムにもっと近づいてください。</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>chat_ui.pickup_unavailable</t>
+          <t>chat_ui.already_claimed</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>これ以上獲得できないアイテムです。</t>
+          <t>すでに獲得済みのアイテムです。</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>chat_ui.item_unavailable</t>
+          <t>chat_ui.pickup_unavailable</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>対象のアイテムが見つかりません。</t>
+          <t>これ以上獲得できないアイテムです。</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>chat_ui.stale_revision</t>
+          <t>chat_ui.item_unavailable</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>アイテムの状態が変わりました。もう一度お試しください。</t>
+          <t>対象のアイテムが見つかりません。</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>chat_ui.recovery_failed</t>
+          <t>chat_ui.stale_revision</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>アイテムのドロップとインベントリの復元に失敗しました。インベントリの状態を確認してください。</t>
+          <t>アイテムの状態が変わりました。もう一度お試しください。</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>chat_ui.upgrade_process_failed</t>
+          <t>chat_ui.recovery_failed</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>強化を処理できませんでした。もう一度お試しください。</t>
+          <t>アイテムのドロップとインベントリの復元に失敗しました。インベントリの状態を確認してください。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>chat_ui.drop_failed</t>
+          <t>chat_ui.upgrade_process_failed</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>アイテムをフィールドに置けませんでした。もう一度お試しください。</t>
+          <t>強化を処理できませんでした。もう一度お試しください。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>chat_ui.acquisition_failed</t>
+          <t>chat_ui.drop_failed</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>アイテムを獲得できませんでした。もう一度お試しください。</t>
+          <t>アイテムをフィールドに置けませんでした。もう一度お試しください。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>chat_ui.shop_state_changed</t>
+          <t>chat_ui.acquisition_failed</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ショップの状態が変わりました。もう一度選択してください。</t>
+          <t>アイテムを獲得できませんでした。もう一度お試しください。</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_state_changed</t>
+          <t>chat_ui.shop_state_changed</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>インベントリの状態が変わりました。もう一度お試しください。</t>
+          <t>ショップの状態が変わりました。もう一度選択してください。</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>chat_ui.trade_failed</t>
+          <t>chat_ui.inventory_state_changed</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>取引を処理できませんでした。もう一度お試しください。</t>
+          <t>インベントリの状態が変わりました。もう一度お試しください。</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>loading_ui.tooltip_title</t>
+          <t>chat_ui.trade_failed</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>デブリス-9</t>
+          <t>取引を処理できませんでした。もう一度お試しください。</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>loading_ui.tooltip_content</t>
+          <t>loading_ui.tooltip_title</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>この場所は汚染によって人間が住めない廃墟の地でしたが、何百年もの間積み重なったロボットの残骸が自らを修復・改造し始め、奇怪なメカ生態系が生まれました。</t>
+          <t>デブリス-9</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>common_ui.yes</t>
+          <t>loading_ui.tooltip_content</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>はい</t>
+          <t>この場所は汚染によって人間が住めない廃墟の地でしたが、何百年もの間積み重なったロボットの残骸が自らを修復・改造し始め、奇怪なメカ生態系が生まれました。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>common_ui.confirm</t>
+          <t>common_ui.yes</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>確認</t>
+          <t>はい</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>chat_ui.panel_title</t>
+          <t>common_ui.confirm</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>チャット</t>
+          <t>確認</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>chat_ui.input_placeholder</t>
+          <t>chat_ui.panel_title</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>メッセージを入力…</t>
+          <t>チャット</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>chat_ui.connect_hint</t>
+          <t>chat_ui.input_placeholder</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>接続後に会話できます</t>
+          <t>メッセージを入力…</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>chat_ui.unread_indicator</t>
+          <t>chat_ui.connect_hint</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>新着メッセージ ↓</t>
+          <t>接続後に会話できます</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.title</t>
+          <t>chat_ui.unread_indicator</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>スキル進化・強化設定</t>
+          <t>新着メッセージ ↓</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.hint</t>
+          <t>skill_evolution_ui.title</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Kで開閉 - 左ボタン：進化（なし→進化1→2→3）、右ボタン：強化（なし→強化1→2→3）</t>
+          <t>スキル進化・強化設定</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.none</t>
+          <t>skill_evolution_ui.hint</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>Kで開閉 - 左ボタン：進化（なし→進化1→2→3）、右ボタン：強化（なし→強化1→2→3）</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>passive_skill_ui.title</t>
+          <t>skill_evolution_ui.none</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>パッシブアップグレード</t>
+          <t>なし</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>passive_skill_ui.skill_clear</t>
+          <t>passive_skill_ui.title</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>リセット</t>
+          <t>パッシブアップグレード</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>passive_skill_ui.skill_points</t>
+          <t>passive_skill_ui.skill_clear</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>スキルポイント -</t>
+          <t>リセット</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>passive_skill_ui.credit_format</t>
+          <t>passive_skill_ui.skill_points</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>クレジット | {0}</t>
+          <t>スキルポイント -</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>passive_skill_ui.credit_none</t>
+          <t>passive_skill_ui.credit_format</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>クレジット | -</t>
+          <t>クレジット | {0}</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>passive_skill_ui.profile_loading</t>
+          <t>passive_skill_ui.credit_none</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>プロフィール準備中</t>
+          <t>クレジット | -</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>passive_skill_ui.confirm_ok</t>
+          <t>passive_skill_ui.profile_loading</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>プロフィール準備中</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_current_level</t>
+          <t>passive_skill_ui.confirm_ok</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>現在レベル: {0} / {1}</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_current_effect</t>
+          <t>passive_skill_ui.detail_current_level</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>現在効果: {0}</t>
+          <t>現在レベル: {0} / {1}</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_next_level</t>
+          <t>passive_skill_ui.detail_current_effect</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>次レベル: {0}</t>
+          <t>現在効果: {0}</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>common_ui.cancel</t>
+          <t>passive_skill_ui.detail_next_level</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>次レベル: {0}</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rest_ui.header</t>
+          <t>common_ui.cancel</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>休息</t>
+          <t>キャンセル</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>rest_ui.header</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>休息</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>rest_ui.description</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>クレジットを支払って
 休息しますか？</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>rest_ui.health_recovery</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>体力25%回復</t>
-        </is>
-      </c>
-    </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rest_ui.potion_recharge</t>
+          <t>rest_ui.health_recovery</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ポーション補充</t>
+          <t>体力25%回復</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rest_ui.cost_format</t>
+          <t>rest_ui.potion_recharge</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>必要クレジット : {0}</t>
+          <t>ポーション補充</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rest_ui.complete_message</t>
+          <t>rest_ui.cost_format</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>{0}クレジットを消費して体力{1}、ポーション{2}個を補充しました。</t>
+          <t>必要クレジット : {0}</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_chat</t>
+          <t>rest_ui.complete_message</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">[チャット] </t>
+          <t>{0}クレジットを消費して体力{1}、ポーション{2}個を補充しました。</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_acquisition</t>
+          <t>chat_ui.prefix_chat</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">[アイテム] </t>
+          <t xml:space="preserve">[チャット] </t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_warning</t>
+          <t>chat_ui.prefix_acquisition</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">[お知らせ] </t>
+          <t xml:space="preserve">[アイテム] </t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_connection</t>
+          <t>chat_ui.prefix_warning</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">[接続] </t>
+          <t xml:space="preserve">[お知らせ] </t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>chat_ui.item_fallback_name</t>
+          <t>chat_ui.prefix_connection</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>アイテム</t>
+          <t xml:space="preserve">[接続] </t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_cost_format</t>
+          <t>chat_ui.item_fallback_name</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 再抽選</t>
+          <t>アイテム</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_free</t>
+          <t>shop_ui.reroll_cost_format</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>無料 再抽選</t>
+          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 再抽選</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_count_format</t>
+          <t>shop_ui.reroll_free</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[ {0} ]</t>
+          <t>無料 再抽選</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>settings_ui.reset_confirm</t>
+          <t>shop_ui.reroll_count_format</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>設定を初期値に戻しますか？</t>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>settings_ui.reset_warning</t>
+          <t>settings_ui.reset_confirm</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>現在の設定はすべて初期値に戻ります。</t>
+          <t>設定を初期値に戻しますか？</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_confirm</t>
+          <t>settings_ui.reset_warning</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>ゲームをあきらめますか？</t>
+          <t>現在の設定はすべて初期値に戻ります。</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_warning</t>
+          <t>pause_ui.giveup_confirm</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>警告：現在のゲームデータは失われます。</t>
+          <t>ゲームをあきらめますか？</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm</t>
+          <t>pause_ui.giveup_warning</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>本当に諦めますか？</t>
+          <t>警告：現在のゲームデータは失われます。</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm_warning</t>
+          <t>pause_ui.giveup_reconfirm</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>進行中の遠征はリセットされ、クレジットは獲得できません。</t>
+          <t>本当に諦めますか？</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>pause_ui.save_and_quit_confirm</t>
+          <t>pause_ui.giveup_reconfirm_warning</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ゲームを保存して終了しますか？</t>
+          <t>進行中の遠征はリセットされ、クレジットは獲得できません。</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_confirm</t>
+          <t>pause_ui.save_and_quit_confirm</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ホストセッションを終了しますか？</t>
+          <t>ゲームを保存して終了しますか？</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_warning</t>
+          <t>pause_ui.host_end_confirm</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>すべての参加者の接続と現在のランが終了します。</t>
+          <t>ホストセッションを終了しますか？</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>pause_ui.leave_confirm</t>
+          <t>pause_ui.host_end_warning</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>このセッションから退出しますか？</t>
+          <t>すべての参加者の接続と現在のランが終了します。</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>pause_ui.leave_warning</t>
+          <t>pause_ui.leave_confirm</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>参加資格を放棄し、このランには再接続できません。</t>
+          <t>このセッションから退出しますか？</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_confirm</t>
+          <t>pause_ui.leave_warning</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>一時的にセッションから退出しますか？</t>
+          <t>参加資格を放棄し、このランには再接続できません。</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_warning</t>
+          <t>pause_ui.temp_leave_confirm</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>サーバーが維持されている間は5分以内に再接続できます。パーティーのゲームは続行されます。</t>
+          <t>一時的にセッションから退出しますか？</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>pause_ui.adjustment</t>
+          <t>pause_ui.temp_leave_warning</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>精算して終了</t>
+          <t>サーバーが維持されている間は5分以内に再接続できます。パーティーのゲームは続行されます。</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>pause_ui.settle_confirm</t>
+          <t>pause_ui.adjustment</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>精算してゲームを終了しますか？</t>
+          <t>精算して終了</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>pause_ui.settle_confirm</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>精算してゲームを終了しますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
           <t>pause_ui.settle_warning</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>所持クレジットとアイテム原価の50%をアカウントクレジットとして受け取り、現在の遠征はリセットされます。</t>
         </is>
@@ -7121,7 +7157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B185"/>
+  <dimension ref="A1:B186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7895,1451 +7931,1463 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>status_ui.header</t>
+          <t>skill_ui.arc_laser_name</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>电弧激光</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>status_ui.detail_toggle</t>
+          <t>status_ui.header</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>显示详细属性</t>
+          <t>STATUS</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>status_ui.type_header</t>
+          <t>status_ui.detail_toggle</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TYPE</t>
+          <t>显示详细属性</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>shop_ui.header</t>
+          <t>status_ui.type_header</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>商店</t>
+          <t>TYPE</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>inventory_ui.header</t>
+          <t>shop_ui.header</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>物品栏</t>
+          <t>商店</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>upgrade_ui.header</t>
+          <t>inventory_ui.header</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>强化</t>
+          <t>物品栏</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>item_tooltip_ui.sub_option_label</t>
+          <t>upgrade_ui.header</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>附加选项</t>
+          <t>强化</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>item_tooltip_ui.unique_effect_label</t>
+          <t>item_tooltip_ui.sub_option_label</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>固有效果</t>
+          <t>附加选项</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>upgrade_ui.current_stat</t>
+          <t>item_tooltip_ui.unique_effect_label</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>当前属性：{0} + {1}</t>
+          <t>固有效果</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>upgrade_ui.next_stat</t>
+          <t>upgrade_ui.current_stat</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>强化后属性：{0} + {1}</t>
+          <t>当前属性：{0} + {1}</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>upgrade_ui.cost</t>
+          <t>upgrade_ui.next_stat</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>强化费用：{0}</t>
+          <t>强化后属性：{0} + {1}</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>upgrade_ui.cost_unavailable</t>
+          <t>upgrade_ui.cost</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>强化费用：-</t>
+          <t>强化费用：{0}</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>upgrade_ui.unknown_item</t>
+          <t>upgrade_ui.cost_unavailable</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>物品</t>
+          <t>强化费用：-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>upgrade_ui.selection_required</t>
+          <t>upgrade_ui.unknown_item</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>请选择要强化的物品。</t>
+          <t>物品</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_success</t>
+          <t>upgrade_ui.selection_required</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{0} +{1} 强化成功</t>
+          <t>请选择要强化的物品。</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_not_enough_gold</t>
+          <t>upgrade_ui.result_success</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>信用点不足。</t>
+          <t>{0} +{1} 强化成功</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_invalid_item</t>
+          <t>upgrade_ui.result_not_enough_gold</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>该物品无法强化。</t>
+          <t>信用点不足。</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_invalid_cost</t>
+          <t>upgrade_ui.result_invalid_item</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>强化费用设置不正确。</t>
+          <t>该物品无法强化。</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_wallet_unavailable</t>
+          <t>upgrade_ui.result_invalid_cost</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>强化处理过程中发生了问题。</t>
+          <t>强化费用设置不正确。</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>upgrade_ui.result_failed</t>
+          <t>upgrade_ui.result_wallet_unavailable</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>强化失败。</t>
+          <t>强化处理过程中发生了问题。</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>npc_ui.quest</t>
+          <t>upgrade_ui.result_failed</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>委托</t>
+          <t>强化失败。</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>npc_ui.rest</t>
+          <t>npc_ui.quest</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>休息</t>
+          <t>委托</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>chat_ui.equip_success</t>
+          <t>npc_ui.rest</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>装备处理已完成。</t>
+          <t>休息</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>chat_ui.equip_swapped</t>
+          <t>chat_ui.equip_success</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>已更换装备。</t>
+          <t>装备处理已完成。</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>chat_ui.equip_invalid_item</t>
+          <t>chat_ui.equip_swapped</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>该物品无法装备。</t>
+          <t>已更换装备。</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>chat_ui.equip_invalid_slot</t>
+          <t>chat_ui.equip_invalid_item</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>无法装备到该栏位。</t>
+          <t>该物品无法装备。</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>chat_ui.equip_slot_occupied</t>
+          <t>chat_ui.equip_invalid_slot</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>该位置已装备物品。</t>
+          <t>无法装备到该栏位。</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>chat_ui.equip_not_equipped</t>
+          <t>chat_ui.equip_slot_occupied</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>没有可卸下的装备。</t>
+          <t>该位置已装备物品。</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>chat_ui.equip_no_return_space</t>
+          <t>chat_ui.equip_not_equipped</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>背包中没有空间放置原有装备。</t>
+          <t>没有可卸下的装备。</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>chat_ui.equip_failed</t>
+          <t>chat_ui.equip_no_return_space</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>装备处理失败。</t>
+          <t>背包中没有空间放置原有装备。</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>chat_ui.equip_wrong_class</t>
+          <t>chat_ui.equip_failed</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>该角色无法装备此武器。</t>
+          <t>装备处理失败。</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>chat_ui.equip_unknown</t>
+          <t>chat_ui.equip_wrong_class</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>未知的装备处理结果。</t>
+          <t>该角色无法装备此武器。</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_acquisition</t>
+          <t>chat_ui.equip_unknown</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>获得了物品：{0}。</t>
+          <t>未知的装备处理结果。</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_acquisition_colored</t>
+          <t>chat_ui.inventory_acquisition</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>获得了{0}。</t>
+          <t>获得了物品：{0}。</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_success_position</t>
+          <t>chat_ui.inventory_acquisition_colored</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{0} 位置：{1}, {2}</t>
+          <t>获得了{0}。</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_invalid_item</t>
+          <t>chat_ui.inventory_success_position</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>无效的物品。</t>
+          <t>{0} 位置：{1}, {2}</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_no_space</t>
+          <t>chat_ui.inventory_invalid_item</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>背包已满！</t>
+          <t>无效的物品。</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_grid_unavailable</t>
+          <t>chat_ui.inventory_no_space</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>无法使用背包。</t>
+          <t>背包已满！</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_placement_failed</t>
+          <t>chat_ui.inventory_grid_unavailable</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>未能将物品放入背包。</t>
+          <t>无法使用背包。</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_add_failed</t>
+          <t>chat_ui.inventory_placement_failed</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>获取物品失败。</t>
+          <t>未能将物品放入背包。</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_success</t>
+          <t>chat_ui.inventory_add_failed</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>已删除{0}。</t>
+          <t>获取物品失败。</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_invalid_item</t>
+          <t>chat_ui.inventory_remove_success</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>无效的物品。</t>
+          <t>已删除{0}。</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_unavailable</t>
+          <t>chat_ui.inventory_remove_invalid_item</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>无法使用背包。</t>
+          <t>无效的物品。</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_not_player</t>
+          <t>chat_ui.inventory_remove_unavailable</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>只能删除自己背包中的物品。</t>
+          <t>无法使用背包。</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
+          <t>chat_ui.inventory_remove_not_player</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>已装备的物品无法直接删除。</t>
+          <t>只能删除自己背包中的物品。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_failed</t>
+          <t>chat_ui.inventory_remove_equipped_not_allowed</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>删除物品失败。</t>
+          <t>已装备的物品无法直接删除。</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_remove_default_failed</t>
+          <t>chat_ui.inventory_remove_failed</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>无法删除物品。</t>
+          <t>删除物品失败。</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>chat_ui.shop_buy_success</t>
+          <t>chat_ui.inventory_remove_default_failed</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>已购买{0}。</t>
+          <t>无法删除物品。</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>chat_ui.shop_sell_success</t>
+          <t>chat_ui.shop_buy_success</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>已出售{0}。</t>
+          <t>已购买{0}。</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>chat_ui.shop_not_enough_gold</t>
+          <t>chat_ui.shop_sell_success</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>信用点不足，购买{0}失败。</t>
+          <t>已出售{0}。</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>chat_ui.shop_no_space_buy</t>
+          <t>chat_ui.shop_not_enough_gold</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>背包中没有空间。</t>
+          <t>信用点不足，购买{0}失败。</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>chat_ui.shop_no_space_sell</t>
+          <t>chat_ui.shop_no_space_buy</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>商店中没有空间放置出售的物品。</t>
+          <t>背包中没有空间。</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>chat_ui.shop_invalid_item</t>
+          <t>chat_ui.shop_no_space_sell</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>无效的物品。</t>
+          <t>商店中没有空间放置出售的物品。</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>chat_ui.shop_transfer_failed</t>
+          <t>chat_ui.shop_invalid_item</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>移动{0}时交易失败。</t>
+          <t>无效的物品。</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>chat_ui.shop_stock_update_failed</t>
+          <t>chat_ui.shop_transfer_failed</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>{0}库存处理失败。</t>
+          <t>移动{0}时交易失败。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>chat_ui.shop_failed</t>
+          <t>chat_ui.shop_stock_update_failed</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>交易处理失败。</t>
+          <t>{0}库存处理失败。</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>chat_ui.pickup_default</t>
+          <t>chat_ui.shop_failed</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>获得了物品。</t>
+          <t>交易处理失败。</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>chat_ui.out_of_range</t>
+          <t>chat_ui.pickup_default</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>请靠近物品。</t>
+          <t>获得了物品。</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>chat_ui.already_claimed</t>
+          <t>chat_ui.out_of_range</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>该物品已被获取。</t>
+          <t>请靠近物品。</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>chat_ui.pickup_unavailable</t>
+          <t>chat_ui.already_claimed</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>该物品无法再获取。</t>
+          <t>该物品已被获取。</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>chat_ui.item_unavailable</t>
+          <t>chat_ui.pickup_unavailable</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>找不到目标物品。</t>
+          <t>该物品无法再获取。</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>chat_ui.stale_revision</t>
+          <t>chat_ui.item_unavailable</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>物品状态已更改，请重试。</t>
+          <t>找不到目标物品。</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>chat_ui.recovery_failed</t>
+          <t>chat_ui.stale_revision</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>物品掉落及背包恢复失败，请检查背包状态。</t>
+          <t>物品状态已更改，请重试。</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>chat_ui.upgrade_process_failed</t>
+          <t>chat_ui.recovery_failed</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>强化处理失败，请重试。</t>
+          <t>物品掉落及背包恢复失败，请检查背包状态。</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>chat_ui.drop_failed</t>
+          <t>chat_ui.upgrade_process_failed</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>未能将物品放置到场地上，请重试。</t>
+          <t>强化处理失败，请重试。</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>chat_ui.acquisition_failed</t>
+          <t>chat_ui.drop_failed</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>获取物品失败，请重试。</t>
+          <t>未能将物品放置到场地上，请重试。</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>chat_ui.shop_state_changed</t>
+          <t>chat_ui.acquisition_failed</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>商店状态已更改，请重新选择。</t>
+          <t>获取物品失败，请重试。</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>chat_ui.inventory_state_changed</t>
+          <t>chat_ui.shop_state_changed</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>背包状态已更改，请重试。</t>
+          <t>商店状态已更改，请重新选择。</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>chat_ui.trade_failed</t>
+          <t>chat_ui.inventory_state_changed</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>交易处理失败，请重试。</t>
+          <t>背包状态已更改，请重试。</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>loading_ui.tooltip_title</t>
+          <t>chat_ui.trade_failed</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>残骸-9</t>
+          <t>交易处理失败，请重试。</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>loading_ui.tooltip_content</t>
+          <t>loading_ui.tooltip_title</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>这里原本是因污染而无法居住的废弃之地，但数百年间堆积的机器人残骸开始自我修复与改造，形成了诡异的机甲生态系统。</t>
+          <t>残骸-9</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>common_ui.yes</t>
+          <t>loading_ui.tooltip_content</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>这里原本是因污染而无法居住的废弃之地，但数百年间堆积的机器人残骸开始自我修复与改造，形成了诡异的机甲生态系统。</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>common_ui.confirm</t>
+          <t>common_ui.yes</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>确认</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>chat_ui.panel_title</t>
+          <t>common_ui.confirm</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>聊天</t>
+          <t>确认</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>chat_ui.input_placeholder</t>
+          <t>chat_ui.panel_title</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>输入消息…</t>
+          <t>聊天</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>chat_ui.connect_hint</t>
+          <t>chat_ui.input_placeholder</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>连接后可以聊天</t>
+          <t>输入消息…</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>chat_ui.unread_indicator</t>
+          <t>chat_ui.connect_hint</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>新消息 ↓</t>
+          <t>连接后可以聊天</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.title</t>
+          <t>chat_ui.unread_indicator</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>技能进化·强化设置</t>
+          <t>新消息 ↓</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.hint</t>
+          <t>skill_evolution_ui.title</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>按K键开关 - 左键：进化（无→进化1→2→3），右键：强化（无→强化1→2→3）</t>
+          <t>技能进化·强化设置</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>skill_evolution_ui.none</t>
+          <t>skill_evolution_ui.hint</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>按K键开关 - 左键：进化（无→进化1→2→3），右键：强化（无→强化1→2→3）</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>passive_skill_ui.title</t>
+          <t>skill_evolution_ui.none</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>被动升级</t>
+          <t>无</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>passive_skill_ui.skill_clear</t>
+          <t>passive_skill_ui.title</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>重置</t>
+          <t>被动升级</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>passive_skill_ui.skill_points</t>
+          <t>passive_skill_ui.skill_clear</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>技能点 -</t>
+          <t>重置</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>passive_skill_ui.credit_format</t>
+          <t>passive_skill_ui.skill_points</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>点数 | {0}</t>
+          <t>技能点 -</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>passive_skill_ui.credit_none</t>
+          <t>passive_skill_ui.credit_format</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>点数 | -</t>
+          <t>点数 | {0}</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>passive_skill_ui.profile_loading</t>
+          <t>passive_skill_ui.credit_none</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>配置准备中</t>
+          <t>点数 | -</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>passive_skill_ui.confirm_ok</t>
+          <t>passive_skill_ui.profile_loading</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>确定</t>
+          <t>配置准备中</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_current_level</t>
+          <t>passive_skill_ui.confirm_ok</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>当前等级: {0} / {1}</t>
+          <t>确定</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_current_effect</t>
+          <t>passive_skill_ui.detail_current_level</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>当前效果: {0}</t>
+          <t>当前等级: {0} / {1}</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>passive_skill_ui.detail_next_level</t>
+          <t>passive_skill_ui.detail_current_effect</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>下一级: {0}</t>
+          <t>当前效果: {0}</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>common_ui.cancel</t>
+          <t>passive_skill_ui.detail_next_level</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>取消</t>
+          <t>下一级: {0}</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rest_ui.header</t>
+          <t>common_ui.cancel</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>休息</t>
+          <t>取消</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>rest_ui.header</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>休息</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>rest_ui.description</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>支付信用点
 进行休息吗？</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>rest_ui.health_recovery</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>恢复25%生命</t>
-        </is>
-      </c>
-    </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rest_ui.potion_recharge</t>
+          <t>rest_ui.health_recovery</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>药水补充</t>
+          <t>恢复25%生命</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rest_ui.cost_format</t>
+          <t>rest_ui.potion_recharge</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>所需信用点 : {0}</t>
+          <t>药水补充</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rest_ui.complete_message</t>
+          <t>rest_ui.cost_format</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>消耗{0}信用点，恢复了{1}点生命和{2}个药水。</t>
+          <t>所需信用点 : {0}</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_chat</t>
+          <t>rest_ui.complete_message</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">[聊天] </t>
+          <t>消耗{0}信用点，恢复了{1}点生命和{2}个药水。</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_acquisition</t>
+          <t>chat_ui.prefix_chat</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">[物品] </t>
+          <t xml:space="preserve">[聊天] </t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_warning</t>
+          <t>chat_ui.prefix_acquisition</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">[提示] </t>
+          <t xml:space="preserve">[物品] </t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_connection</t>
+          <t>chat_ui.prefix_warning</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">[连接] </t>
+          <t xml:space="preserve">[提示] </t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>chat_ui.item_fallback_name</t>
+          <t>chat_ui.prefix_connection</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>物品</t>
+          <t xml:space="preserve">[连接] </t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_cost_format</t>
+          <t>chat_ui.item_fallback_name</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 刷新</t>
+          <t>物品</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_free</t>
+          <t>shop_ui.reroll_cost_format</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>免费刷新</t>
+          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 刷新</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_count_format</t>
+          <t>shop_ui.reroll_free</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>[ {0} ]</t>
+          <t>免费刷新</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>settings_ui.reset_confirm</t>
+          <t>shop_ui.reroll_count_format</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>要将设置恢复为默认值吗？</t>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>settings_ui.reset_warning</t>
+          <t>settings_ui.reset_confirm</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>当前所有设置都将恢复为默认值。</t>
+          <t>要将设置恢复为默认值吗？</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_confirm</t>
+          <t>settings_ui.reset_warning</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>要放弃游戏吗？</t>
+          <t>当前所有设置都将恢复为默认值。</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_warning</t>
+          <t>pause_ui.giveup_confirm</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>警告：当前游戏数据将会丢失。</t>
+          <t>要放弃游戏吗？</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm</t>
+          <t>pause_ui.giveup_warning</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>确定要放弃吗？</t>
+          <t>警告：当前游戏数据将会丢失。</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm_warning</t>
+          <t>pause_ui.giveup_reconfirm</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>当前远征将被重置，且无法获得信用点。</t>
+          <t>确定要放弃吗？</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>pause_ui.save_and_quit_confirm</t>
+          <t>pause_ui.giveup_reconfirm_warning</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>要保存并退出游戏吗？</t>
+          <t>当前远征将被重置，且无法获得信用点。</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_confirm</t>
+          <t>pause_ui.save_and_quit_confirm</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>要结束主机会话吗？</t>
+          <t>要保存并退出游戏吗？</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_warning</t>
+          <t>pause_ui.host_end_confirm</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>所有参与者的连接和当前轮次都将结束。</t>
+          <t>要结束主机会话吗？</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>pause_ui.leave_confirm</t>
+          <t>pause_ui.host_end_warning</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>要离开此会话吗？</t>
+          <t>所有参与者的连接和当前轮次都将结束。</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>pause_ui.leave_warning</t>
+          <t>pause_ui.leave_confirm</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>你将放弃参与资格，且无法重新加入本轮。</t>
+          <t>要离开此会话吗？</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_confirm</t>
+          <t>pause_ui.leave_warning</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>要暂时离开会话吗？</t>
+          <t>你将放弃参与资格，且无法重新加入本轮。</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_warning</t>
+          <t>pause_ui.temp_leave_confirm</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>服务器保持运行期间，可在5分钟内重新连接。队伍的游戏将继续进行。</t>
+          <t>要暂时离开会话吗？</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>pause_ui.adjustment</t>
+          <t>pause_ui.temp_leave_warning</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>结算并结束</t>
+          <t>服务器保持运行期间，可在5分钟内重新连接。队伍的游戏将继续进行。</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>pause_ui.settle_confirm</t>
+          <t>pause_ui.adjustment</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>要结算并结束游戏吗？</t>
+          <t>结算并结束</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>pause_ui.settle_confirm</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>要结算并结束游戏吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
           <t>pause_ui.settle_warning</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B186" t="inlineStr">
         <is>
           <t>将获得持有信用点及物品原价的50%作为账号信用点，当前远征将被重置。</t>
         </is>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B300"/>
+  <dimension ref="A1:B305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3712,310 +3712,370 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>session_ui.end_host</t>
+          <t>result_ui.act_clear_description</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>호스트 세션 종료</t>
+          <t>액트를 클리어했습니다.</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>session_ui.leave</t>
+          <t>result_ui.settle_description</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>세션 떠나기</t>
+          <t>정산을 완료했습니다.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>session_ui.leave_temporarily</t>
+          <t>result_ui.current_stage</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>잠시 나가기</t>
+          <t>현재 도달 스테이지</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>session_ui.confirm_end_host</t>
+          <t>result_ui.farming_value</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>호스트 세션을 종료하시겠습니까?</t>
+          <t>파밍 가치 현황</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>session_ui.warn_end_host</t>
+          <t>result_ui.continue</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>모든 참가자의 연결과 현재 런이 종료됩니다.</t>
+          <t>계속하기</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>session_ui.confirm_leave</t>
+          <t>session_ui.end_host</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>이 세션에서 떠나시겠습니까?</t>
+          <t>호스트 세션 종료</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>session_ui.warn_leave</t>
+          <t>session_ui.leave</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</t>
+          <t>세션 떠나기</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>session_ui.confirm_temporary_leave</t>
+          <t>session_ui.leave_temporarily</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>잠시 세션에서 나가시겠습니까?</t>
+          <t>잠시 나가기</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>session_ui.warn_temporary_leave</t>
+          <t>session_ui.confirm_end_host</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</t>
+          <t>호스트 세션을 종료하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>session_ui.passive_locked</t>
+          <t>session_ui.warn_end_host</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>준비를 취소한 뒤 패시브를 변경할 수 있습니다.</t>
+          <t>모든 참가자의 연결과 현재 런이 종료됩니다.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait</t>
+          <t>session_ui.confirm_leave</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</t>
+          <t>이 세션에서 떠나시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_host</t>
+          <t>session_ui.warn_leave</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>참가자의 결과 저장을 기다리고 있습니다. 저장 후 세션을 종료해 주세요.</t>
+          <t>현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_player</t>
+          <t>session_ui.confirm_temporary_leave</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>{0}의 결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</t>
+          <t>잠시 세션에서 나가시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>session_ui.lobby_loading</t>
+          <t>session_ui.warn_temporary_leave</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>로비 이동이 끝난 뒤 출발할 수 있습니다.</t>
+          <t>서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>session_ui.player_prefabs_missing</t>
+          <t>session_ui.passive_locked</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>두 클래스의 네트워크 프리팹 연결을 확인하세요.</t>
+          <t>준비를 취소한 뒤 패시브를 변경할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>session_ui.session_missing</t>
+          <t>session_ui.settlement_wait</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>참여 중인 세션을 찾을 수 없습니다.</t>
+          <t>결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>session_ui.unsupported_request</t>
+          <t>session_ui.settlement_wait_host</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>지원하지 않는 로비 요청입니다.</t>
+          <t>참가자의 결과 저장을 기다리고 있습니다. 저장 후 세션을 종료해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>session_ui.return_lobby_denied</t>
+          <t>session_ui.settlement_wait_player</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>서버가 결과를 확정한 뒤 방장만 파티를 로비로 이동할 수 있습니다.</t>
+          <t>{0}의 결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>session_ui.passive_invalid</t>
+          <t>session_ui.lobby_loading</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>패시브 프로필을 확인할 수 없습니다.</t>
+          <t>로비 이동이 끝난 뒤 출발할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>session_ui.party_not_ready</t>
+          <t>session_ui.player_prefabs_missing</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>모든 참가자가 캐릭터 선택과 준비를 완료해야 합니다.</t>
+          <t>두 클래스의 네트워크 프리팹 연결을 확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>preparation_ui.waiting</t>
+          <t>session_ui.session_missing</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>플레이를 준비하고 있습니다…</t>
+          <t>참여 중인 세션을 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout</t>
+          <t>session_ui.unsupported_request</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>플레이 준비 시간이 초과되었습니다.</t>
+          <t>지원하지 않는 로비 요청입니다.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout_retry</t>
+          <t>session_ui.return_lobby_denied</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>플레이 준비 시간이 초과되었습니다. 연결을 종료하고 다시 시도하세요.</t>
+          <t>서버가 결과를 확정한 뒤 방장만 파티를 로비로 이동할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>preparation_ui.combat_failed</t>
+          <t>session_ui.passive_invalid</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>전투 웨이브 또는 생성 지점 준비에 실패했습니다.</t>
+          <t>패시브 프로필을 확인할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>preparation_ui.disconnected</t>
+          <t>session_ui.party_not_ready</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>연결이 종료되었습니다.</t>
+          <t>모든 참가자가 캐릭터 선택과 준비를 완료해야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
+          <t>preparation_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>플레이를 준비하고 있습니다…</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>플레이 준비 시간이 초과되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout_retry</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>플레이 준비 시간이 초과되었습니다. 연결을 종료하고 다시 시도하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>preparation_ui.combat_failed</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>전투 웨이브 또는 생성 지점 준비에 실패했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>연결이 종료되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
           <t>preparation_ui.exit</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>나가기</t>
         </is>
@@ -4032,7 +4092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B300"/>
+  <dimension ref="A1:B305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7328,310 +7388,370 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>session_ui.end_host</t>
+          <t>result_ui.act_clear_description</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>End Host Session</t>
+          <t>Act cleared!</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>session_ui.leave</t>
+          <t>result_ui.settle_description</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Leave Session</t>
+          <t>Settlement complete.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>session_ui.leave_temporarily</t>
+          <t>result_ui.current_stage</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Disconnect Temporarily</t>
+          <t>Current Stage</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>session_ui.confirm_end_host</t>
+          <t>result_ui.farming_value</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>End this host session?</t>
+          <t>Loot Value</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>session_ui.warn_end_host</t>
+          <t>result_ui.continue</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>All players will disconnect and the current run will end.</t>
+          <t>Continue</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>session_ui.confirm_leave</t>
+          <t>session_ui.end_host</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Leave this session?</t>
+          <t>End Host Session</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>session_ui.warn_leave</t>
+          <t>session_ui.leave</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>You will forfeit your place and cannot rejoin this run.</t>
+          <t>Leave Session</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>session_ui.confirm_temporary_leave</t>
+          <t>session_ui.leave_temporarily</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Disconnect from this session temporarily?</t>
+          <t>Disconnect Temporarily</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>session_ui.warn_temporary_leave</t>
+          <t>session_ui.confirm_end_host</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>You can reconnect within 5 minutes while the server stays online. The party will keep playing.</t>
+          <t>End this host session?</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>session_ui.passive_locked</t>
+          <t>session_ui.warn_end_host</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Cancel Ready before changing passives.</t>
+          <t>All players will disconnect and the current run will end.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait</t>
+          <t>session_ui.confirm_leave</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Results are still being saved. Please try again shortly.</t>
+          <t>Leave this session?</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_host</t>
+          <t>session_ui.warn_leave</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Waiting for player results to save. End the session after saving finishes.</t>
+          <t>You will forfeit your place and cannot rejoin this run.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_player</t>
+          <t>session_ui.confirm_temporary_leave</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Waiting for {0}'s results to save. Please try again shortly.</t>
+          <t>Disconnect from this session temporarily?</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>session_ui.lobby_loading</t>
+          <t>session_ui.warn_temporary_leave</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Wait for the lobby to finish loading before starting.</t>
+          <t>You can reconnect within 5 minutes while the server stays online. The party will keep playing.</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>session_ui.player_prefabs_missing</t>
+          <t>session_ui.passive_locked</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Player setup is incomplete. Please reconnect.</t>
+          <t>Cancel Ready before changing passives.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>session_ui.session_missing</t>
+          <t>session_ui.settlement_wait</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>The current session could not be found.</t>
+          <t>Results are still being saved. Please try again shortly.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>session_ui.unsupported_request</t>
+          <t>session_ui.settlement_wait_host</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>This lobby action is unavailable.</t>
+          <t>Waiting for player results to save. End the session after saving finishes.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>session_ui.return_lobby_denied</t>
+          <t>session_ui.settlement_wait_player</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Only the leader can return the party to the lobby after results are confirmed.</t>
+          <t>Waiting for {0}'s results to save. Please try again shortly.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>session_ui.passive_invalid</t>
+          <t>session_ui.lobby_loading</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Your passive profile could not be verified.</t>
+          <t>Wait for the lobby to finish loading before starting.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>session_ui.party_not_ready</t>
+          <t>session_ui.player_prefabs_missing</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>All players must choose a character and be ready.</t>
+          <t>Player setup is incomplete. Please reconnect.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>preparation_ui.waiting</t>
+          <t>session_ui.session_missing</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Preparing the game…</t>
+          <t>The current session could not be found.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout</t>
+          <t>session_ui.unsupported_request</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Game preparation timed out.</t>
+          <t>This lobby action is unavailable.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout_retry</t>
+          <t>session_ui.return_lobby_denied</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Game preparation timed out. Disconnect and try again.</t>
+          <t>Only the leader can return the party to the lobby after results are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>preparation_ui.combat_failed</t>
+          <t>session_ui.passive_invalid</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>The battle could not be prepared. Please reconnect.</t>
+          <t>Your passive profile could not be verified.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>preparation_ui.disconnected</t>
+          <t>session_ui.party_not_ready</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>The connection has ended.</t>
+          <t>All players must choose a character and be ready.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
+          <t>preparation_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Preparing the game…</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Game preparation timed out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout_retry</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Game preparation timed out. Disconnect and try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>preparation_ui.combat_failed</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>The battle could not be prepared. Please reconnect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>The connection has ended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
           <t>preparation_ui.exit</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -7648,7 +7768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B300"/>
+  <dimension ref="A1:B305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10944,310 +11064,370 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>session_ui.end_host</t>
+          <t>result_ui.act_clear_description</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>ホストセッションを終了</t>
+          <t>アクトをクリアしました。</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>session_ui.leave</t>
+          <t>result_ui.settle_description</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>セッションを退出</t>
+          <t>精算が完了しました。</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>session_ui.leave_temporarily</t>
+          <t>result_ui.current_stage</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>一時的に退出</t>
+          <t>現在の到達ステージ</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>session_ui.confirm_end_host</t>
+          <t>result_ui.farming_value</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>ホストセッションを終了しますか？</t>
+          <t>獲得価値</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>session_ui.warn_end_host</t>
+          <t>result_ui.continue</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>全員の接続と現在のプレイが終了します。</t>
+          <t>続ける</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>session_ui.confirm_leave</t>
+          <t>session_ui.end_host</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>このセッションを退出しますか？</t>
+          <t>ホストセッションを終了</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>session_ui.warn_leave</t>
+          <t>session_ui.leave</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>参加権を放棄するため、このプレイには再接続できません。</t>
+          <t>セッションを退出</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>session_ui.confirm_temporary_leave</t>
+          <t>session_ui.leave_temporarily</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>セッションから一時的に退出しますか？</t>
+          <t>一時的に退出</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>session_ui.warn_temporary_leave</t>
+          <t>session_ui.confirm_end_host</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>サーバーが稼働中なら5分以内に再接続できます。パーティーのゲームは続行されます。</t>
+          <t>ホストセッションを終了しますか？</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>session_ui.passive_locked</t>
+          <t>session_ui.warn_end_host</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>準備を解除するとパッシブを変更できます。</t>
+          <t>全員の接続と現在のプレイが終了します。</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait</t>
+          <t>session_ui.confirm_leave</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>結果を保存しています。少し待ってからお試しください。</t>
+          <t>このセッションを退出しますか？</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_host</t>
+          <t>session_ui.warn_leave</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>参加者の結果を保存しています。保存完了後にセッションを終了してください。</t>
+          <t>参加権を放棄するため、このプレイには再接続できません。</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_player</t>
+          <t>session_ui.confirm_temporary_leave</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>{0}の結果を保存しています。少し待ってからお試しください。</t>
+          <t>セッションから一時的に退出しますか？</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>session_ui.lobby_loading</t>
+          <t>session_ui.warn_temporary_leave</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>ロビーの読み込みが終わってから出発してください。</t>
+          <t>サーバーが稼働中なら5分以内に再接続できます。パーティーのゲームは続行されます。</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>session_ui.player_prefabs_missing</t>
+          <t>session_ui.passive_locked</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>プレイヤーの準備が不完全です。再接続してください。</t>
+          <t>準備を解除するとパッシブを変更できます。</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>session_ui.session_missing</t>
+          <t>session_ui.settlement_wait</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>参加中のセッションが見つかりません。</t>
+          <t>結果を保存しています。少し待ってからお試しください。</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>session_ui.unsupported_request</t>
+          <t>session_ui.settlement_wait_host</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>このロビー操作は利用できません。</t>
+          <t>参加者の結果を保存しています。保存完了後にセッションを終了してください。</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>session_ui.return_lobby_denied</t>
+          <t>session_ui.settlement_wait_player</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>結果確定後、リーダーのみがパーティーをロビーに戻せます。</t>
+          <t>{0}の結果を保存しています。少し待ってからお試しください。</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>session_ui.passive_invalid</t>
+          <t>session_ui.lobby_loading</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>パッシブのプロフィールを確認できません。</t>
+          <t>ロビーの読み込みが終わってから出発してください。</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>session_ui.party_not_ready</t>
+          <t>session_ui.player_prefabs_missing</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>全員がキャラクターを選択し、準備を完了してください。</t>
+          <t>プレイヤーの準備が不完全です。再接続してください。</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>preparation_ui.waiting</t>
+          <t>session_ui.session_missing</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>ゲームを準備しています…</t>
+          <t>参加中のセッションが見つかりません。</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout</t>
+          <t>session_ui.unsupported_request</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ゲームの準備がタイムアウトしました。</t>
+          <t>このロビー操作は利用できません。</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout_retry</t>
+          <t>session_ui.return_lobby_denied</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>ゲームの準備がタイムアウトしました。切断してもう一度お試しください。</t>
+          <t>結果確定後、リーダーのみがパーティーをロビーに戻せます。</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>preparation_ui.combat_failed</t>
+          <t>session_ui.passive_invalid</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>戦闘の準備に失敗しました。再接続してください。</t>
+          <t>パッシブのプロフィールを確認できません。</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>preparation_ui.disconnected</t>
+          <t>session_ui.party_not_ready</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>接続が終了しました。</t>
+          <t>全員がキャラクターを選択し、準備を完了してください。</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
+          <t>preparation_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>ゲームを準備しています…</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>ゲームの準備がタイムアウトしました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout_retry</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>ゲームの準備がタイムアウトしました。切断してもう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>preparation_ui.combat_failed</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>戦闘の準備に失敗しました。再接続してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>接続が終了しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
           <t>preparation_ui.exit</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>退出</t>
         </is>
@@ -11264,7 +11444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B300"/>
+  <dimension ref="A1:B305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14560,310 +14740,370 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>session_ui.end_host</t>
+          <t>result_ui.act_clear_description</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>结束主机会话</t>
+          <t>已通关本章节。</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>session_ui.leave</t>
+          <t>result_ui.settle_description</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>离开会话</t>
+          <t>结算完成。</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>session_ui.leave_temporarily</t>
+          <t>result_ui.current_stage</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>暂时离开</t>
+          <t>当前到达关卡</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>session_ui.confirm_end_host</t>
+          <t>result_ui.farming_value</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>要结束主机会话吗？</t>
+          <t>收获价值</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>session_ui.warn_end_host</t>
+          <t>result_ui.continue</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>所有玩家将断开连接，当前冒险将结束。</t>
+          <t>继续</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>session_ui.confirm_leave</t>
+          <t>session_ui.end_host</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>要离开此会话吗？</t>
+          <t>结束主机会话</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>session_ui.warn_leave</t>
+          <t>session_ui.leave</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>您将放弃参与资格，无法重新加入本次冒险。</t>
+          <t>离开会话</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>session_ui.confirm_temporary_leave</t>
+          <t>session_ui.leave_temporarily</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>要暂时离开此会话吗？</t>
+          <t>暂时离开</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>session_ui.warn_temporary_leave</t>
+          <t>session_ui.confirm_end_host</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>服务器在线时可在5分钟内重新连接。队伍的游戏会继续。</t>
+          <t>要结束主机会话吗？</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>session_ui.passive_locked</t>
+          <t>session_ui.warn_end_host</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>取消准备后才能更改被动技能。</t>
+          <t>所有玩家将断开连接，当前冒险将结束。</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait</t>
+          <t>session_ui.confirm_leave</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>正在保存结果，请稍后重试。</t>
+          <t>要离开此会话吗？</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_host</t>
+          <t>session_ui.warn_leave</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>正在等待玩家结果保存。请在保存完成后结束会话。</t>
+          <t>您将放弃参与资格，无法重新加入本次冒险。</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_player</t>
+          <t>session_ui.confirm_temporary_leave</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>正在等待{0}的结果保存，请稍后重试。</t>
+          <t>要暂时离开此会话吗？</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>session_ui.lobby_loading</t>
+          <t>session_ui.warn_temporary_leave</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>请等待大厅加载完成后再出发。</t>
+          <t>服务器在线时可在5分钟内重新连接。队伍的游戏会继续。</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>session_ui.player_prefabs_missing</t>
+          <t>session_ui.passive_locked</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>玩家配置不完整，请重新连接。</t>
+          <t>取消准备后才能更改被动技能。</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>session_ui.session_missing</t>
+          <t>session_ui.settlement_wait</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>未找到当前会话。</t>
+          <t>正在保存结果，请稍后重试。</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>session_ui.unsupported_request</t>
+          <t>session_ui.settlement_wait_host</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>此大厅操作不可用。</t>
+          <t>正在等待玩家结果保存。请在保存完成后结束会话。</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>session_ui.return_lobby_denied</t>
+          <t>session_ui.settlement_wait_player</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>结果确认后，仅队长能带领队伍返回大厅。</t>
+          <t>正在等待{0}的结果保存，请稍后重试。</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>session_ui.passive_invalid</t>
+          <t>session_ui.lobby_loading</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>无法验证被动技能资料。</t>
+          <t>请等待大厅加载完成后再出发。</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>session_ui.party_not_ready</t>
+          <t>session_ui.player_prefabs_missing</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>所有玩家必须选择角色并准备就绪。</t>
+          <t>玩家配置不完整，请重新连接。</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>preparation_ui.waiting</t>
+          <t>session_ui.session_missing</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>正在准备游戏…</t>
+          <t>未找到当前会话。</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout</t>
+          <t>session_ui.unsupported_request</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>游戏准备超时。</t>
+          <t>此大厅操作不可用。</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout_retry</t>
+          <t>session_ui.return_lobby_denied</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>游戏准备超时，请断开连接后重试。</t>
+          <t>结果确认后，仅队长能带领队伍返回大厅。</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>preparation_ui.combat_failed</t>
+          <t>session_ui.passive_invalid</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>战斗准备失败，请重新连接。</t>
+          <t>无法验证被动技能资料。</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>preparation_ui.disconnected</t>
+          <t>session_ui.party_not_ready</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>连接已结束。</t>
+          <t>所有玩家必须选择角色并准备就绪。</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
+          <t>preparation_ui.waiting</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>正在准备游戏…</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>游戏准备超时。</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>preparation_ui.timeout_retry</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>游戏准备超时，请断开连接后重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>preparation_ui.combat_failed</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>战斗准备失败，请重新连接。</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>连接已结束。</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
           <t>preparation_ui.exit</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>离开</t>
         </is>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B305"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2331,1751 +2331,1763 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rest_ui.potion_recharge</t>
+          <t>rest_ui.health_recovery_format</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>포션 충전</t>
+          <t>체력 {0}% 회복</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rest_ui.cost_format</t>
+          <t>rest_ui.potion_recharge</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>필요 크레딧 : {0}</t>
+          <t>포션 충전</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rest_ui.complete_message</t>
+          <t>rest_ui.cost_format</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>{0} 크레딧을 소비하여 체력 {1}, 포션 {2}개를 채웠습니다.</t>
+          <t>필요 크레딧 : {0}</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_chat</t>
+          <t>rest_ui.complete_message</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">[채팅] </t>
+          <t>{0} 크레딧을 소비하여 체력 {1}, 포션 {2}개를 채웠습니다.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_acquisition</t>
+          <t>chat_ui.prefix_chat</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">[획득] </t>
+          <t xml:space="preserve">[채팅] </t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_warning</t>
+          <t>chat_ui.prefix_acquisition</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">[안내] </t>
+          <t xml:space="preserve">[획득] </t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_connection</t>
+          <t>chat_ui.prefix_warning</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">[연결] </t>
+          <t xml:space="preserve">[안내] </t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>chat_ui.item_fallback_name</t>
+          <t>chat_ui.prefix_connection</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>아이템</t>
+          <t xml:space="preserve">[연결] </t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_cost_format</t>
+          <t>chat_ui.item_fallback_name</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 리롤</t>
+          <t>아이템</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_free</t>
+          <t>shop_ui.reroll_cost_format</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>무료 리롤</t>
+          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 리롤</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_count_format</t>
+          <t>shop_ui.reroll_free</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>[ {0} ]</t>
+          <t>무료 리롤</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>settings_ui.reset_confirm</t>
+          <t>shop_ui.reroll_count_format</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>설정을 기본값으로 초기화하시겠습니까?</t>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>settings_ui.reset_warning</t>
+          <t>settings_ui.reset_confirm</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>현재 설정이 모두 기본값으로 변경됩니다.</t>
+          <t>설정을 기본값으로 초기화하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_confirm</t>
+          <t>settings_ui.reset_warning</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>게임을 포기하시겠습니까?</t>
+          <t>현재 설정이 모두 기본값으로 변경됩니다.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_warning</t>
+          <t>pause_ui.giveup_confirm</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>경고: 현재 게임 데이터가 사라집니다.</t>
+          <t>게임을 포기하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm</t>
+          <t>pause_ui.giveup_warning</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>정말 포기하시겠습니까?</t>
+          <t>경고: 현재 게임 데이터가 사라집니다.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm_warning</t>
+          <t>pause_ui.giveup_reconfirm</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>진행 중인 원정이 초기화되며 크레딧을 받을 수 없습니다.</t>
+          <t>정말 포기하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>pause_ui.save_and_quit_confirm</t>
+          <t>pause_ui.giveup_reconfirm_warning</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>게임을 저장하고 종료하시겠습니까?</t>
+          <t>진행 중인 원정이 초기화되며 크레딧을 받을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_confirm</t>
+          <t>pause_ui.save_and_quit_confirm</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>호스트 세션을 종료하시겠습니까?</t>
+          <t>게임을 저장하고 종료하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_warning</t>
+          <t>pause_ui.host_end_confirm</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>모든 참가자의 연결과 현재 런이 종료됩니다.</t>
+          <t>호스트 세션을 종료하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>pause_ui.leave_confirm</t>
+          <t>pause_ui.host_end_warning</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>이 세션에서 떠나시겠습니까?</t>
+          <t>모든 참가자의 연결과 현재 런이 종료됩니다.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>pause_ui.leave_warning</t>
+          <t>pause_ui.leave_confirm</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</t>
+          <t>이 세션에서 떠나시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_confirm</t>
+          <t>pause_ui.leave_warning</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>잠시 세션에서 나가시겠습니까?</t>
+          <t>현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_warning</t>
+          <t>pause_ui.temp_leave_confirm</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</t>
+          <t>잠시 세션에서 나가시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>pause_ui.adjustment</t>
+          <t>pause_ui.temp_leave_warning</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>정산 후 액트 종료</t>
+          <t>서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>pause_ui.settle_confirm</t>
+          <t>pause_ui.adjustment</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>정산 후 게임을 종료하시겠습니까?</t>
+          <t>정산 후 액트 종료</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>pause_ui.settle_warning</t>
+          <t>pause_ui.settle_confirm</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>보유 크레딧과 아이템 원가의 50%를 계정 크레딧으로 받고, 현재 원정은 초기화됩니다.</t>
+          <t>정산 후 게임을 종료하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>login_ui.title</t>
+          <t>pause_ui.settle_warning</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>사용자 인증</t>
+          <t>보유 크레딧과 아이템 원가의 50%를 계정 크레딧으로 받고, 현재 원정은 초기화됩니다.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>login_ui.subtitle</t>
+          <t>login_ui.title</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>사용자 인증 터미널</t>
+          <t>사용자 인증</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>login_ui.account</t>
+          <t>login_ui.subtitle</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>계정 ID</t>
+          <t>사용자 인증 터미널</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>login_ui.email_placeholder</t>
+          <t>login_ui.account</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>이메일</t>
+          <t>계정 ID</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>login_ui.password</t>
+          <t>login_ui.email_placeholder</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>비밀번호</t>
+          <t>이메일</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>login_ui.confirm_password</t>
+          <t>login_ui.password</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>비밀번호 확인</t>
+          <t>비밀번호</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>login_ui.submit</t>
+          <t>login_ui.confirm_password</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>접속</t>
+          <t>비밀번호 확인</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>login_ui.no_account</t>
+          <t>login_ui.submit</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>계정이 없는 상태인가요?</t>
+          <t>접속</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>login_ui.create_account</t>
+          <t>login_ui.no_account</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>계정 생성</t>
+          <t>계정이 없는 상태인가요?</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>login_ui.create</t>
+          <t>login_ui.create_account</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>생성</t>
+          <t>계정 생성</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>login_ui.has_account</t>
+          <t>login_ui.create</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>계정이 있으신가요?</t>
+          <t>생성</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>login_ui.login</t>
+          <t>login_ui.has_account</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>로그인</t>
+          <t>계정이 있으신가요?</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>login_ui.footer</t>
+          <t>login_ui.login</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>보안 접속 터미널</t>
+          <t>로그인</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>login_ui.submitting</t>
+          <t>login_ui.footer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>로그인 중...</t>
+          <t>보안 접속 터미널</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>login_ui.creating</t>
+          <t>login_ui.submitting</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>계정 생성 중...</t>
+          <t>로그인 중...</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>login_ui.required</t>
+          <t>login_ui.creating</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>이메일과 비밀번호를 입력해 주세요.</t>
+          <t>계정 생성 중...</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>login_ui.account_required</t>
+          <t>login_ui.required</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>계정 ID와 비밀번호를 입력하십시오.</t>
+          <t>이메일과 비밀번호를 입력해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>login_ui.confirm_required</t>
+          <t>login_ui.account_required</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>비밀번호 확인을 입력하십시오.</t>
+          <t>계정 ID와 비밀번호를 입력하십시오.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>login_ui.password_mismatch</t>
+          <t>login_ui.confirm_required</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>비밀번호가 일치하지 않습니다.</t>
+          <t>비밀번호 확인을 입력하십시오.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>login_ui.login_error</t>
+          <t>login_ui.password_mismatch</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>로그인 처리 중 오류가 발생했습니다.</t>
+          <t>비밀번호가 일치하지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>login_ui.profile_incomplete</t>
+          <t>login_ui.login_error</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>계정은 생성되었지만 기본 프로필을 준비하지 못했습니다. 로그인 화면에서 다시 로그인해 주세요.</t>
+          <t>로그인 처리 중 오류가 발생했습니다.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>login_ui.created</t>
+          <t>login_ui.profile_incomplete</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>계정 생성이 완료되었습니다. 로그인 화면에서 새 계정으로 로그인해 주세요.</t>
+          <t>계정은 생성되었지만 기본 프로필을 준비하지 못했습니다. 로그인 화면에서 다시 로그인해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>login_ui.create_error</t>
+          <t>login_ui.created</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>계정 생성 처리 중 오류가 발생했습니다.</t>
+          <t>계정 생성이 완료되었습니다. 로그인 화면에서 새 계정으로 로그인해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>login_ui.loader_missing</t>
+          <t>login_ui.create_error</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>씬 로더가 준비되지 않았습니다. Start 씬부터 실행해 주세요.</t>
+          <t>계정 생성 처리 중 오류가 발생했습니다.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>login_ui.scenes_missing</t>
+          <t>login_ui.loader_missing</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>TitleScene과 LoadingScene의 빌드 등록을 확인해 주세요.</t>
+          <t>씬 로더가 준비되지 않았습니다. Start 씬부터 실행해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>login_ui.user_missing</t>
+          <t>login_ui.scenes_missing</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>로그인 결과에서 사용자 정보를 확인하지 못했습니다.</t>
+          <t>TitleScene과 LoadingScene의 빌드 등록을 확인해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
+          <t>login_ui.user_missing</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>로그인 결과에서 사용자 정보를 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>login_ui.auth_failed</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>로그인에 실패했습니다.
 이메일, 비밀번호와 Firebase 인증 설정을 확인해 주세요.</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>login_ui.firebase_login_error</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Firebase 로그인 중 오류가 발생했습니다.</t>
-        </is>
-      </c>
-    </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>login_ui.created_user_missing</t>
+          <t>login_ui.firebase_login_error</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>계정 생성 결과에서 사용자 정보를 확인하지 못했습니다.</t>
+          <t>Firebase 로그인 중 오류가 발생했습니다.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>login_ui.firebase_create_error</t>
+          <t>login_ui.created_user_missing</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Firebase 계정 생성 중 오류가 발생했습니다.</t>
+          <t>계정 생성 결과에서 사용자 정보를 확인하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>login_ui.email_in_use</t>
+          <t>login_ui.firebase_create_error</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>이미 사용 중인 이메일입니다.</t>
+          <t>Firebase 계정 생성 중 오류가 발생했습니다.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>login_ui.invalid_email</t>
+          <t>login_ui.email_in_use</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>올바른 이메일 주소를 입력해 주세요.</t>
+          <t>이미 사용 중인 이메일입니다.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>login_ui.password_policy</t>
+          <t>login_ui.invalid_email</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Firebase 비밀번호 정책을 만족하는 비밀번호를 입력해 주세요.</t>
+          <t>올바른 이메일 주소를 입력해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>login_ui.auth_disabled</t>
+          <t>login_ui.password_policy</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Firebase Console에서 이메일/비밀번호 로그인을 활성화해 주세요.</t>
+          <t>Firebase 비밀번호 정책을 만족하는 비밀번호를 입력해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>login_ui.network_error</t>
+          <t>login_ui.auth_disabled</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>네트워크 연결을 확인한 뒤 다시 시도해 주세요.</t>
+          <t>Firebase Console에서 이메일/비밀번호 로그인을 활성화해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>login_ui.too_many_requests</t>
+          <t>login_ui.network_error</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>요청이 너무 많습니다. 잠시 후 다시 시도해 주세요.</t>
+          <t>네트워크 연결을 확인한 뒤 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>login_ui.create_failed</t>
+          <t>login_ui.too_many_requests</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>계정을 생성하지 못했습니다. 입력값과 Firebase 인증 설정을 확인해 주세요.</t>
+          <t>요청이 너무 많습니다. 잠시 후 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>login_ui.config_missing</t>
+          <t>login_ui.create_failed</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Firebase 설정 파일이 없습니다. google-services.json 또는 GoogleService-Info.plist를 Assets 폴더에 추가해 주세요.</t>
+          <t>계정을 생성하지 못했습니다. 입력값과 Firebase 인증 설정을 확인해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>login_ui.dependencies</t>
+          <t>login_ui.config_missing</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Firebase 의존성을 준비하지 못했습니다: {0}</t>
+          <t>Firebase 설정 파일이 없습니다. google-services.json 또는 GoogleService-Info.plist를 Assets 폴더에 추가해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>login_ui.init_failed</t>
+          <t>login_ui.dependencies</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Firebase 초기화에 실패했습니다. 설정 파일과 프로젝트 연결 상태를 확인해 주세요.</t>
+          <t>Firebase 의존성을 준비하지 못했습니다: {0}</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>connection_ui.title</t>
+          <t>login_ui.init_failed</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>멀티플레이 접속</t>
+          <t>Firebase 초기화에 실패했습니다. 설정 파일과 프로젝트 연결 상태를 확인해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>connection_ui.subtitle</t>
+          <t>connection_ui.title</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>멀티플레이 접속 터미널</t>
+          <t>멀티플레이 접속</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>connection_ui.address</t>
+          <t>connection_ui.subtitle</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>서버 주소</t>
+          <t>멀티플레이 접속 터미널</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>connection_ui.address_placeholder</t>
+          <t>connection_ui.address</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>서버 IP 또는 호스트명</t>
+          <t>서버 주소</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>connection_ui.nickname</t>
+          <t>connection_ui.address_placeholder</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>닉네임</t>
+          <t>서버 IP 또는 호스트명</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>connection_ui.host</t>
+          <t>connection_ui.nickname</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>로컬 테스트 · Host</t>
+          <t>닉네임</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>connection_ui.join</t>
+          <t>connection_ui.host</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>서버 접속</t>
+          <t>로컬 테스트 · Host</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>connection_ui.server</t>
+          <t>connection_ui.join</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>로컬 테스트 · 서버</t>
+          <t>서버 접속</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect</t>
+          <t>connection_ui.server</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>최근 세션으로 복귀</t>
+          <t>로컬 테스트 · 서버</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>connection_ui.return_title</t>
+          <t>connection_ui.reconnect</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>타이틀로 돌아가기</t>
+          <t>최근 세션으로 복귀</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>connection_ui.settings_missing</t>
+          <t>connection_ui.return_title</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>세션 연결 설정을 찾을 수 없습니다.</t>
+          <t>타이틀로 돌아가기</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>connection_ui.invalid_nickname</t>
+          <t>connection_ui.settings_missing</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>닉네임을 1~24자로 입력해 주세요. 태그와 줄바꿈은 사용할 수 없습니다.</t>
+          <t>세션 연결 설정을 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>connection_ui.invalid_address</t>
+          <t>connection_ui.invalid_nickname</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>서버 IP 또는 호스트명을 입력해 주세요. 포트 번호는 붙이지 않습니다.</t>
+          <t>닉네임을 1~24자로 입력해 주세요. 태그와 줄바꿈은 사용할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>connection_ui.connecting</t>
+          <t>connection_ui.invalid_address</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>연결 중…</t>
+          <t>서버 IP 또는 호스트명을 입력해 주세요. 포트 번호는 붙이지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>connection_ui.server_running</t>
+          <t>connection_ui.connecting</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>전용 서버 실행 중 · 참가자 대기</t>
+          <t>연결 중…</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>connection_ui.no_session</t>
+          <t>connection_ui.server_running</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>이 프로필에 저장된 최근 세션이 없습니다.</t>
+          <t>전용 서버 실행 중 · 참가자 대기</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>connection_ui.profile_large</t>
+          <t>connection_ui.no_session</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>재접속 프로필 자료가 너무 큽니다.</t>
+          <t>이 프로필에 저장된 최근 세션이 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>connection_ui.profile_invalid</t>
+          <t>connection_ui.profile_large</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>재접속 프로필 자료가 올바르지 않습니다.</t>
+          <t>재접속 프로필 자료가 너무 큽니다.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>connection_ui.profile_read</t>
+          <t>connection_ui.profile_invalid</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>재접속 프로필을 읽을 수 없습니다. 파일 형식 또는 저장소 접근 권한을 확인하세요.</t>
+          <t>재접속 프로필 자료가 올바르지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>connection_ui.profile_path</t>
+          <t>connection_ui.profile_read</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>재접속 프로필 저장 위치를 사용할 수 없습니다.</t>
+          <t>재접속 프로필을 읽을 수 없습니다. 파일 형식 또는 저장소 접근 권한을 확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>connection_ui.run_started</t>
+          <t>connection_ui.profile_path</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>이미 출발한 세션에는 새로 참가할 수 없습니다.</t>
+          <t>재접속 프로필 저장 위치를 사용할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>connection_ui.connection_invalid</t>
+          <t>connection_ui.run_started</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>이미 등록되었거나 유효하지 않은 연결입니다.</t>
+          <t>이미 출발한 세션에는 새로 참가할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>connection_ui.full</t>
+          <t>connection_ui.connection_invalid</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>세션 정원이 찼습니다.</t>
+          <t>이미 등록되었거나 유효하지 않은 연결입니다.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect_denied</t>
+          <t>connection_ui.full</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>재접속 자격을 확인할 수 없습니다.</t>
+          <t>세션 정원이 찼습니다.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect_expired</t>
+          <t>connection_ui.reconnect_denied</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>재접속 예약이 없거나 만료되었습니다.</t>
+          <t>재접속 자격을 확인할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>connection_ui.version_mismatch</t>
+          <t>connection_ui.reconnect_expired</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>서버와 클라이언트의 빌드 버전이 다릅니다.</t>
+          <t>재접속 예약이 없거나 만료되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>connection_ui.passive_profile</t>
+          <t>connection_ui.version_mismatch</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>저장된 패시브 프로필을 읽지 못했습니다.</t>
+          <t>서버와 클라이언트의 빌드 버전이 다릅니다.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>connection_ui.timeout</t>
+          <t>connection_ui.passive_profile</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>서버 참가 승인 시간이 초과되었습니다.</t>
+          <t>저장된 패시브 프로필을 읽지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>connection_ui.admitted</t>
+          <t>connection_ui.timeout</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>참가 승인 완료</t>
+          <t>서버 참가 승인 시간이 초과되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>connection_ui.before_connect</t>
+          <t>connection_ui.admitted</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>서버 연결 전</t>
+          <t>참가 승인 완료</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>connection_ui.waiting</t>
+          <t>connection_ui.before_connect</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>서버 연결 대기 중</t>
+          <t>서버 연결 전</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>connection_ui.disconnected</t>
+          <t>connection_ui.waiting</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>서버와 연결이 끊어졌습니다.</t>
+          <t>서버 연결 대기 중</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>upgrade_ui.request_failed</t>
+          <t>connection_ui.disconnected</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>서버 강화 요청을 시작하지 못했습니다.</t>
+          <t>서버와 연결이 끊어졌습니다.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>upgrade_ui.request_pending</t>
+          <t>upgrade_ui.request_failed</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>서버가 강화 가능 여부와 골드를 확인하고 있습니다.</t>
+          <t>서버 강화 요청을 시작하지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>upgrade_ui.state_changed</t>
+          <t>upgrade_ui.request_pending</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>아이템 상태가 먼저 바뀌어 강화를 취소했습니다. 다시 선택해 주세요.</t>
+          <t>서버가 강화 가능 여부와 골드를 확인하고 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>upgrade_ui.item_missing</t>
+          <t>upgrade_ui.state_changed</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>인벤토리에서 해당 아이템을 찾지 못했습니다.</t>
+          <t>아이템 상태가 먼저 바뀌어 강화를 취소했습니다. 다시 선택해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>result_ui.stage</t>
+          <t>upgrade_ui.item_missing</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>최종 도달 스테이지</t>
+          <t>인벤토리에서 해당 아이템을 찾지 못했습니다.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>result_ui.defeated</t>
+          <t>result_ui.stage</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>처치한 적</t>
+          <t>최종 도달 스테이지</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>result_ui.play_time</t>
+          <t>result_ui.defeated</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>플레이 시간</t>
+          <t>처치한 적</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>result_ui.credits</t>
+          <t>result_ui.play_time</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>획득 크레딧</t>
+          <t>플레이 시간</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>result_ui.retry</t>
+          <t>result_ui.credits</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>다시 시작</t>
+          <t>획득 크레딧</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>result_ui.return_lobby</t>
+          <t>result_ui.retry</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>로비로 돌아가기</t>
+          <t>다시 시작</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>result_ui.leave_session</t>
+          <t>result_ui.return_lobby</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>세션 나가기</t>
+          <t>로비로 돌아가기</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>result_ui.clear_description</t>
+          <t>result_ui.leave_session</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>모든 스테이지를 클리어했습니다!</t>
+          <t>세션 나가기</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>result_ui.defeat_description</t>
+          <t>result_ui.clear_description</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>이번 원정이 종료되었습니다.</t>
+          <t>모든 스테이지를 클리어했습니다!</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>result_ui.data_waiting</t>
+          <t>result_ui.defeat_description</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>서버에서 결과를 받는 중입니다…</t>
+          <t>이번 원정이 종료되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>result_ui.data_missing</t>
+          <t>result_ui.data_waiting</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>결과를 아직 받지 못했습니다. 계속 기다리거나 나갈 수 있습니다.</t>
+          <t>서버에서 결과를 받는 중입니다…</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>result_ui.request_pending</t>
+          <t>result_ui.data_missing</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>서버 응답을 기다리고 있습니다…</t>
+          <t>결과를 아직 받지 못했습니다. 계속 기다리거나 나갈 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>result_ui.act_clear_description</t>
+          <t>result_ui.request_pending</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>액트를 클리어했습니다.</t>
+          <t>서버 응답을 기다리고 있습니다…</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>result_ui.settle_description</t>
+          <t>result_ui.act_clear_description</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>정산을 완료했습니다.</t>
+          <t>액트를 클리어했습니다.</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>result_ui.current_stage</t>
+          <t>result_ui.settle_description</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>현재 도달 스테이지</t>
+          <t>정산을 완료했습니다.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>result_ui.farming_value</t>
+          <t>result_ui.current_stage</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>파밍 가치 현황</t>
+          <t>현재 도달 스테이지</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>result_ui.continue</t>
+          <t>result_ui.farming_value</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>계속하기</t>
+          <t>파밍 가치 현황</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>session_ui.end_host</t>
+          <t>result_ui.continue</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>호스트 세션 종료</t>
+          <t>계속하기</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>session_ui.leave</t>
+          <t>session_ui.end_host</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>세션 떠나기</t>
+          <t>호스트 세션 종료</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>session_ui.leave_temporarily</t>
+          <t>session_ui.leave</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>잠시 나가기</t>
+          <t>세션 떠나기</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>session_ui.confirm_end_host</t>
+          <t>session_ui.leave_temporarily</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>호스트 세션을 종료하시겠습니까?</t>
+          <t>잠시 나가기</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>session_ui.warn_end_host</t>
+          <t>session_ui.confirm_end_host</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>모든 참가자의 연결과 현재 런이 종료됩니다.</t>
+          <t>호스트 세션을 종료하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>session_ui.confirm_leave</t>
+          <t>session_ui.warn_end_host</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>이 세션에서 떠나시겠습니까?</t>
+          <t>모든 참가자의 연결과 현재 런이 종료됩니다.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>session_ui.warn_leave</t>
+          <t>session_ui.confirm_leave</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</t>
+          <t>이 세션에서 떠나시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>session_ui.confirm_temporary_leave</t>
+          <t>session_ui.warn_leave</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>잠시 세션에서 나가시겠습니까?</t>
+          <t>현재 참가 자격을 포기하며 이 런에 재접속할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>session_ui.warn_temporary_leave</t>
+          <t>session_ui.confirm_temporary_leave</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</t>
+          <t>잠시 세션에서 나가시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>session_ui.passive_locked</t>
+          <t>session_ui.warn_temporary_leave</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>준비를 취소한 뒤 패시브를 변경할 수 있습니다.</t>
+          <t>서버가 유지되는 동안 5분 안에 재접속할 수 있습니다. 파티의 게임은 계속됩니다.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait</t>
+          <t>session_ui.passive_locked</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</t>
+          <t>준비를 취소한 뒤 패시브를 변경할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_host</t>
+          <t>session_ui.settlement_wait</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>참가자의 결과 저장을 기다리고 있습니다. 저장 후 세션을 종료해 주세요.</t>
+          <t>결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_player</t>
+          <t>session_ui.settlement_wait_host</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>{0}의 결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</t>
+          <t>참가자의 결과 저장을 기다리고 있습니다. 저장 후 세션을 종료해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>session_ui.lobby_loading</t>
+          <t>session_ui.settlement_wait_player</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>로비 이동이 끝난 뒤 출발할 수 있습니다.</t>
+          <t>{0}의 결과 저장을 기다리고 있습니다. 잠시 후 다시 시도해 주세요.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>session_ui.player_prefabs_missing</t>
+          <t>session_ui.lobby_loading</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>두 클래스의 네트워크 프리팹 연결을 확인하세요.</t>
+          <t>로비 이동이 끝난 뒤 출발할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>session_ui.session_missing</t>
+          <t>session_ui.player_prefabs_missing</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>참여 중인 세션을 찾을 수 없습니다.</t>
+          <t>두 클래스의 네트워크 프리팹 연결을 확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>session_ui.unsupported_request</t>
+          <t>session_ui.session_missing</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>지원하지 않는 로비 요청입니다.</t>
+          <t>참여 중인 세션을 찾을 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>session_ui.return_lobby_denied</t>
+          <t>session_ui.unsupported_request</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>서버가 결과를 확정한 뒤 방장만 파티를 로비로 이동할 수 있습니다.</t>
+          <t>지원하지 않는 로비 요청입니다.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>session_ui.passive_invalid</t>
+          <t>session_ui.return_lobby_denied</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>패시브 프로필을 확인할 수 없습니다.</t>
+          <t>서버가 결과를 확정한 뒤 방장만 파티를 로비로 이동할 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>session_ui.party_not_ready</t>
+          <t>session_ui.passive_invalid</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>모든 참가자가 캐릭터 선택과 준비를 완료해야 합니다.</t>
+          <t>패시브 프로필을 확인할 수 없습니다.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>preparation_ui.waiting</t>
+          <t>session_ui.party_not_ready</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>플레이를 준비하고 있습니다…</t>
+          <t>모든 참가자가 캐릭터 선택과 준비를 완료해야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout</t>
+          <t>preparation_ui.waiting</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>플레이 준비 시간이 초과되었습니다.</t>
+          <t>플레이를 준비하고 있습니다…</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout_retry</t>
+          <t>preparation_ui.timeout</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>플레이 준비 시간이 초과되었습니다. 연결을 종료하고 다시 시도하세요.</t>
+          <t>플레이 준비 시간이 초과되었습니다.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>preparation_ui.combat_failed</t>
+          <t>preparation_ui.timeout_retry</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>전투 웨이브 또는 생성 지점 준비에 실패했습니다.</t>
+          <t>플레이 준비 시간이 초과되었습니다. 연결을 종료하고 다시 시도하세요.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>preparation_ui.disconnected</t>
+          <t>preparation_ui.combat_failed</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>연결이 종료되었습니다.</t>
+          <t>전투 웨이브 또는 생성 지점 준비에 실패했습니다.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>연결이 종료되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
           <t>preparation_ui.exit</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>나가기</t>
         </is>
@@ -4092,7 +4104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B305"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6007,1751 +6019,1763 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rest_ui.potion_recharge</t>
+          <t>rest_ui.health_recovery_format</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Potion Charges</t>
+          <t>Restore {0}% HP</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rest_ui.cost_format</t>
+          <t>rest_ui.potion_recharge</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Required Credits : {0}</t>
+          <t>Potion Charges</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rest_ui.complete_message</t>
+          <t>rest_ui.cost_format</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Spent {0} credits to restore {1} HP and {2} potion charge(s).</t>
+          <t>Required Credits : {0}</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_chat</t>
+          <t>rest_ui.complete_message</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Chat] </t>
+          <t>Spent {0} credits to restore {1} HP and {2} potion charge(s).</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_acquisition</t>
+          <t>chat_ui.prefix_chat</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Item] </t>
+          <t xml:space="preserve">[Chat] </t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_warning</t>
+          <t>chat_ui.prefix_acquisition</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Notice] </t>
+          <t xml:space="preserve">[Item] </t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_connection</t>
+          <t>chat_ui.prefix_warning</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Network] </t>
+          <t xml:space="preserve">[Notice] </t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>chat_ui.item_fallback_name</t>
+          <t>chat_ui.prefix_connection</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>item</t>
+          <t xml:space="preserve">[Network] </t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_cost_format</t>
+          <t>chat_ui.item_fallback_name</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Reroll &lt;color=#FFEB04&gt;{0}&lt;/color&gt;</t>
+          <t>item</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_free</t>
+          <t>shop_ui.reroll_cost_format</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Free Reroll</t>
+          <t>Reroll &lt;color=#FFEB04&gt;{0}&lt;/color&gt;</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_count_format</t>
+          <t>shop_ui.reroll_free</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>[ {0} ]</t>
+          <t>Free Reroll</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>settings_ui.reset_confirm</t>
+          <t>shop_ui.reroll_count_format</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Reset all settings to their defaults?</t>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>settings_ui.reset_warning</t>
+          <t>settings_ui.reset_confirm</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>All current settings will be restored to their defaults.</t>
+          <t>Reset all settings to their defaults?</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_confirm</t>
+          <t>settings_ui.reset_warning</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Give up this game?</t>
+          <t>All current settings will be restored to their defaults.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_warning</t>
+          <t>pause_ui.giveup_confirm</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Warning: Your current game data will be lost.</t>
+          <t>Give up this game?</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm</t>
+          <t>pause_ui.giveup_warning</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Are you sure you want to give up?</t>
+          <t>Warning: Your current game data will be lost.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm_warning</t>
+          <t>pause_ui.giveup_reconfirm</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>The current run will be reset and no credits will be earned.</t>
+          <t>Are you sure you want to give up?</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>pause_ui.save_and_quit_confirm</t>
+          <t>pause_ui.giveup_reconfirm_warning</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Save and quit the game?</t>
+          <t>The current run will be reset and no credits will be earned.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_confirm</t>
+          <t>pause_ui.save_and_quit_confirm</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>End the host session?</t>
+          <t>Save and quit the game?</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_warning</t>
+          <t>pause_ui.host_end_confirm</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>All participants will be disconnected and the current run will end.</t>
+          <t>End the host session?</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>pause_ui.leave_confirm</t>
+          <t>pause_ui.host_end_warning</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Leave this session?</t>
+          <t>All participants will be disconnected and the current run will end.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>pause_ui.leave_warning</t>
+          <t>pause_ui.leave_confirm</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>You will give up your spot and cannot rejoin this run.</t>
+          <t>Leave this session?</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_confirm</t>
+          <t>pause_ui.leave_warning</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Step out of the session for now?</t>
+          <t>You will give up your spot and cannot rejoin this run.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_warning</t>
+          <t>pause_ui.temp_leave_confirm</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>You can rejoin within 5 minutes while the server is running. The party's game will continue.</t>
+          <t>Step out of the session for now?</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>pause_ui.adjustment</t>
+          <t>pause_ui.temp_leave_warning</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Settle &amp; End Run</t>
+          <t>You can rejoin within 5 minutes while the server is running. The party's game will continue.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>pause_ui.settle_confirm</t>
+          <t>pause_ui.adjustment</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Settle and end the game?</t>
+          <t>Settle &amp; End Run</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>pause_ui.settle_warning</t>
+          <t>pause_ui.settle_confirm</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>You will receive your credits plus 50% of your items' base value as account credits, and the current run will be reset.</t>
+          <t>Settle and end the game?</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>login_ui.title</t>
+          <t>pause_ui.settle_warning</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>User Authentication</t>
+          <t>You will receive your credits plus 50% of your items' base value as account credits, and the current run will be reset.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>login_ui.subtitle</t>
+          <t>login_ui.title</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>OPERATOR AUTHENTICATION</t>
+          <t>User Authentication</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>login_ui.account</t>
+          <t>login_ui.subtitle</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Account ID</t>
+          <t>OPERATOR AUTHENTICATION</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>login_ui.email_placeholder</t>
+          <t>login_ui.account</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Account ID</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>login_ui.password</t>
+          <t>login_ui.email_placeholder</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Password</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>login_ui.confirm_password</t>
+          <t>login_ui.password</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Confirm Password</t>
+          <t>Password</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>login_ui.submit</t>
+          <t>login_ui.confirm_password</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Log In</t>
+          <t>Confirm Password</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>login_ui.no_account</t>
+          <t>login_ui.submit</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Don't have an account?</t>
+          <t>Log In</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>login_ui.create_account</t>
+          <t>login_ui.no_account</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Create Account</t>
+          <t>Don't have an account?</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>login_ui.create</t>
+          <t>login_ui.create_account</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Create</t>
+          <t>Create Account</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>login_ui.has_account</t>
+          <t>login_ui.create</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Already have an account?</t>
+          <t>Create</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>login_ui.login</t>
+          <t>login_ui.has_account</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Log In</t>
+          <t>Already have an account?</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>login_ui.footer</t>
+          <t>login_ui.login</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SECURE ACCESS TERMINAL</t>
+          <t>Log In</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>login_ui.submitting</t>
+          <t>login_ui.footer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Logging in...</t>
+          <t>SECURE ACCESS TERMINAL</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>login_ui.creating</t>
+          <t>login_ui.submitting</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Creating account...</t>
+          <t>Logging in...</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>login_ui.required</t>
+          <t>login_ui.creating</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Enter your email and password.</t>
+          <t>Creating account...</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>login_ui.account_required</t>
+          <t>login_ui.required</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Enter your account ID and password.</t>
+          <t>Enter your email and password.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>login_ui.confirm_required</t>
+          <t>login_ui.account_required</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Confirm your password.</t>
+          <t>Enter your account ID and password.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>login_ui.password_mismatch</t>
+          <t>login_ui.confirm_required</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Passwords do not match.</t>
+          <t>Confirm your password.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>login_ui.login_error</t>
+          <t>login_ui.password_mismatch</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>An error occurred while logging in.</t>
+          <t>Passwords do not match.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>login_ui.profile_incomplete</t>
+          <t>login_ui.login_error</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Account created, but profile setup failed. Please log in again.</t>
+          <t>An error occurred while logging in.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>login_ui.created</t>
+          <t>login_ui.profile_incomplete</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Account created. Log in with your new account.</t>
+          <t>Account created, but profile setup failed. Please log in again.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>login_ui.create_error</t>
+          <t>login_ui.created</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>An error occurred while creating your account.</t>
+          <t>Account created. Log in with your new account.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>login_ui.loader_missing</t>
+          <t>login_ui.create_error</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Scene loader is unavailable. Launch from the Start scene.</t>
+          <t>An error occurred while creating your account.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>login_ui.scenes_missing</t>
+          <t>login_ui.loader_missing</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Check that TitleScene and LoadingScene are included in the build.</t>
+          <t>Scene loader is unavailable. Launch from the Start scene.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>login_ui.user_missing</t>
+          <t>login_ui.scenes_missing</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>User information was missing from the login response.</t>
+          <t>Check that TitleScene and LoadingScene are included in the build.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
+          <t>login_ui.user_missing</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>User information was missing from the login response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>login_ui.auth_failed</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>Login failed.
 Check your email, password and Firebase authentication settings.</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>login_ui.firebase_login_error</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>A Firebase login error occurred.</t>
-        </is>
-      </c>
-    </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>login_ui.created_user_missing</t>
+          <t>login_ui.firebase_login_error</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>User information was missing from the account creation response.</t>
+          <t>A Firebase login error occurred.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>login_ui.firebase_create_error</t>
+          <t>login_ui.created_user_missing</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>A Firebase account creation error occurred.</t>
+          <t>User information was missing from the account creation response.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>login_ui.email_in_use</t>
+          <t>login_ui.firebase_create_error</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>This email is already in use.</t>
+          <t>A Firebase account creation error occurred.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>login_ui.invalid_email</t>
+          <t>login_ui.email_in_use</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Enter a valid email address.</t>
+          <t>This email is already in use.</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>login_ui.password_policy</t>
+          <t>login_ui.invalid_email</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Choose a password that meets the password policy.</t>
+          <t>Enter a valid email address.</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>login_ui.auth_disabled</t>
+          <t>login_ui.password_policy</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Enable email/password sign-in in Firebase Console.</t>
+          <t>Choose a password that meets the password policy.</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>login_ui.network_error</t>
+          <t>login_ui.auth_disabled</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Check your network connection and try again.</t>
+          <t>Enable email/password sign-in in Firebase Console.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>login_ui.too_many_requests</t>
+          <t>login_ui.network_error</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Too many requests. Please try again later.</t>
+          <t>Check your network connection and try again.</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>login_ui.create_failed</t>
+          <t>login_ui.too_many_requests</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Account creation failed. Check your input and Firebase authentication settings.</t>
+          <t>Too many requests. Please try again later.</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>login_ui.config_missing</t>
+          <t>login_ui.create_failed</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Firebase configuration is missing. Add google-services.json or GoogleService-Info.plist to Assets.</t>
+          <t>Account creation failed. Check your input and Firebase authentication settings.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>login_ui.dependencies</t>
+          <t>login_ui.config_missing</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Could not initialize Firebase dependencies: {0}</t>
+          <t>Firebase configuration is missing. Add google-services.json or GoogleService-Info.plist to Assets.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>login_ui.init_failed</t>
+          <t>login_ui.dependencies</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Firebase initialization failed. Check configuration and project connection.</t>
+          <t>Could not initialize Firebase dependencies: {0}</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>connection_ui.title</t>
+          <t>login_ui.init_failed</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Multiplayer Connection</t>
+          <t>Firebase initialization failed. Check configuration and project connection.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>connection_ui.subtitle</t>
+          <t>connection_ui.title</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>MULTIPLAYER CONNECTION</t>
+          <t>Multiplayer Connection</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>connection_ui.address</t>
+          <t>connection_ui.subtitle</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Server Address</t>
+          <t>MULTIPLAYER CONNECTION</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>connection_ui.address_placeholder</t>
+          <t>connection_ui.address</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Server IP or hostname</t>
+          <t>Server Address</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>connection_ui.nickname</t>
+          <t>connection_ui.address_placeholder</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Nickname</t>
+          <t>Server IP or hostname</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>connection_ui.host</t>
+          <t>connection_ui.nickname</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Local Test · Host</t>
+          <t>Nickname</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>connection_ui.join</t>
+          <t>connection_ui.host</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Connect to Server</t>
+          <t>Local Test · Host</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>connection_ui.server</t>
+          <t>connection_ui.join</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Local Test · Server</t>
+          <t>Connect to Server</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect</t>
+          <t>connection_ui.server</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Rejoin Last Session</t>
+          <t>Local Test · Server</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>connection_ui.return_title</t>
+          <t>connection_ui.reconnect</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Return to Title</t>
+          <t>Rejoin Last Session</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>connection_ui.settings_missing</t>
+          <t>connection_ui.return_title</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Session connection settings are unavailable.</t>
+          <t>Return to Title</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>connection_ui.invalid_nickname</t>
+          <t>connection_ui.settings_missing</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Enter a nickname of 1–24 characters without tags or line breaks.</t>
+          <t>Session connection settings are unavailable.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>connection_ui.invalid_address</t>
+          <t>connection_ui.invalid_nickname</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Enter a server IP or hostname without a port number.</t>
+          <t>Enter a nickname of 1–24 characters without tags or line breaks.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>connection_ui.connecting</t>
+          <t>connection_ui.invalid_address</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Connecting…</t>
+          <t>Enter a server IP or hostname without a port number.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>connection_ui.server_running</t>
+          <t>connection_ui.connecting</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Dedicated server running · Waiting for players</t>
+          <t>Connecting…</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>connection_ui.no_session</t>
+          <t>connection_ui.server_running</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>No recent session is saved for this profile.</t>
+          <t>Dedicated server running · Waiting for players</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>connection_ui.profile_large</t>
+          <t>connection_ui.no_session</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>The reconnect profile is too large.</t>
+          <t>No recent session is saved for this profile.</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>connection_ui.profile_invalid</t>
+          <t>connection_ui.profile_large</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>The reconnect profile is invalid.</t>
+          <t>The reconnect profile is too large.</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>connection_ui.profile_read</t>
+          <t>connection_ui.profile_invalid</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Cannot read the reconnect profile. Check its format and storage permissions.</t>
+          <t>The reconnect profile is invalid.</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>connection_ui.profile_path</t>
+          <t>connection_ui.profile_read</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>The reconnect profile storage location is unavailable.</t>
+          <t>Cannot read the reconnect profile. Check its format and storage permissions.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>connection_ui.run_started</t>
+          <t>connection_ui.profile_path</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>You cannot join a session that has already started.</t>
+          <t>The reconnect profile storage location is unavailable.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>connection_ui.connection_invalid</t>
+          <t>connection_ui.run_started</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>This connection is already registered or invalid.</t>
+          <t>You cannot join a session that has already started.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>connection_ui.full</t>
+          <t>connection_ui.connection_invalid</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>The session is full.</t>
+          <t>This connection is already registered or invalid.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect_denied</t>
+          <t>connection_ui.full</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Reconnect eligibility could not be verified.</t>
+          <t>The session is full.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect_expired</t>
+          <t>connection_ui.reconnect_denied</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>The reconnect reservation is missing or expired.</t>
+          <t>Reconnect eligibility could not be verified.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>connection_ui.version_mismatch</t>
+          <t>connection_ui.reconnect_expired</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Server and client build versions do not match.</t>
+          <t>The reconnect reservation is missing or expired.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>connection_ui.passive_profile</t>
+          <t>connection_ui.version_mismatch</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Could not load the saved passive skill profile.</t>
+          <t>Server and client build versions do not match.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>connection_ui.timeout</t>
+          <t>connection_ui.passive_profile</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Server admission timed out.</t>
+          <t>Could not load the saved passive skill profile.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>connection_ui.admitted</t>
+          <t>connection_ui.timeout</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Admission approved</t>
+          <t>Server admission timed out.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>connection_ui.before_connect</t>
+          <t>connection_ui.admitted</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Not connected</t>
+          <t>Admission approved</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>connection_ui.waiting</t>
+          <t>connection_ui.before_connect</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Waiting for server connection</t>
+          <t>Not connected</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>connection_ui.disconnected</t>
+          <t>connection_ui.waiting</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Disconnected from the server.</t>
+          <t>Waiting for server connection</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>upgrade_ui.request_failed</t>
+          <t>connection_ui.disconnected</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Could not send the upgrade request.</t>
+          <t>Disconnected from the server.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>upgrade_ui.request_pending</t>
+          <t>upgrade_ui.request_failed</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Checking the item and available gold…</t>
+          <t>Could not send the upgrade request.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>upgrade_ui.state_changed</t>
+          <t>upgrade_ui.request_pending</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>The item changed. Select it again to upgrade.</t>
+          <t>Checking the item and available gold…</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>upgrade_ui.item_missing</t>
+          <t>upgrade_ui.state_changed</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>The item is no longer in your inventory.</t>
+          <t>The item changed. Select it again to upgrade.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>result_ui.stage</t>
+          <t>upgrade_ui.item_missing</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Stage Reached</t>
+          <t>The item is no longer in your inventory.</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>result_ui.defeated</t>
+          <t>result_ui.stage</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Enemies Defeated</t>
+          <t>Stage Reached</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>result_ui.play_time</t>
+          <t>result_ui.defeated</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Play Time</t>
+          <t>Enemies Defeated</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>result_ui.credits</t>
+          <t>result_ui.play_time</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Credits Earned</t>
+          <t>Play Time</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>result_ui.retry</t>
+          <t>result_ui.credits</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Play Again</t>
+          <t>Credits Earned</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>result_ui.return_lobby</t>
+          <t>result_ui.retry</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Return to Lobby</t>
+          <t>Play Again</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>result_ui.leave_session</t>
+          <t>result_ui.return_lobby</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Leave Session</t>
+          <t>Return to Lobby</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>result_ui.clear_description</t>
+          <t>result_ui.leave_session</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>All stages cleared!</t>
+          <t>Leave Session</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>result_ui.defeat_description</t>
+          <t>result_ui.clear_description</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>This expedition has ended.</t>
+          <t>All stages cleared!</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>result_ui.data_waiting</t>
+          <t>result_ui.defeat_description</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Receiving results from the server…</t>
+          <t>This expedition has ended.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>result_ui.data_missing</t>
+          <t>result_ui.data_waiting</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Results have not arrived yet. You can wait or leave.</t>
+          <t>Receiving results from the server…</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>result_ui.request_pending</t>
+          <t>result_ui.data_missing</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Waiting for the server…</t>
+          <t>Results have not arrived yet. You can wait or leave.</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>result_ui.act_clear_description</t>
+          <t>result_ui.request_pending</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Act cleared!</t>
+          <t>Waiting for the server…</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>result_ui.settle_description</t>
+          <t>result_ui.act_clear_description</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Settlement complete.</t>
+          <t>Act cleared!</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>result_ui.current_stage</t>
+          <t>result_ui.settle_description</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Current Stage</t>
+          <t>Settlement complete.</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>result_ui.farming_value</t>
+          <t>result_ui.current_stage</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Loot Value</t>
+          <t>Current Stage</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>result_ui.continue</t>
+          <t>result_ui.farming_value</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Continue</t>
+          <t>Loot Value</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>session_ui.end_host</t>
+          <t>result_ui.continue</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>End Host Session</t>
+          <t>Continue</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>session_ui.leave</t>
+          <t>session_ui.end_host</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Leave Session</t>
+          <t>End Host Session</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>session_ui.leave_temporarily</t>
+          <t>session_ui.leave</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Disconnect Temporarily</t>
+          <t>Leave Session</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>session_ui.confirm_end_host</t>
+          <t>session_ui.leave_temporarily</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>End this host session?</t>
+          <t>Disconnect Temporarily</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>session_ui.warn_end_host</t>
+          <t>session_ui.confirm_end_host</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>All players will disconnect and the current run will end.</t>
+          <t>End this host session?</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>session_ui.confirm_leave</t>
+          <t>session_ui.warn_end_host</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Leave this session?</t>
+          <t>All players will disconnect and the current run will end.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>session_ui.warn_leave</t>
+          <t>session_ui.confirm_leave</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>You will forfeit your place and cannot rejoin this run.</t>
+          <t>Leave this session?</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>session_ui.confirm_temporary_leave</t>
+          <t>session_ui.warn_leave</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Disconnect from this session temporarily?</t>
+          <t>You will forfeit your place and cannot rejoin this run.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>session_ui.warn_temporary_leave</t>
+          <t>session_ui.confirm_temporary_leave</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>You can reconnect within 5 minutes while the server stays online. The party will keep playing.</t>
+          <t>Disconnect from this session temporarily?</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>session_ui.passive_locked</t>
+          <t>session_ui.warn_temporary_leave</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Cancel Ready before changing passives.</t>
+          <t>You can reconnect within 5 minutes while the server stays online. The party will keep playing.</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait</t>
+          <t>session_ui.passive_locked</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Results are still being saved. Please try again shortly.</t>
+          <t>Cancel Ready before changing passives.</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_host</t>
+          <t>session_ui.settlement_wait</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Waiting for player results to save. End the session after saving finishes.</t>
+          <t>Results are still being saved. Please try again shortly.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_player</t>
+          <t>session_ui.settlement_wait_host</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Waiting for {0}'s results to save. Please try again shortly.</t>
+          <t>Waiting for player results to save. End the session after saving finishes.</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>session_ui.lobby_loading</t>
+          <t>session_ui.settlement_wait_player</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Wait for the lobby to finish loading before starting.</t>
+          <t>Waiting for {0}'s results to save. Please try again shortly.</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>session_ui.player_prefabs_missing</t>
+          <t>session_ui.lobby_loading</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Player setup is incomplete. Please reconnect.</t>
+          <t>Wait for the lobby to finish loading before starting.</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>session_ui.session_missing</t>
+          <t>session_ui.player_prefabs_missing</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>The current session could not be found.</t>
+          <t>Player setup is incomplete. Please reconnect.</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>session_ui.unsupported_request</t>
+          <t>session_ui.session_missing</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>This lobby action is unavailable.</t>
+          <t>The current session could not be found.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>session_ui.return_lobby_denied</t>
+          <t>session_ui.unsupported_request</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Only the leader can return the party to the lobby after results are confirmed.</t>
+          <t>This lobby action is unavailable.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>session_ui.passive_invalid</t>
+          <t>session_ui.return_lobby_denied</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Your passive profile could not be verified.</t>
+          <t>Only the leader can return the party to the lobby after results are confirmed.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>session_ui.party_not_ready</t>
+          <t>session_ui.passive_invalid</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>All players must choose a character and be ready.</t>
+          <t>Your passive profile could not be verified.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>preparation_ui.waiting</t>
+          <t>session_ui.party_not_ready</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Preparing the game…</t>
+          <t>All players must choose a character and be ready.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout</t>
+          <t>preparation_ui.waiting</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Game preparation timed out.</t>
+          <t>Preparing the game…</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout_retry</t>
+          <t>preparation_ui.timeout</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Game preparation timed out. Disconnect and try again.</t>
+          <t>Game preparation timed out.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>preparation_ui.combat_failed</t>
+          <t>preparation_ui.timeout_retry</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>The battle could not be prepared. Please reconnect.</t>
+          <t>Game preparation timed out. Disconnect and try again.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>preparation_ui.disconnected</t>
+          <t>preparation_ui.combat_failed</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>The connection has ended.</t>
+          <t>The battle could not be prepared. Please reconnect.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>The connection has ended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
           <t>preparation_ui.exit</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>Leave</t>
         </is>
@@ -7768,7 +7792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B305"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9683,1751 +9707,1763 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rest_ui.potion_recharge</t>
+          <t>rest_ui.health_recovery_format</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ポーション補充</t>
+          <t>体力{0}%回復</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rest_ui.cost_format</t>
+          <t>rest_ui.potion_recharge</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>必要クレジット : {0}</t>
+          <t>ポーション補充</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rest_ui.complete_message</t>
+          <t>rest_ui.cost_format</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>{0}クレジットを消費して体力{1}、ポーション{2}個を補充しました。</t>
+          <t>必要クレジット : {0}</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_chat</t>
+          <t>rest_ui.complete_message</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">[チャット] </t>
+          <t>{0}クレジットを消費して体力{1}、ポーション{2}個を補充しました。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_acquisition</t>
+          <t>chat_ui.prefix_chat</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">[アイテム] </t>
+          <t xml:space="preserve">[チャット] </t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_warning</t>
+          <t>chat_ui.prefix_acquisition</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">[お知らせ] </t>
+          <t xml:space="preserve">[アイテム] </t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_connection</t>
+          <t>chat_ui.prefix_warning</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">[接続] </t>
+          <t xml:space="preserve">[お知らせ] </t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>chat_ui.item_fallback_name</t>
+          <t>chat_ui.prefix_connection</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>アイテム</t>
+          <t xml:space="preserve">[接続] </t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_cost_format</t>
+          <t>chat_ui.item_fallback_name</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 再抽選</t>
+          <t>アイテム</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_free</t>
+          <t>shop_ui.reroll_cost_format</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>無料 再抽選</t>
+          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 再抽選</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_count_format</t>
+          <t>shop_ui.reroll_free</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>[ {0} ]</t>
+          <t>無料 再抽選</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>settings_ui.reset_confirm</t>
+          <t>shop_ui.reroll_count_format</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>設定を初期値に戻しますか？</t>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>settings_ui.reset_warning</t>
+          <t>settings_ui.reset_confirm</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>現在の設定はすべて初期値に戻ります。</t>
+          <t>設定を初期値に戻しますか？</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_confirm</t>
+          <t>settings_ui.reset_warning</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ゲームをあきらめますか？</t>
+          <t>現在の設定はすべて初期値に戻ります。</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_warning</t>
+          <t>pause_ui.giveup_confirm</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>警告：現在のゲームデータは失われます。</t>
+          <t>ゲームをあきらめますか？</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm</t>
+          <t>pause_ui.giveup_warning</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>本当に諦めますか？</t>
+          <t>警告：現在のゲームデータは失われます。</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm_warning</t>
+          <t>pause_ui.giveup_reconfirm</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>進行中の遠征はリセットされ、クレジットは獲得できません。</t>
+          <t>本当に諦めますか？</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>pause_ui.save_and_quit_confirm</t>
+          <t>pause_ui.giveup_reconfirm_warning</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ゲームを保存して終了しますか？</t>
+          <t>進行中の遠征はリセットされ、クレジットは獲得できません。</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_confirm</t>
+          <t>pause_ui.save_and_quit_confirm</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ホストセッションを終了しますか？</t>
+          <t>ゲームを保存して終了しますか？</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_warning</t>
+          <t>pause_ui.host_end_confirm</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>すべての参加者の接続と現在のランが終了します。</t>
+          <t>ホストセッションを終了しますか？</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>pause_ui.leave_confirm</t>
+          <t>pause_ui.host_end_warning</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>このセッションから退出しますか？</t>
+          <t>すべての参加者の接続と現在のランが終了します。</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>pause_ui.leave_warning</t>
+          <t>pause_ui.leave_confirm</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>参加資格を放棄し、このランには再接続できません。</t>
+          <t>このセッションから退出しますか？</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_confirm</t>
+          <t>pause_ui.leave_warning</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>一時的にセッションから退出しますか？</t>
+          <t>参加資格を放棄し、このランには再接続できません。</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_warning</t>
+          <t>pause_ui.temp_leave_confirm</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>サーバーが維持されている間は5分以内に再接続できます。パーティーのゲームは続行されます。</t>
+          <t>一時的にセッションから退出しますか？</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>pause_ui.adjustment</t>
+          <t>pause_ui.temp_leave_warning</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>精算して終了</t>
+          <t>サーバーが維持されている間は5分以内に再接続できます。パーティーのゲームは続行されます。</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>pause_ui.settle_confirm</t>
+          <t>pause_ui.adjustment</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>精算してゲームを終了しますか？</t>
+          <t>精算して終了</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>pause_ui.settle_warning</t>
+          <t>pause_ui.settle_confirm</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>所持クレジットとアイテム原価の50%をアカウントクレジットとして受け取り、現在の遠征はリセットされます。</t>
+          <t>精算してゲームを終了しますか？</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>login_ui.title</t>
+          <t>pause_ui.settle_warning</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ユーザー認証</t>
+          <t>所持クレジットとアイテム原価の50%をアカウントクレジットとして受け取り、現在の遠征はリセットされます。</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>login_ui.subtitle</t>
+          <t>login_ui.title</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ユーザー認証端末</t>
+          <t>ユーザー認証</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>login_ui.account</t>
+          <t>login_ui.subtitle</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>アカウントID</t>
+          <t>ユーザー認証端末</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>login_ui.email_placeholder</t>
+          <t>login_ui.account</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>メールアドレス</t>
+          <t>アカウントID</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>login_ui.password</t>
+          <t>login_ui.email_placeholder</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>パスワード</t>
+          <t>メールアドレス</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>login_ui.confirm_password</t>
+          <t>login_ui.password</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>パスワード確認</t>
+          <t>パスワード</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>login_ui.submit</t>
+          <t>login_ui.confirm_password</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ログイン</t>
+          <t>パスワード確認</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>login_ui.no_account</t>
+          <t>login_ui.submit</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>アカウントをお持ちでない方</t>
+          <t>ログイン</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>login_ui.create_account</t>
+          <t>login_ui.no_account</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>アカウント作成</t>
+          <t>アカウントをお持ちでない方</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>login_ui.create</t>
+          <t>login_ui.create_account</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>作成</t>
+          <t>アカウント作成</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>login_ui.has_account</t>
+          <t>login_ui.create</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>アカウントをお持ちの方</t>
+          <t>作成</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>login_ui.login</t>
+          <t>login_ui.has_account</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ログイン</t>
+          <t>アカウントをお持ちの方</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>login_ui.footer</t>
+          <t>login_ui.login</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>セキュアアクセス端末</t>
+          <t>ログイン</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>login_ui.submitting</t>
+          <t>login_ui.footer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ログイン中…</t>
+          <t>セキュアアクセス端末</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>login_ui.creating</t>
+          <t>login_ui.submitting</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>アカウント作成中…</t>
+          <t>ログイン中…</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>login_ui.required</t>
+          <t>login_ui.creating</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>メールアドレスとパスワードを入力してください。</t>
+          <t>アカウント作成中…</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>login_ui.account_required</t>
+          <t>login_ui.required</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>アカウントIDとパスワードを入力してください。</t>
+          <t>メールアドレスとパスワードを入力してください。</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>login_ui.confirm_required</t>
+          <t>login_ui.account_required</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>確認用パスワードを入力してください。</t>
+          <t>アカウントIDとパスワードを入力してください。</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>login_ui.password_mismatch</t>
+          <t>login_ui.confirm_required</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>パスワードが一致しません。</t>
+          <t>確認用パスワードを入力してください。</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>login_ui.login_error</t>
+          <t>login_ui.password_mismatch</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ログイン処理中にエラーが発生しました。</t>
+          <t>パスワードが一致しません。</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>login_ui.profile_incomplete</t>
+          <t>login_ui.login_error</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>アカウントは作成されましたが、プロフィールの準備に失敗しました。再度ログインしてください。</t>
+          <t>ログイン処理中にエラーが発生しました。</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>login_ui.created</t>
+          <t>login_ui.profile_incomplete</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>アカウントを作成しました。新しいアカウントでログインしてください。</t>
+          <t>アカウントは作成されましたが、プロフィールの準備に失敗しました。再度ログインしてください。</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>login_ui.create_error</t>
+          <t>login_ui.created</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>アカウント作成中にエラーが発生しました。</t>
+          <t>アカウントを作成しました。新しいアカウントでログインしてください。</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>login_ui.loader_missing</t>
+          <t>login_ui.create_error</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>シーンローダーが未準備です。Startシーンから実行してください。</t>
+          <t>アカウント作成中にエラーが発生しました。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>login_ui.scenes_missing</t>
+          <t>login_ui.loader_missing</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>TitleSceneとLoadingSceneのビルド登録を確認してください。</t>
+          <t>シーンローダーが未準備です。Startシーンから実行してください。</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>login_ui.user_missing</t>
+          <t>login_ui.scenes_missing</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ログイン結果からユーザー情報を取得できませんでした。</t>
+          <t>TitleSceneとLoadingSceneのビルド登録を確認してください。</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
+          <t>login_ui.user_missing</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ログイン結果からユーザー情報を取得できませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>login_ui.auth_failed</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>ログインに失敗しました。
 メールアドレス、パスワード、Firebase認証設定を確認してください。</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>login_ui.firebase_login_error</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Firebaseログイン中にエラーが発生しました。</t>
-        </is>
-      </c>
-    </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>login_ui.created_user_missing</t>
+          <t>login_ui.firebase_login_error</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>アカウント作成結果からユーザー情報を取得できませんでした。</t>
+          <t>Firebaseログイン中にエラーが発生しました。</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>login_ui.firebase_create_error</t>
+          <t>login_ui.created_user_missing</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Firebaseアカウント作成中にエラーが発生しました。</t>
+          <t>アカウント作成結果からユーザー情報を取得できませんでした。</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>login_ui.email_in_use</t>
+          <t>login_ui.firebase_create_error</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>このメールアドレスは既に使用されています。</t>
+          <t>Firebaseアカウント作成中にエラーが発生しました。</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>login_ui.invalid_email</t>
+          <t>login_ui.email_in_use</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>有効なメールアドレスを入力してください。</t>
+          <t>このメールアドレスは既に使用されています。</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>login_ui.password_policy</t>
+          <t>login_ui.invalid_email</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>パスワードの要件を満たすパスワードを入力してください。</t>
+          <t>有効なメールアドレスを入力してください。</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>login_ui.auth_disabled</t>
+          <t>login_ui.password_policy</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Firebase Consoleでメールとパスワードによるログインを有効にしてください。</t>
+          <t>パスワードの要件を満たすパスワードを入力してください。</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>login_ui.network_error</t>
+          <t>login_ui.auth_disabled</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ネットワーク接続を確認して再試行してください。</t>
+          <t>Firebase Consoleでメールとパスワードによるログインを有効にしてください。</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>login_ui.too_many_requests</t>
+          <t>login_ui.network_error</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>リクエストが多すぎます。しばらくしてから再試行してください。</t>
+          <t>ネットワーク接続を確認して再試行してください。</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>login_ui.create_failed</t>
+          <t>login_ui.too_many_requests</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>アカウントを作成できませんでした。入力内容とFirebase認証設定を確認してください。</t>
+          <t>リクエストが多すぎます。しばらくしてから再試行してください。</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>login_ui.config_missing</t>
+          <t>login_ui.create_failed</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Firebase設定ファイルがありません。google-services.jsonまたはGoogleService-Info.plistをAssetsに追加してください。</t>
+          <t>アカウントを作成できませんでした。入力内容とFirebase認証設定を確認してください。</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>login_ui.dependencies</t>
+          <t>login_ui.config_missing</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Firebaseの依存関係を準備できませんでした：{0}</t>
+          <t>Firebase設定ファイルがありません。google-services.jsonまたはGoogleService-Info.plistをAssetsに追加してください。</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>login_ui.init_failed</t>
+          <t>login_ui.dependencies</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Firebaseの初期化に失敗しました。設定ファイルとプロジェクト接続を確認してください。</t>
+          <t>Firebaseの依存関係を準備できませんでした：{0}</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>connection_ui.title</t>
+          <t>login_ui.init_failed</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>マルチプレイ接続</t>
+          <t>Firebaseの初期化に失敗しました。設定ファイルとプロジェクト接続を確認してください。</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>connection_ui.subtitle</t>
+          <t>connection_ui.title</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>マルチプレイ接続端末</t>
+          <t>マルチプレイ接続</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>connection_ui.address</t>
+          <t>connection_ui.subtitle</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>サーバーアドレス</t>
+          <t>マルチプレイ接続端末</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>connection_ui.address_placeholder</t>
+          <t>connection_ui.address</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>サーバーIPまたはホスト名</t>
+          <t>サーバーアドレス</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>connection_ui.nickname</t>
+          <t>connection_ui.address_placeholder</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ニックネーム</t>
+          <t>サーバーIPまたはホスト名</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>connection_ui.host</t>
+          <t>connection_ui.nickname</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ローカルテスト · ホスト</t>
+          <t>ニックネーム</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>connection_ui.join</t>
+          <t>connection_ui.host</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>サーバーに接続</t>
+          <t>ローカルテスト · ホスト</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>connection_ui.server</t>
+          <t>connection_ui.join</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ローカルテスト · サーバー</t>
+          <t>サーバーに接続</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect</t>
+          <t>connection_ui.server</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>前回のセッションに復帰</t>
+          <t>ローカルテスト · サーバー</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>connection_ui.return_title</t>
+          <t>connection_ui.reconnect</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>タイトルに戻る</t>
+          <t>前回のセッションに復帰</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>connection_ui.settings_missing</t>
+          <t>connection_ui.return_title</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>セッション接続設定が見つかりません。</t>
+          <t>タイトルに戻る</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>connection_ui.invalid_nickname</t>
+          <t>connection_ui.settings_missing</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ニックネームは1～24文字で入力してください。タグと改行は使えません。</t>
+          <t>セッション接続設定が見つかりません。</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>connection_ui.invalid_address</t>
+          <t>connection_ui.invalid_nickname</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ポート番号を付けずにサーバーIPまたはホスト名を入力してください。</t>
+          <t>ニックネームは1～24文字で入力してください。タグと改行は使えません。</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>connection_ui.connecting</t>
+          <t>connection_ui.invalid_address</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>接続中…</t>
+          <t>ポート番号を付けずにサーバーIPまたはホスト名を入力してください。</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>connection_ui.server_running</t>
+          <t>connection_ui.connecting</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>専用サーバー稼働中 · 参加者待機</t>
+          <t>接続中…</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>connection_ui.no_session</t>
+          <t>connection_ui.server_running</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>このプロフィールに保存されたセッションはありません。</t>
+          <t>専用サーバー稼働中 · 参加者待機</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>connection_ui.profile_large</t>
+          <t>connection_ui.no_session</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>再接続プロフィールのデータが大きすぎます。</t>
+          <t>このプロフィールに保存されたセッションはありません。</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>connection_ui.profile_invalid</t>
+          <t>connection_ui.profile_large</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>再接続プロフィールのデータが無効です。</t>
+          <t>再接続プロフィールのデータが大きすぎます。</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>connection_ui.profile_read</t>
+          <t>connection_ui.profile_invalid</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>再接続プロフィールを読み込めません。形式とストレージ権限を確認してください。</t>
+          <t>再接続プロフィールのデータが無効です。</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>connection_ui.profile_path</t>
+          <t>connection_ui.profile_read</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>再接続プロフィールの保存先を使用できません。</t>
+          <t>再接続プロフィールを読み込めません。形式とストレージ権限を確認してください。</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>connection_ui.run_started</t>
+          <t>connection_ui.profile_path</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>開始済みのセッションには新規参加できません。</t>
+          <t>再接続プロフィールの保存先を使用できません。</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>connection_ui.connection_invalid</t>
+          <t>connection_ui.run_started</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>登録済み、または無効な接続です。</t>
+          <t>開始済みのセッションには新規参加できません。</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>connection_ui.full</t>
+          <t>connection_ui.connection_invalid</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>セッションが満員です。</t>
+          <t>登録済み、または無効な接続です。</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect_denied</t>
+          <t>connection_ui.full</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>再接続の資格を確認できません。</t>
+          <t>セッションが満員です。</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect_expired</t>
+          <t>connection_ui.reconnect_denied</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>再接続予約が存在しないか、有効期限が切れています。</t>
+          <t>再接続の資格を確認できません。</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>connection_ui.version_mismatch</t>
+          <t>connection_ui.reconnect_expired</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>サーバーとクライアントのビルドバージョンが一致しません。</t>
+          <t>再接続予約が存在しないか、有効期限が切れています。</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>connection_ui.passive_profile</t>
+          <t>connection_ui.version_mismatch</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>保存されたパッシブプロフィールを読み込めませんでした。</t>
+          <t>サーバーとクライアントのビルドバージョンが一致しません。</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>connection_ui.timeout</t>
+          <t>connection_ui.passive_profile</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>サーバーの参加承認がタイムアウトしました。</t>
+          <t>保存されたパッシブプロフィールを読み込めませんでした。</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>connection_ui.admitted</t>
+          <t>connection_ui.timeout</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>参加が承認されました</t>
+          <t>サーバーの参加承認がタイムアウトしました。</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>connection_ui.before_connect</t>
+          <t>connection_ui.admitted</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>未接続</t>
+          <t>参加が承認されました</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>connection_ui.waiting</t>
+          <t>connection_ui.before_connect</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>サーバー接続待機中</t>
+          <t>未接続</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>connection_ui.disconnected</t>
+          <t>connection_ui.waiting</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>サーバーとの接続が切れました。</t>
+          <t>サーバー接続待機中</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>upgrade_ui.request_failed</t>
+          <t>connection_ui.disconnected</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>強化リクエストを送信できませんでした。</t>
+          <t>サーバーとの接続が切れました。</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>upgrade_ui.request_pending</t>
+          <t>upgrade_ui.request_failed</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>アイテムと所持ゴールドを確認しています…</t>
+          <t>強化リクエストを送信できませんでした。</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>upgrade_ui.state_changed</t>
+          <t>upgrade_ui.request_pending</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>アイテムの状態が変わりました。もう一度選択してください。</t>
+          <t>アイテムと所持ゴールドを確認しています…</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>upgrade_ui.item_missing</t>
+          <t>upgrade_ui.state_changed</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>インベントリに対象のアイテムがありません。</t>
+          <t>アイテムの状態が変わりました。もう一度選択してください。</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>result_ui.stage</t>
+          <t>upgrade_ui.item_missing</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>最終到達ステージ</t>
+          <t>インベントリに対象のアイテムがありません。</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>result_ui.defeated</t>
+          <t>result_ui.stage</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>倒した敵</t>
+          <t>最終到達ステージ</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>result_ui.play_time</t>
+          <t>result_ui.defeated</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>プレイ時間</t>
+          <t>倒した敵</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>result_ui.credits</t>
+          <t>result_ui.play_time</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>獲得クレジット</t>
+          <t>プレイ時間</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>result_ui.retry</t>
+          <t>result_ui.credits</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>もう一度プレイ</t>
+          <t>獲得クレジット</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>result_ui.return_lobby</t>
+          <t>result_ui.retry</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>ロビーに戻る</t>
+          <t>もう一度プレイ</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>result_ui.leave_session</t>
+          <t>result_ui.return_lobby</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>セッションを退出</t>
+          <t>ロビーに戻る</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>result_ui.clear_description</t>
+          <t>result_ui.leave_session</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>全ステージをクリアしました！</t>
+          <t>セッションを退出</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>result_ui.defeat_description</t>
+          <t>result_ui.clear_description</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>今回の遠征は終了しました。</t>
+          <t>全ステージをクリアしました！</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>result_ui.data_waiting</t>
+          <t>result_ui.defeat_description</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>サーバーから結果を受信しています…</t>
+          <t>今回の遠征は終了しました。</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>result_ui.data_missing</t>
+          <t>result_ui.data_waiting</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>結果がまだ届いていません。待機するか退出できます。</t>
+          <t>サーバーから結果を受信しています…</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>result_ui.request_pending</t>
+          <t>result_ui.data_missing</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>サーバーの応答を待っています…</t>
+          <t>結果がまだ届いていません。待機するか退出できます。</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>result_ui.act_clear_description</t>
+          <t>result_ui.request_pending</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>アクトをクリアしました。</t>
+          <t>サーバーの応答を待っています…</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>result_ui.settle_description</t>
+          <t>result_ui.act_clear_description</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>精算が完了しました。</t>
+          <t>アクトをクリアしました。</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>result_ui.current_stage</t>
+          <t>result_ui.settle_description</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>現在の到達ステージ</t>
+          <t>精算が完了しました。</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>result_ui.farming_value</t>
+          <t>result_ui.current_stage</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>獲得価値</t>
+          <t>現在の到達ステージ</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>result_ui.continue</t>
+          <t>result_ui.farming_value</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>続ける</t>
+          <t>獲得価値</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>session_ui.end_host</t>
+          <t>result_ui.continue</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>ホストセッションを終了</t>
+          <t>続ける</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>session_ui.leave</t>
+          <t>session_ui.end_host</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>セッションを退出</t>
+          <t>ホストセッションを終了</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>session_ui.leave_temporarily</t>
+          <t>session_ui.leave</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>一時的に退出</t>
+          <t>セッションを退出</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>session_ui.confirm_end_host</t>
+          <t>session_ui.leave_temporarily</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>ホストセッションを終了しますか？</t>
+          <t>一時的に退出</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>session_ui.warn_end_host</t>
+          <t>session_ui.confirm_end_host</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>全員の接続と現在のプレイが終了します。</t>
+          <t>ホストセッションを終了しますか？</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>session_ui.confirm_leave</t>
+          <t>session_ui.warn_end_host</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>このセッションを退出しますか？</t>
+          <t>全員の接続と現在のプレイが終了します。</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>session_ui.warn_leave</t>
+          <t>session_ui.confirm_leave</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>参加権を放棄するため、このプレイには再接続できません。</t>
+          <t>このセッションを退出しますか？</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>session_ui.confirm_temporary_leave</t>
+          <t>session_ui.warn_leave</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>セッションから一時的に退出しますか？</t>
+          <t>参加権を放棄するため、このプレイには再接続できません。</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>session_ui.warn_temporary_leave</t>
+          <t>session_ui.confirm_temporary_leave</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>サーバーが稼働中なら5分以内に再接続できます。パーティーのゲームは続行されます。</t>
+          <t>セッションから一時的に退出しますか？</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>session_ui.passive_locked</t>
+          <t>session_ui.warn_temporary_leave</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>準備を解除するとパッシブを変更できます。</t>
+          <t>サーバーが稼働中なら5分以内に再接続できます。パーティーのゲームは続行されます。</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait</t>
+          <t>session_ui.passive_locked</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>結果を保存しています。少し待ってからお試しください。</t>
+          <t>準備を解除するとパッシブを変更できます。</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_host</t>
+          <t>session_ui.settlement_wait</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>参加者の結果を保存しています。保存完了後にセッションを終了してください。</t>
+          <t>結果を保存しています。少し待ってからお試しください。</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_player</t>
+          <t>session_ui.settlement_wait_host</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>{0}の結果を保存しています。少し待ってからお試しください。</t>
+          <t>参加者の結果を保存しています。保存完了後にセッションを終了してください。</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>session_ui.lobby_loading</t>
+          <t>session_ui.settlement_wait_player</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>ロビーの読み込みが終わってから出発してください。</t>
+          <t>{0}の結果を保存しています。少し待ってからお試しください。</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>session_ui.player_prefabs_missing</t>
+          <t>session_ui.lobby_loading</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>プレイヤーの準備が不完全です。再接続してください。</t>
+          <t>ロビーの読み込みが終わってから出発してください。</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>session_ui.session_missing</t>
+          <t>session_ui.player_prefabs_missing</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>参加中のセッションが見つかりません。</t>
+          <t>プレイヤーの準備が不完全です。再接続してください。</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>session_ui.unsupported_request</t>
+          <t>session_ui.session_missing</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>このロビー操作は利用できません。</t>
+          <t>参加中のセッションが見つかりません。</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>session_ui.return_lobby_denied</t>
+          <t>session_ui.unsupported_request</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>結果確定後、リーダーのみがパーティーをロビーに戻せます。</t>
+          <t>このロビー操作は利用できません。</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>session_ui.passive_invalid</t>
+          <t>session_ui.return_lobby_denied</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>パッシブのプロフィールを確認できません。</t>
+          <t>結果確定後、リーダーのみがパーティーをロビーに戻せます。</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>session_ui.party_not_ready</t>
+          <t>session_ui.passive_invalid</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>全員がキャラクターを選択し、準備を完了してください。</t>
+          <t>パッシブのプロフィールを確認できません。</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>preparation_ui.waiting</t>
+          <t>session_ui.party_not_ready</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>ゲームを準備しています…</t>
+          <t>全員がキャラクターを選択し、準備を完了してください。</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout</t>
+          <t>preparation_ui.waiting</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>ゲームの準備がタイムアウトしました。</t>
+          <t>ゲームを準備しています…</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout_retry</t>
+          <t>preparation_ui.timeout</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>ゲームの準備がタイムアウトしました。切断してもう一度お試しください。</t>
+          <t>ゲームの準備がタイムアウトしました。</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>preparation_ui.combat_failed</t>
+          <t>preparation_ui.timeout_retry</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>戦闘の準備に失敗しました。再接続してください。</t>
+          <t>ゲームの準備がタイムアウトしました。切断してもう一度お試しください。</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>preparation_ui.disconnected</t>
+          <t>preparation_ui.combat_failed</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>接続が終了しました。</t>
+          <t>戦闘の準備に失敗しました。再接続してください。</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>接続が終了しました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
           <t>preparation_ui.exit</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>退出</t>
         </is>
@@ -11444,7 +11480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B305"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13359,1751 +13395,1763 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rest_ui.potion_recharge</t>
+          <t>rest_ui.health_recovery_format</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>药水补充</t>
+          <t>恢复{0}%生命</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rest_ui.cost_format</t>
+          <t>rest_ui.potion_recharge</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>所需信用点 : {0}</t>
+          <t>药水补充</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rest_ui.complete_message</t>
+          <t>rest_ui.cost_format</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>消耗{0}信用点，恢复了{1}点生命和{2}个药水。</t>
+          <t>所需信用点 : {0}</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_chat</t>
+          <t>rest_ui.complete_message</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">[聊天] </t>
+          <t>消耗{0}信用点，恢复了{1}点生命和{2}个药水。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_acquisition</t>
+          <t>chat_ui.prefix_chat</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">[物品] </t>
+          <t xml:space="preserve">[聊天] </t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_warning</t>
+          <t>chat_ui.prefix_acquisition</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">[提示] </t>
+          <t xml:space="preserve">[物品] </t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>chat_ui.prefix_connection</t>
+          <t>chat_ui.prefix_warning</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">[连接] </t>
+          <t xml:space="preserve">[提示] </t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>chat_ui.item_fallback_name</t>
+          <t>chat_ui.prefix_connection</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>物品</t>
+          <t xml:space="preserve">[连接] </t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_cost_format</t>
+          <t>chat_ui.item_fallback_name</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 刷新</t>
+          <t>物品</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_free</t>
+          <t>shop_ui.reroll_cost_format</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>免费刷新</t>
+          <t>&lt;color=#FFEB04&gt;{0}&lt;/color&gt; 刷新</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>shop_ui.reroll_count_format</t>
+          <t>shop_ui.reroll_free</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>[ {0} ]</t>
+          <t>免费刷新</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>settings_ui.reset_confirm</t>
+          <t>shop_ui.reroll_count_format</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>要将设置恢复为默认值吗？</t>
+          <t>[ {0} ]</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>settings_ui.reset_warning</t>
+          <t>settings_ui.reset_confirm</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>当前所有设置都将恢复为默认值。</t>
+          <t>要将设置恢复为默认值吗？</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_confirm</t>
+          <t>settings_ui.reset_warning</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>要放弃游戏吗？</t>
+          <t>当前所有设置都将恢复为默认值。</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_warning</t>
+          <t>pause_ui.giveup_confirm</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>警告：当前游戏数据将会丢失。</t>
+          <t>要放弃游戏吗？</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm</t>
+          <t>pause_ui.giveup_warning</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>确定要放弃吗？</t>
+          <t>警告：当前游戏数据将会丢失。</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>pause_ui.giveup_reconfirm_warning</t>
+          <t>pause_ui.giveup_reconfirm</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>当前远征将被重置，且无法获得信用点。</t>
+          <t>确定要放弃吗？</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>pause_ui.save_and_quit_confirm</t>
+          <t>pause_ui.giveup_reconfirm_warning</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>要保存并退出游戏吗？</t>
+          <t>当前远征将被重置，且无法获得信用点。</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_confirm</t>
+          <t>pause_ui.save_and_quit_confirm</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>要结束主机会话吗？</t>
+          <t>要保存并退出游戏吗？</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>pause_ui.host_end_warning</t>
+          <t>pause_ui.host_end_confirm</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>所有参与者的连接和当前轮次都将结束。</t>
+          <t>要结束主机会话吗？</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>pause_ui.leave_confirm</t>
+          <t>pause_ui.host_end_warning</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>要离开此会话吗？</t>
+          <t>所有参与者的连接和当前轮次都将结束。</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>pause_ui.leave_warning</t>
+          <t>pause_ui.leave_confirm</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>你将放弃参与资格，且无法重新加入本轮。</t>
+          <t>要离开此会话吗？</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_confirm</t>
+          <t>pause_ui.leave_warning</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>要暂时离开会话吗？</t>
+          <t>你将放弃参与资格，且无法重新加入本轮。</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>pause_ui.temp_leave_warning</t>
+          <t>pause_ui.temp_leave_confirm</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>服务器保持运行期间，可在5分钟内重新连接。队伍的游戏将继续进行。</t>
+          <t>要暂时离开会话吗？</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>pause_ui.adjustment</t>
+          <t>pause_ui.temp_leave_warning</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>结算并结束</t>
+          <t>服务器保持运行期间，可在5分钟内重新连接。队伍的游戏将继续进行。</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>pause_ui.settle_confirm</t>
+          <t>pause_ui.adjustment</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>要结算并结束游戏吗？</t>
+          <t>结算并结束</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>pause_ui.settle_warning</t>
+          <t>pause_ui.settle_confirm</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>将获得持有信用点及物品原价的50%作为账号信用点，当前远征将被重置。</t>
+          <t>要结算并结束游戏吗？</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>login_ui.title</t>
+          <t>pause_ui.settle_warning</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>用户认证</t>
+          <t>将获得持有信用点及物品原价的50%作为账号信用点，当前远征将被重置。</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>login_ui.subtitle</t>
+          <t>login_ui.title</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>用户认证终端</t>
+          <t>用户认证</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>login_ui.account</t>
+          <t>login_ui.subtitle</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>用户认证终端</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>login_ui.email_placeholder</t>
+          <t>login_ui.account</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>电子邮箱</t>
+          <t>账号</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>login_ui.password</t>
+          <t>login_ui.email_placeholder</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>密码</t>
+          <t>电子邮箱</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>login_ui.confirm_password</t>
+          <t>login_ui.password</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>确认密码</t>
+          <t>密码</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>login_ui.submit</t>
+          <t>login_ui.confirm_password</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>登录</t>
+          <t>确认密码</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>login_ui.no_account</t>
+          <t>login_ui.submit</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>还没有账号？</t>
+          <t>登录</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>login_ui.create_account</t>
+          <t>login_ui.no_account</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>创建账号</t>
+          <t>还没有账号？</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>login_ui.create</t>
+          <t>login_ui.create_account</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>创建</t>
+          <t>创建账号</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>login_ui.has_account</t>
+          <t>login_ui.create</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>已有账号？</t>
+          <t>创建</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>login_ui.login</t>
+          <t>login_ui.has_account</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>登录</t>
+          <t>已有账号？</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>login_ui.footer</t>
+          <t>login_ui.login</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>安全访问终端</t>
+          <t>登录</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>login_ui.submitting</t>
+          <t>login_ui.footer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>正在登录…</t>
+          <t>安全访问终端</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>login_ui.creating</t>
+          <t>login_ui.submitting</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>正在创建账号…</t>
+          <t>正在登录…</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>login_ui.required</t>
+          <t>login_ui.creating</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>请输入邮箱和密码。</t>
+          <t>正在创建账号…</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>login_ui.account_required</t>
+          <t>login_ui.required</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>请输入账号和密码。</t>
+          <t>请输入邮箱和密码。</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>login_ui.confirm_required</t>
+          <t>login_ui.account_required</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>请再次输入密码。</t>
+          <t>请输入账号和密码。</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>login_ui.password_mismatch</t>
+          <t>login_ui.confirm_required</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>两次输入的密码不一致。</t>
+          <t>请再次输入密码。</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>login_ui.login_error</t>
+          <t>login_ui.password_mismatch</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>登录时发生错误。</t>
+          <t>两次输入的密码不一致。</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>login_ui.profile_incomplete</t>
+          <t>login_ui.login_error</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>账号已创建，但资料初始化失败。请重新登录。</t>
+          <t>登录时发生错误。</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>login_ui.created</t>
+          <t>login_ui.profile_incomplete</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>账号创建成功。请使用新账号登录。</t>
+          <t>账号已创建，但资料初始化失败。请重新登录。</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>login_ui.create_error</t>
+          <t>login_ui.created</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>创建账号时发生错误。</t>
+          <t>账号创建成功。请使用新账号登录。</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>login_ui.loader_missing</t>
+          <t>login_ui.create_error</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>场景加载器尚未就绪。请从Start场景运行。</t>
+          <t>创建账号时发生错误。</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>login_ui.scenes_missing</t>
+          <t>login_ui.loader_missing</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>请确认TitleScene和LoadingScene已加入构建。</t>
+          <t>场景加载器尚未就绪。请从Start场景运行。</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>login_ui.user_missing</t>
+          <t>login_ui.scenes_missing</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>登录结果中未找到用户信息。</t>
+          <t>请确认TitleScene和LoadingScene已加入构建。</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
+          <t>login_ui.user_missing</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>登录结果中未找到用户信息。</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>login_ui.auth_failed</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>登录失败。
 请检查邮箱、密码及Firebase认证设置。</t>
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>login_ui.firebase_login_error</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Firebase登录时发生错误。</t>
-        </is>
-      </c>
-    </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>login_ui.created_user_missing</t>
+          <t>login_ui.firebase_login_error</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>账号创建结果中未找到用户信息。</t>
+          <t>Firebase登录时发生错误。</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>login_ui.firebase_create_error</t>
+          <t>login_ui.created_user_missing</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>创建Firebase账号时发生错误。</t>
+          <t>账号创建结果中未找到用户信息。</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>login_ui.email_in_use</t>
+          <t>login_ui.firebase_create_error</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>此邮箱已被使用。</t>
+          <t>创建Firebase账号时发生错误。</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>login_ui.invalid_email</t>
+          <t>login_ui.email_in_use</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>请输入有效的邮箱地址。</t>
+          <t>此邮箱已被使用。</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>login_ui.password_policy</t>
+          <t>login_ui.invalid_email</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>请输入符合密码要求的密码。</t>
+          <t>请输入有效的邮箱地址。</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>login_ui.auth_disabled</t>
+          <t>login_ui.password_policy</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>请在Firebase Console启用邮箱和密码登录。</t>
+          <t>请输入符合密码要求的密码。</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>login_ui.network_error</t>
+          <t>login_ui.auth_disabled</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>请检查网络连接后重试。</t>
+          <t>请在Firebase Console启用邮箱和密码登录。</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>login_ui.too_many_requests</t>
+          <t>login_ui.network_error</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>请求过于频繁，请稍后重试。</t>
+          <t>请检查网络连接后重试。</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>login_ui.create_failed</t>
+          <t>login_ui.too_many_requests</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>无法创建账号。请检查输入内容及Firebase认证设置。</t>
+          <t>请求过于频繁，请稍后重试。</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>login_ui.config_missing</t>
+          <t>login_ui.create_failed</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>缺少Firebase配置文件。请将google-services.json或GoogleService-Info.plist添加到Assets。</t>
+          <t>无法创建账号。请检查输入内容及Firebase认证设置。</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>login_ui.dependencies</t>
+          <t>login_ui.config_missing</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>无法初始化Firebase依赖项：{0}</t>
+          <t>缺少Firebase配置文件。请将google-services.json或GoogleService-Info.plist添加到Assets。</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>login_ui.init_failed</t>
+          <t>login_ui.dependencies</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Firebase初始化失败。请检查配置文件及项目连接。</t>
+          <t>无法初始化Firebase依赖项：{0}</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>connection_ui.title</t>
+          <t>login_ui.init_failed</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>多人游戏连接</t>
+          <t>Firebase初始化失败。请检查配置文件及项目连接。</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>connection_ui.subtitle</t>
+          <t>connection_ui.title</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>多人游戏连接终端</t>
+          <t>多人游戏连接</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>connection_ui.address</t>
+          <t>connection_ui.subtitle</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>服务器地址</t>
+          <t>多人游戏连接终端</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>connection_ui.address_placeholder</t>
+          <t>connection_ui.address</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>服务器IP或主机名</t>
+          <t>服务器地址</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>connection_ui.nickname</t>
+          <t>connection_ui.address_placeholder</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>昵称</t>
+          <t>服务器IP或主机名</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>connection_ui.host</t>
+          <t>connection_ui.nickname</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>本地测试 · 主机</t>
+          <t>昵称</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>connection_ui.join</t>
+          <t>connection_ui.host</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>连接服务器</t>
+          <t>本地测试 · 主机</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>connection_ui.server</t>
+          <t>connection_ui.join</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>本地测试 · 服务器</t>
+          <t>连接服务器</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect</t>
+          <t>connection_ui.server</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>返回上次会话</t>
+          <t>本地测试 · 服务器</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>connection_ui.return_title</t>
+          <t>connection_ui.reconnect</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>返回标题界面</t>
+          <t>返回上次会话</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>connection_ui.settings_missing</t>
+          <t>connection_ui.return_title</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>未找到会话连接设置。</t>
+          <t>返回标题界面</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>connection_ui.invalid_nickname</t>
+          <t>connection_ui.settings_missing</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>请输入1至24个字符的昵称，不可使用标签或换行。</t>
+          <t>未找到会话连接设置。</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>connection_ui.invalid_address</t>
+          <t>connection_ui.invalid_nickname</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>请输入服务器IP或主机名，不要附加端口号。</t>
+          <t>请输入1至24个字符的昵称，不可使用标签或换行。</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>connection_ui.connecting</t>
+          <t>connection_ui.invalid_address</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>正在连接…</t>
+          <t>请输入服务器IP或主机名，不要附加端口号。</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>connection_ui.server_running</t>
+          <t>connection_ui.connecting</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>专用服务器运行中 · 等待玩家</t>
+          <t>正在连接…</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>connection_ui.no_session</t>
+          <t>connection_ui.server_running</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>此资料中没有保存的最近会话。</t>
+          <t>专用服务器运行中 · 等待玩家</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>connection_ui.profile_large</t>
+          <t>connection_ui.no_session</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>重连资料数据过大。</t>
+          <t>此资料中没有保存的最近会话。</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>connection_ui.profile_invalid</t>
+          <t>connection_ui.profile_large</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>重连资料数据无效。</t>
+          <t>重连资料数据过大。</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>connection_ui.profile_read</t>
+          <t>connection_ui.profile_invalid</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>无法读取重连资料。请检查文件格式及存储权限。</t>
+          <t>重连资料数据无效。</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>connection_ui.profile_path</t>
+          <t>connection_ui.profile_read</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>无法使用重连资料的存储位置。</t>
+          <t>无法读取重连资料。请检查文件格式及存储权限。</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>connection_ui.run_started</t>
+          <t>connection_ui.profile_path</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>无法加入已开始的会话。</t>
+          <t>无法使用重连资料的存储位置。</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>connection_ui.connection_invalid</t>
+          <t>connection_ui.run_started</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>连接已注册或无效。</t>
+          <t>无法加入已开始的会话。</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>connection_ui.full</t>
+          <t>connection_ui.connection_invalid</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>会话人数已满。</t>
+          <t>连接已注册或无效。</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect_denied</t>
+          <t>connection_ui.full</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>无法确认重连资格。</t>
+          <t>会话人数已满。</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>connection_ui.reconnect_expired</t>
+          <t>connection_ui.reconnect_denied</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>重连预约不存在或已过期。</t>
+          <t>无法确认重连资格。</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>connection_ui.version_mismatch</t>
+          <t>connection_ui.reconnect_expired</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>服务器与客户端的构建版本不一致。</t>
+          <t>重连预约不存在或已过期。</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>connection_ui.passive_profile</t>
+          <t>connection_ui.version_mismatch</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>无法读取已保存的被动技能资料。</t>
+          <t>服务器与客户端的构建版本不一致。</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>connection_ui.timeout</t>
+          <t>connection_ui.passive_profile</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>等待服务器批准加入超时。</t>
+          <t>无法读取已保存的被动技能资料。</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>connection_ui.admitted</t>
+          <t>connection_ui.timeout</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>已批准加入</t>
+          <t>等待服务器批准加入超时。</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>connection_ui.before_connect</t>
+          <t>connection_ui.admitted</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>尚未连接</t>
+          <t>已批准加入</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>connection_ui.waiting</t>
+          <t>connection_ui.before_connect</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>等待连接服务器</t>
+          <t>尚未连接</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>connection_ui.disconnected</t>
+          <t>connection_ui.waiting</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>与服务器的连接已断开。</t>
+          <t>等待连接服务器</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>upgrade_ui.request_failed</t>
+          <t>connection_ui.disconnected</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>无法发送强化请求。</t>
+          <t>与服务器的连接已断开。</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>upgrade_ui.request_pending</t>
+          <t>upgrade_ui.request_failed</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>正在确认物品和金币…</t>
+          <t>无法发送强化请求。</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>upgrade_ui.state_changed</t>
+          <t>upgrade_ui.request_pending</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>物品状态已变更，请重新选择。</t>
+          <t>正在确认物品和金币…</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>upgrade_ui.item_missing</t>
+          <t>upgrade_ui.state_changed</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>背包中未找到该物品。</t>
+          <t>物品状态已变更，请重新选择。</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>result_ui.stage</t>
+          <t>upgrade_ui.item_missing</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>最终到达关卡</t>
+          <t>背包中未找到该物品。</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>result_ui.defeated</t>
+          <t>result_ui.stage</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>击败敌人数</t>
+          <t>最终到达关卡</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>result_ui.play_time</t>
+          <t>result_ui.defeated</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>游戏时间</t>
+          <t>击败敌人数</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>result_ui.credits</t>
+          <t>result_ui.play_time</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>获得信用点</t>
+          <t>游戏时间</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>result_ui.retry</t>
+          <t>result_ui.credits</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>再玩一次</t>
+          <t>获得信用点</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>result_ui.return_lobby</t>
+          <t>result_ui.retry</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>返回大厅</t>
+          <t>再玩一次</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>result_ui.leave_session</t>
+          <t>result_ui.return_lobby</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>离开会话</t>
+          <t>返回大厅</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>result_ui.clear_description</t>
+          <t>result_ui.leave_session</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>已通关全部关卡！</t>
+          <t>离开会话</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>result_ui.defeat_description</t>
+          <t>result_ui.clear_description</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>本次远征已结束。</t>
+          <t>已通关全部关卡！</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>result_ui.data_waiting</t>
+          <t>result_ui.defeat_description</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>正在接收服务器结果…</t>
+          <t>本次远征已结束。</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>result_ui.data_missing</t>
+          <t>result_ui.data_waiting</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>尚未收到结果。您可以继续等待或离开。</t>
+          <t>正在接收服务器结果…</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>result_ui.request_pending</t>
+          <t>result_ui.data_missing</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>正在等待服务器响应…</t>
+          <t>尚未收到结果。您可以继续等待或离开。</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>result_ui.act_clear_description</t>
+          <t>result_ui.request_pending</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>已通关本章节。</t>
+          <t>正在等待服务器响应…</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>result_ui.settle_description</t>
+          <t>result_ui.act_clear_description</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>结算完成。</t>
+          <t>已通关本章节。</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>result_ui.current_stage</t>
+          <t>result_ui.settle_description</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>当前到达关卡</t>
+          <t>结算完成。</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>result_ui.farming_value</t>
+          <t>result_ui.current_stage</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>收获价值</t>
+          <t>当前到达关卡</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>result_ui.continue</t>
+          <t>result_ui.farming_value</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>继续</t>
+          <t>收获价值</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>session_ui.end_host</t>
+          <t>result_ui.continue</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>结束主机会话</t>
+          <t>继续</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>session_ui.leave</t>
+          <t>session_ui.end_host</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>离开会话</t>
+          <t>结束主机会话</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>session_ui.leave_temporarily</t>
+          <t>session_ui.leave</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>暂时离开</t>
+          <t>离开会话</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>session_ui.confirm_end_host</t>
+          <t>session_ui.leave_temporarily</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>要结束主机会话吗？</t>
+          <t>暂时离开</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>session_ui.warn_end_host</t>
+          <t>session_ui.confirm_end_host</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>所有玩家将断开连接，当前冒险将结束。</t>
+          <t>要结束主机会话吗？</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>session_ui.confirm_leave</t>
+          <t>session_ui.warn_end_host</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>要离开此会话吗？</t>
+          <t>所有玩家将断开连接，当前冒险将结束。</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>session_ui.warn_leave</t>
+          <t>session_ui.confirm_leave</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>您将放弃参与资格，无法重新加入本次冒险。</t>
+          <t>要离开此会话吗？</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>session_ui.confirm_temporary_leave</t>
+          <t>session_ui.warn_leave</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>要暂时离开此会话吗？</t>
+          <t>您将放弃参与资格，无法重新加入本次冒险。</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>session_ui.warn_temporary_leave</t>
+          <t>session_ui.confirm_temporary_leave</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>服务器在线时可在5分钟内重新连接。队伍的游戏会继续。</t>
+          <t>要暂时离开此会话吗？</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>session_ui.passive_locked</t>
+          <t>session_ui.warn_temporary_leave</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>取消准备后才能更改被动技能。</t>
+          <t>服务器在线时可在5分钟内重新连接。队伍的游戏会继续。</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait</t>
+          <t>session_ui.passive_locked</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>正在保存结果，请稍后重试。</t>
+          <t>取消准备后才能更改被动技能。</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_host</t>
+          <t>session_ui.settlement_wait</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>正在等待玩家结果保存。请在保存完成后结束会话。</t>
+          <t>正在保存结果，请稍后重试。</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>session_ui.settlement_wait_player</t>
+          <t>session_ui.settlement_wait_host</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>正在等待{0}的结果保存，请稍后重试。</t>
+          <t>正在等待玩家结果保存。请在保存完成后结束会话。</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>session_ui.lobby_loading</t>
+          <t>session_ui.settlement_wait_player</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>请等待大厅加载完成后再出发。</t>
+          <t>正在等待{0}的结果保存，请稍后重试。</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>session_ui.player_prefabs_missing</t>
+          <t>session_ui.lobby_loading</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>玩家配置不完整，请重新连接。</t>
+          <t>请等待大厅加载完成后再出发。</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>session_ui.session_missing</t>
+          <t>session_ui.player_prefabs_missing</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>未找到当前会话。</t>
+          <t>玩家配置不完整，请重新连接。</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>session_ui.unsupported_request</t>
+          <t>session_ui.session_missing</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>此大厅操作不可用。</t>
+          <t>未找到当前会话。</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>session_ui.return_lobby_denied</t>
+          <t>session_ui.unsupported_request</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>结果确认后，仅队长能带领队伍返回大厅。</t>
+          <t>此大厅操作不可用。</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>session_ui.passive_invalid</t>
+          <t>session_ui.return_lobby_denied</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>无法验证被动技能资料。</t>
+          <t>结果确认后，仅队长能带领队伍返回大厅。</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>session_ui.party_not_ready</t>
+          <t>session_ui.passive_invalid</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>所有玩家必须选择角色并准备就绪。</t>
+          <t>无法验证被动技能资料。</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>preparation_ui.waiting</t>
+          <t>session_ui.party_not_ready</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>正在准备游戏…</t>
+          <t>所有玩家必须选择角色并准备就绪。</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout</t>
+          <t>preparation_ui.waiting</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>游戏准备超时。</t>
+          <t>正在准备游戏…</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>preparation_ui.timeout_retry</t>
+          <t>preparation_ui.timeout</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>游戏准备超时，请断开连接后重试。</t>
+          <t>游戏准备超时。</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>preparation_ui.combat_failed</t>
+          <t>preparation_ui.timeout_retry</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>战斗准备失败，请重新连接。</t>
+          <t>游戏准备超时，请断开连接后重试。</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>preparation_ui.disconnected</t>
+          <t>preparation_ui.combat_failed</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>连接已结束。</t>
+          <t>战斗准备失败，请重新连接。</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
+          <t>preparation_ui.disconnected</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>连接已结束。</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
           <t>preparation_ui.exit</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>离开</t>
         </is>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B309"/>
+  <dimension ref="A1:B346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>닉네임을 1~24자로 입력해 주세요. 태그와 줄바꿈은 사용할 수 없습니다.</t>
+          <t>닉네임은 1~24자로 입력해 주세요.</t>
         </is>
       </c>
     </row>
@@ -4126,6 +4126,450 @@
       <c r="B309" t="inlineStr">
         <is>
           <t>나가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>settings_ui.label_allied_buff_effects</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>아군 버프 효과 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>settings_ui.desc_allied_buff_effects</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>다른 플레이어의 버프 범위와 버프 효과 표시 여부를 설정할 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_ready</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>전투 준비</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_progress</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>웨이브 {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_cleared</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>전원 처치! · 포털로 이동하세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>title_ui.logout</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>로그아웃</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>title_ui.signed_in</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>로그인 중</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>title_ui.signed_out</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>로그인 안 됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>title_ui.checking_account</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>계정 확인 중...</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>title_ui.syncing</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>동기화 중...</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>title_ui.account_changed_retry</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>로그인 계정이 변경되었습니다. 멀티플레이를 다시 선택해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>title_ui.local_progress_kept</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>로컬 진행도는 보존했습니다. 인터넷 연결을 확인하고 동기화를 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>title_ui.scene_missing</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>{0}과 LoadingScene의 빌드 등록을 확인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>title_ui.multiplayer_error</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>멀티플레이 계정 준비 중 오류가 발생했습니다. 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>title_ui.logout_disconnect_first</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>멀티플레이 연결을 종료한 뒤 로그아웃해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>title_ui.logout_test_account</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>개발 테스트 계정은 실행 중 로그아웃할 수 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>title_ui.logout_failed</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>로그아웃하지 못했습니다. 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>login_ui.back</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>뒤로 가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>login_ui.cached_session_failed</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>저장된 로그인 상태를 확인하지 못했습니다. 다시 로그인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>login_ui.multiplayer_login_required</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>멀티플레이에 진입하려면 로그인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>login_ui.account_changed</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>로그인 계정이 변경되었습니다. 다시 로그인해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>connection_ui.login_required</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>멀티플레이는 로그인이 필요합니다. 메인 화면에서 멀티플레이를 선택해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>connection_ui.syncing_progress</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>로컬 진행도를 동기화하는 중…</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>connection_ui.prepare_failed</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>연결 준비 실패: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>connection_ui.sync_retry</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>로컬 진행도는 보존했습니다. 인터넷 연결을 확인하고 멀티플레이 동기화를 다시 시도해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>connection_ui.sync_incomplete</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>로컬 진행도는 보존했습니다. 멀티플레이 동기화가 끝나지 않아 진입하지 않았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>connection_ui.account_changed</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>로그인 계정이 변경되었습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>stage_select_ui.normal_enemy</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>일반 적</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>stage_select_ui.elite_enemy</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>엘리트 적</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>stage_select_ui.camp</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>캠프</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>stage_select_ui.unknown</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>미지</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>title_ui.single_play</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>싱글 플레이</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>title_ui.multi_play</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>멀티 플레이</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>title_ui.continue</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>이어하기</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>title_ui.passive_skill</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>패시브 스킬</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>title_ui.settings</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>환경 설정</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>title_ui.quit</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>게임 종료</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B309"/>
+  <dimension ref="A1:B346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7045,7 +7489,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Enter a nickname of 1–24 characters without tags or line breaks.</t>
+          <t>Enter a nickname of 1–24 characters.</t>
         </is>
       </c>
     </row>
@@ -7850,6 +8294,450 @@
       <c r="B309" t="inlineStr">
         <is>
           <t>Leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>settings_ui.label_allied_buff_effects</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Ally Buff Effects</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>settings_ui.desc_allied_buff_effects</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>You can set whether other players' buff ranges and buff effects are shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_ready</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Get Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_progress</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Wave {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_cleared</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>All enemies defeated! · Head to the portal</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>title_ui.logout</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Log Out</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>title_ui.signed_in</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Signed In</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>title_ui.signed_out</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Not Signed In</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>title_ui.checking_account</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Checking account...</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>title_ui.syncing</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Syncing...</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>title_ui.account_changed_retry</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>The signed-in account has changed. Please select Multiplayer again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>title_ui.local_progress_kept</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Your local progress has been kept. Check your internet connection and try syncing again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>title_ui.scene_missing</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Check that {0} and LoadingScene are registered in the build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>title_ui.multiplayer_error</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>An error occurred while preparing your multiplayer account. Please try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>title_ui.logout_disconnect_first</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Please end the multiplayer connection before logging out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>title_ui.logout_test_account</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>The development test account cannot log out while running.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>title_ui.logout_failed</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Could not log out. Please try again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>login_ui.back</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>login_ui.cached_session_failed</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Could not verify the saved sign-in. Please sign in again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>login_ui.multiplayer_login_required</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Please sign in to enter multiplayer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>login_ui.account_changed</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>The signed-in account has changed. Please sign in again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>connection_ui.login_required</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Multiplayer requires signing in. Please select Multiplayer from the main screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>connection_ui.syncing_progress</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Syncing local progress…</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>connection_ui.prepare_failed</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Connection setup failed: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>connection_ui.sync_retry</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Your local progress has been kept. Check your internet connection and retry multiplayer sync.</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>connection_ui.sync_incomplete</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Your local progress has been kept. Multiplayer sync did not finish, so you did not enter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>connection_ui.account_changed</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>The signed-in account has changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>stage_select_ui.normal_enemy</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Normal Enemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>stage_select_ui.elite_enemy</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Elite Enemy</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>stage_select_ui.camp</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Camp</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>stage_select_ui.unknown</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>title_ui.single_play</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Single Play</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>title_ui.multi_play</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Multiplayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>title_ui.continue</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Continue</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>title_ui.passive_skill</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Passive Skills</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>title_ui.settings</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>title_ui.quit</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Quit Game</t>
         </is>
       </c>
     </row>
@@ -7864,7 +8752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B309"/>
+  <dimension ref="A1:B346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10769,7 +11657,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>ニックネームは1～24文字で入力してください。タグと改行は使えません。</t>
+          <t>ニックネームは1～24文字で入力してください。</t>
         </is>
       </c>
     </row>
@@ -11574,6 +12462,450 @@
       <c r="B309" t="inlineStr">
         <is>
           <t>退出</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>settings_ui.label_allied_buff_effects</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>味方バフ効果表示</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>settings_ui.desc_allied_buff_effects</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>他のプレイヤーのバフ範囲とバフ効果を表示するかどうかを設定できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_ready</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>戦闘準備</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_progress</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>ウェーブ {0}/{1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_cleared</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>敵を全滅！ · ポータルへ移動してください</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>title_ui.logout</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>ログアウト</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>title_ui.signed_in</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>ログイン中</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>title_ui.signed_out</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>未ログイン</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>title_ui.checking_account</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>アカウントを確認中...</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>title_ui.syncing</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>同期中...</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>title_ui.account_changed_retry</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>ログインアカウントが変更されました。マルチプレイをもう一度選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>title_ui.local_progress_kept</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>ローカルの進行状況は保存されています。インターネット接続を確認して、もう一度同期してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>title_ui.scene_missing</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>{0}とLoadingSceneのビルド登録を確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>title_ui.multiplayer_error</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>マルチプレイ用アカウントの準備中にエラーが発生しました。もう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>title_ui.logout_disconnect_first</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>マルチプレイの接続を終了してからログアウトしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>title_ui.logout_test_account</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>開発用テストアカウントは実行中にログアウトできません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>title_ui.logout_failed</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>ログアウトできませんでした。もう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>login_ui.back</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>login_ui.cached_session_failed</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>保存されたログイン状態を確認できませんでした。もう一度ログインしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>login_ui.multiplayer_login_required</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>マルチプレイに入るにはログインしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>login_ui.account_changed</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>ログインアカウントが変更されました。もう一度ログインしてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>connection_ui.login_required</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>マルチプレイにはログインが必要です。メイン画面でマルチプレイを選択してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>connection_ui.syncing_progress</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>ローカルの進行状況を同期中…</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>connection_ui.prepare_failed</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>接続準備に失敗しました: {0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>connection_ui.sync_retry</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>ローカルの進行状況は保存されています。インターネット接続を確認して、マルチプレイの同期をもう一度お試しください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>connection_ui.sync_incomplete</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ローカルの進行状況は保存されています。マルチプレイの同期が完了しなかったため、入室しませんでした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>connection_ui.account_changed</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>ログインアカウントが変更されました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>stage_select_ui.normal_enemy</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>通常の敵</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>stage_select_ui.elite_enemy</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>エリート敵</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>stage_select_ui.camp</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>キャンプ</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>stage_select_ui.unknown</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>title_ui.single_play</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>シングルプレイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>title_ui.multi_play</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>マルチプレイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>title_ui.continue</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>続きから</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>title_ui.passive_skill</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>パッシブスキル</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>title_ui.settings</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>title_ui.quit</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>ゲーム終了</t>
         </is>
       </c>
     </row>
@@ -11588,7 +12920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B309"/>
+  <dimension ref="A1:B346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14493,7 +15825,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>请输入1至24个字符的昵称，不可使用标签或换行。</t>
+          <t>请输入1至24个字符的昵称。</t>
         </is>
       </c>
     </row>
@@ -15298,6 +16630,450 @@
       <c r="B309" t="inlineStr">
         <is>
           <t>离开</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>settings_ui.label_allied_buff_effects</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>友方增益效果显示</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>settings_ui.desc_allied_buff_effects</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>可以设置是否显示其他玩家的增益范围和增益效果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_ready</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>战斗准备</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_progress</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>第 {0}/{1} 波</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>hud_ui.wave_cleared</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>敌人已全部击败！· 请前往传送门</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>title_ui.logout</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>退出登录</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>title_ui.signed_in</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>已登录</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>title_ui.signed_out</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>未登录</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>title_ui.checking_account</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>正在确认账户...</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>title_ui.syncing</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>正在同步...</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>title_ui.account_changed_retry</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>登录账户已更改。请重新选择多人游戏。</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>title_ui.local_progress_kept</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>本地进度已保留。请检查网络连接后重新同步。</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>title_ui.scene_missing</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>请确认 {0} 和 LoadingScene 已加入构建。</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>title_ui.multiplayer_error</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>准备多人游戏账户时出错。请重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>title_ui.logout_disconnect_first</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>请先结束多人游戏连接再退出登录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>title_ui.logout_test_account</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>开发测试账户在运行期间无法退出登录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>title_ui.logout_failed</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>无法退出登录。请重试。</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>login_ui.back</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>返回</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>login_ui.cached_session_failed</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>无法确认已保存的登录状态。请重新登录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>login_ui.multiplayer_login_required</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>请登录以进入多人游戏。</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>login_ui.account_changed</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>登录账户已更改。请重新登录。</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>connection_ui.login_required</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>多人游戏需要登录。请在主界面选择多人游戏。</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>connection_ui.syncing_progress</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>正在同步本地进度…</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>connection_ui.prepare_failed</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>连接准备失败：{0}</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>connection_ui.sync_retry</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>本地进度已保留。请检查网络连接后重试多人游戏同步。</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>connection_ui.sync_incomplete</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>本地进度已保留。多人游戏同步未完成，因此未进入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>connection_ui.account_changed</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>登录账户已更改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>stage_select_ui.normal_enemy</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>普通敌人</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>stage_select_ui.elite_enemy</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>精英敌人</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>stage_select_ui.camp</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>营地</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>stage_select_ui.unknown</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>title_ui.single_play</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>单人游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>title_ui.multi_play</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>多人游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>title_ui.continue</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>继续游戏</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>title_ui.passive_skill</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>被动技能</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>title_ui.settings</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>设置</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>title_ui.quit</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>退出游戏</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B346"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4570,6 +4570,66 @@
       <c r="B346" t="inlineStr">
         <is>
           <t>게임 종료</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>title_ui.guest</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>title_ui.logout_confirm</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>로그아웃할까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>title_ui.logout_guest_notice</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>로그아웃하면 싱글 플레이는 게스트 저장으로 전환됩니다. 계정 진행도는 다음 로그인 때 그대로 이어집니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_question</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>이 계정에는 아직 진행도가 없습니다. 게스트로 플레이한 진행도를 이 계정으로 가져올까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_notice</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>가져오지 않으면 새 진행도로 시작하고, 게스트 진행도는 이 기기에 그대로 남습니다.</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B346"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8738,6 +8798,66 @@
       <c r="B346" t="inlineStr">
         <is>
           <t>Quit Game</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>title_ui.guest</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>title_ui.logout_confirm</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Log out?</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>title_ui.logout_guest_notice</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>After logging out, Single Play switches to the guest save. Your account progress continues the next time you log in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_question</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>This account has no progress yet. Bring your guest progress into this account?</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_notice</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>If you skip this, the account starts fresh and your guest progress stays on this device.</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B346"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12906,6 +13026,66 @@
       <c r="B346" t="inlineStr">
         <is>
           <t>ゲーム終了</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>title_ui.guest</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>title_ui.logout_confirm</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>ログアウトしますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>title_ui.logout_guest_notice</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>ログアウトするとシングルプレイはゲストのセーブに切り替わります。アカウントの進行状況は次回ログイン時にそのまま引き継がれます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_question</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>このアカウントにはまだ進行状況がありません。ゲストでプレイした進行状況をこのアカウントに引き継ぎますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_notice</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>引き継がない場合は新しい進行状況で始まり、ゲストの進行状況はこの端末に残ります。</t>
         </is>
       </c>
     </row>
@@ -12920,7 +13100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B346"/>
+  <dimension ref="A1:B351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17077,6 +17257,66 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>title_ui.guest</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>title_ui.logout_confirm</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>要退出登录吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>title_ui.logout_guest_notice</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>退出登录后，单人游戏将切换为访客存档。账号进度将在下次登录时继续。</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_question</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>此账号尚无进度。要将访客游玩的进度导入此账号吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_notice</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>若不导入，将以新进度开始，访客进度会保留在本设备上。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4684,22 +4684,46 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>login_ui.guest_import_question</t>
+          <t>title_ui.new_game_confirm</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>이 계정에는 아직 진행도가 없습니다. 게스트로 플레이한 진행도를 이 계정으로 가져올까요?</t>
+          <t>새 게임을 시작하시겠습니까?</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
+          <t>title_ui.new_game_warning</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>진행 중인 원정이 사라지고 처음부터 시작합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_question</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>이 계정에는 아직 진행도가 없습니다. 게스트로 플레이한 진행도를 이 계정으로 가져올까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
           <t>login_ui.guest_import_notice</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>가져오지 않으면 새 진행도로 시작하고, 게스트 진행도는 이 기기에 그대로 남습니다.</t>
         </is>
@@ -4716,7 +4740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8984,22 +9008,46 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>login_ui.guest_import_question</t>
+          <t>title_ui.new_game_confirm</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>This account has no progress yet. Bring your guest progress into this account?</t>
+          <t>Start a new game?</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
+          <t>title_ui.new_game_warning</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Your current expedition will be lost and you will start from the beginning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_question</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>This account has no progress yet. Bring your guest progress into this account?</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
           <t>login_ui.guest_import_notice</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>If you skip this, the account starts fresh and your guest progress stays on this device.</t>
         </is>
@@ -9016,7 +9064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13284,22 +13332,46 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>login_ui.guest_import_question</t>
+          <t>title_ui.new_game_confirm</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>このアカウントにはまだ進行状況がありません。ゲストでプレイした進行状況をこのアカウントに引き継ぎますか？</t>
+          <t>新しいゲームを始めますか？</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
+          <t>title_ui.new_game_warning</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>進行中の遠征は失われ、最初から始まります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_question</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>このアカウントにはまだ進行状況がありません。ゲストでプレイした進行状況をこのアカウントに引き継ぎますか？</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
           <t>login_ui.guest_import_notice</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>引き継がない場合は新しい進行状況で始まり、ゲストの進行状況はこの端末に残ります。</t>
         </is>
@@ -13316,7 +13388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17584,22 +17656,46 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>login_ui.guest_import_question</t>
+          <t>title_ui.new_game_confirm</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>此账号尚无进度。要将访客游玩的进度导入此账号吗？</t>
+          <t>要开始新游戏吗？</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
+          <t>title_ui.new_game_warning</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>当前进行中的远征将会丢失，并从头开始。</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>login_ui.guest_import_question</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>此账号尚无进度。要将访客游玩的进度导入此账号吗？</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
           <t>login_ui.guest_import_notice</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>若不导入，将以新进度开始，访客进度会保留在本设备上。</t>
         </is>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -4257,7 +4257,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>전원 처치! · 포털로 이동하세요</t>
+          <t>전원 처치! 포탈로 이동하세요</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>All enemies defeated! · Head to the portal</t>
+          <t>All enemies defeated! Head to the portal</t>
         </is>
       </c>
     </row>
@@ -12905,7 +12905,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>敵を全滅！ · ポータルへ移動してください</t>
+          <t>敵を全滅！ ポータルへ移動してください</t>
         </is>
       </c>
     </row>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>敌人已全部击败！· 请前往传送门</t>
+          <t>敌人已全部击败！ 请前往传送门</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
+++ b/Assets/Resources/DataFiles/UIData/1. ExcelFile/UILabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4726,6 +4726,18 @@
       <c r="B359" t="inlineStr">
         <is>
           <t>가져오지 않으면 새 진행도로 시작하고, 게스트 진행도는 이 기기에 그대로 남습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>title_ui.tutorial</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>튜토리얼</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9050,6 +9062,18 @@
       <c r="B359" t="inlineStr">
         <is>
           <t>If you skip this, the account starts fresh and your guest progress stays on this device.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>title_ui.tutorial</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Tutorial</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13374,6 +13398,18 @@
       <c r="B359" t="inlineStr">
         <is>
           <t>引き継がない場合は新しい進行状況で始まり、ゲストの進行状況はこの端末に残ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>title_ui.tutorial</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>チュートリアル</t>
         </is>
       </c>
     </row>
@@ -13388,7 +13424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B359"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17701,6 +17737,18 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>title_ui.tutorial</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>教程</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
